--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$S$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$S$270</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25">
@@ -1101,7 +1101,7 @@
     <row r="37">
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-3 (FRS_BRD03_PRODUCT_MAINTENANCE.md). 39 FRs, 31 BRD IDs, 135 test conditions, 8 scenarios, 263 test cases (122 positive, 141 negative), 150 with an automation reference.</t>
+          <t>Source: FRS BRD-3 (FRS_BRD03_PRODUCT_MAINTENANCE.md). 39 FRs, 31 BRD IDs, 135 test conditions, 8 scenarios, 266 test cases (123 positive, 143 negative), 153 with an automation reference.</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>A request without negotiation (for example RETIRE) goes to FOR_MANCOM without a round.</t>
+          <t>A request without negotiation (for example a retirement) goes to ManCom sign-off without a round.</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>A RETIRE request retires the product at the MBS step; other request types cannot retire.</t>
+          <t>A retirement request retires the product at the MBS step; other request types cannot retire.</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-051.2-01, TC-PM-051.2-02, TC-PM-051.2-03</t>
+          <t>TC-PM-051.2-01, TC-PM-051.2-02, TC-PM-051.2-03, TC-PM-051.2-04, TC-PM-051.2-05, TC-PM-051.2-06</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Sign-off, set-up and release. TSU submits the requirements pack, ManCom signs off, MBS sets up the version, the validator releases it and TSU sends the advisory; a RETIRE request retires a package.</t>
+          <t>Sign-off, set-up and release. TSU submits the requirements pack, ManCom signs off, MBS sets up the version, the validator releases it and TSU sends the advisory; a retirement request retires a package.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -11537,7 +11537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S267"/>
+  <dimension ref="A1:S270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17653,7 +17653,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>A RETIRE request goes to ManCom without negotiation</t>
+          <t>A retirement request goes to ManCom without negotiation</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="J79" s="12" t="inlineStr">
         <is>
-          <t>A RETIRE request on MTR32 recommended by tsulead.
+          <t>A Retire package request on MTR32 recommended by tsulead.
 Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>A RENEW request with Negotiation required unticked, recommended.
+          <t>A Renew package request with Negotiation required unticked, recommended.
 Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
@@ -24128,7 +24128,7 @@
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>Retire MTR32 through a RETIRE request</t>
+          <t>Retire MTR32 through a retirement request</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
@@ -24153,7 +24153,7 @@
       </c>
       <c r="J160" s="12" t="inlineStr">
         <is>
-          <t>RETIRE request on MTR32 signed off by mancom (WITH_MBS).
+          <t>Retire package request on MTR32 signed off by mancom (With MBS for set-up).
 Data: TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>Set up a version on a RETIRE request</t>
+          <t>Set up a version on a retirement request</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="K161" s="12" t="inlineStr">
         <is>
-          <t>1. On the RETIRE request click Set up package version (API).</t>
+          <t>1. On the retirement request click Set up package version (API).</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>Retire on a RENEW request</t>
+          <t>Retire on a renewal request</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
@@ -24328,7 +24328,7 @@
       <c r="L162" s="12" t="inlineStr">
         <is>
           <t>Refused.
-Message "Only a RETIRE request retires the package" (PKG_REQUEST_TYPE_MISMATCH).</t>
+Message "Only a request to retire the package can retire it" (PKG_REQUEST_TYPE_MISMATCH).</t>
         </is>
       </c>
       <c r="M162" s="12" t="inlineStr">
@@ -25129,13 +25129,14 @@
       <c r="K172" s="12" t="inlineStr">
         <is>
           <t>1. Click Request Rate Exception; rate 2.50, reason "Loyal client"; submit.
-2. As approver open My Approvals; approve the exception.
-3. As ao submit the quotation again.</t>
+2. As approver open My Approvals and click the rate exception; the exception record opens.
+3. Check the requested rate against the scheme in force; click Approve, write a comment and confirm.
+4. As ao open the notice, then submit the quotation again.</t>
         </is>
       </c>
       <c r="L172" s="12" t="inlineStr">
         <is>
-          <t>The exception gets a reference number; after approval the quotation is submitted and shows the exception reference.</t>
+          <t>The exception gets a reference number; the record shows Approved with the approver, the date and the comment; the requester is notified; the quotation is submitted and shows the exception reference.</t>
         </is>
       </c>
       <c r="M172" s="12" t="inlineStr">
@@ -25145,7 +25146,7 @@
       </c>
       <c r="N172" s="12" t="inlineStr">
         <is>
-          <t>RatingSchemeIT#quotationAndAccountsCarryTheVersionAndSubmissionNeedsTheException; CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp</t>
+          <t>RatingSchemeIT#theApproverDecidesTheExceptionOnItsRecordOpenedFromMyApprovals; RatingSchemeIT#quotationAndAccountsCarryTheVersionAndSubmissionNeedsTheException; CatalogProductMaintenanceApiIT#theApproverApprovesOrRejectsAnExceptionOnItsRecordOverHttp</t>
         </is>
       </c>
       <c r="O172" s="27" t="inlineStr">
@@ -25181,7 +25182,7 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>Rate exception with a past validity date</t>
+          <t>Rate exception rejected without a reason</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
@@ -25211,13 +25212,13 @@
       </c>
       <c r="K173" s="12" t="inlineStr">
         <is>
-          <t>1. Request Rate Exception with validity date yesterday.</t>
+          <t>1. As approver open the pending exception from My Approvals; click Reject and leave the reason blank.</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST).</t>
+          <t>The Reject button of the confirmation stays disabled; the server refuses a rejection without a reason.
+Message "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED).</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
@@ -25225,7 +25226,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N173" s="12" t="inlineStr"/>
+      <c r="N173" s="12" t="inlineStr">
+        <is>
+          <t>RatingSchemeIT#theApproverDecidesTheExceptionOnItsRecordOpenedFromMyApprovals; CatalogProductMaintenanceApiIT#theApproverApprovesOrRejectsAnExceptionOnItsRecordOverHttp</t>
+        </is>
+      </c>
       <c r="O173" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -25239,7 +25244,7 @@
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-051.3-01</t>
+          <t>TC-PM-051.2-04</t>
         </is>
       </c>
       <c r="B174" s="12" t="inlineStr">
@@ -25259,12 +25264,12 @@
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>Version number on quotation, account and invoice</t>
+          <t>Rate exception rejected with its reason</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="G174" s="12" t="inlineStr">
@@ -25274,10 +25279,14 @@
       </c>
       <c r="H174" s="12" t="inlineStr">
         <is>
-          <t>Booking &gt; Booking Workbench &gt; Booked Invoice</t>
-        </is>
-      </c>
-      <c r="I174" s="12" t="inlineStr"/>
+          <t>Quotation / Proposal &gt; New Quotation</t>
+        </is>
+      </c>
+      <c r="I174" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-22</t>
+        </is>
+      </c>
       <c r="J174" s="12" t="inlineStr">
         <is>
           <t>Data: TD-PM-14 Masked quotation data</t>
@@ -25285,13 +25294,14 @@
       </c>
       <c r="K174" s="12" t="inlineStr">
         <is>
-          <t>1. Accept the quotation, create the account and book the invoice (BRD-1 flow).
-2. Open the quotation, the account and the booked invoice.</t>
+          <t>1. As approver open the pending exception; click Reject, write the reason and confirm.
+2. As ao open the quotation and submit it.</t>
         </is>
       </c>
       <c r="L174" s="12" t="inlineStr">
         <is>
-          <t>All three show the MTR10 version that priced the quotation.</t>
+          <t>The record shows Rejected with the reason; the requester is notified with the reason; the submission is still refused.
+Message "Package MTR10 is priced on the current rate scheme: rate 2.50% needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT).</t>
         </is>
       </c>
       <c r="M174" s="12" t="inlineStr">
@@ -25301,7 +25311,7 @@
       </c>
       <c r="N174" s="12" t="inlineStr">
         <is>
-          <t>RatingSchemeIT#quotationAndAccountsCarryTheVersionAndSubmissionNeedsTheException</t>
+          <t>RatingSchemeIT#aRejectedExceptionKeepsItsReasonAndNeverPricesTheTransaction; CatalogProductMaintenanceApiIT#theApproverApprovesOrRejectsAnExceptionOnItsRecordOverHttp</t>
         </is>
       </c>
       <c r="O174" s="27" t="inlineStr">
@@ -25317,7 +25327,7 @@
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-051.4-01</t>
+          <t>TC-PM-051.2-05</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
@@ -25337,7 +25347,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>Quotation on a package with no version in force</t>
+          <t>The requester cannot decide the exception</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -25362,19 +25372,18 @@
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>A packaged product whose only version is effective next month.
-Data: TD-PM-14 Masked quotation data</t>
+          <t>Data: TD-PM-14 Masked quotation data</t>
         </is>
       </c>
       <c r="K175" s="12" t="inlineStr">
         <is>
-          <t>1. Quote the product today.</t>
+          <t>1. As the user who requested the exception, open its record.</t>
         </is>
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "Package &lt;code&gt; has no released version in force on &lt;date&gt;" (PRODUCT_NOT_SELLABLE).</t>
+          <t>No Approve or Reject button; a decision sent by the requester is refused.
+Message "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION).</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
@@ -25382,7 +25391,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N175" s="12" t="inlineStr"/>
+      <c r="N175" s="12" t="inlineStr">
+        <is>
+          <t>RatingSchemeIT#aRejectedExceptionKeepsItsReasonAndNeverPricesTheTransaction</t>
+        </is>
+      </c>
       <c r="O175" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -25396,7 +25409,7 @@
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-051.1-02</t>
+          <t>TC-PM-051.2-06</t>
         </is>
       </c>
       <c r="B176" s="12" t="inlineStr">
@@ -25416,12 +25429,12 @@
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>Renewal and endorsement keep the version of the original account</t>
+          <t>Rate exception with a past validity date</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G176" s="12" t="inlineStr">
@@ -25431,12 +25444,12 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Premium Calculator</t>
+          <t>Quotation / Proposal &gt; New Quotation</t>
         </is>
       </c>
       <c r="I176" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-21</t>
+          <t>SCR-PM-22</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
@@ -25446,12 +25459,13 @@
       </c>
       <c r="K176" s="12" t="inlineStr">
         <is>
-          <t>1. In the Premium Calculator choose purpose Renewal for an account sold on MTR10 version 1.</t>
+          <t>1. Request Rate Exception with validity date yesterday.</t>
         </is>
       </c>
       <c r="L176" s="12" t="inlineStr">
         <is>
-          <t>The premium uses version 1, not the version in force.</t>
+          <t>Refused.
+Message "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST).</t>
         </is>
       </c>
       <c r="M176" s="12" t="inlineStr">
@@ -25459,11 +25473,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N176" s="12" t="inlineStr">
-        <is>
-          <t>RatingSchemeIT#renewalsAndEndorsementsUseTheirOwnVersion</t>
-        </is>
-      </c>
+      <c r="N176" s="12" t="inlineStr"/>
       <c r="O176" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -25477,7 +25487,7 @@
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-052.1-01</t>
+          <t>TC-PM-051.3-01</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
@@ -25487,50 +25497,49 @@
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-052</t>
+          <t>FR-PM-051</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>BRPM.006</t>
+          <t>BRPM.007</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>Daily job expires a package whose end date passed</t>
+          <t>Version number on quotation, account and invoice</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; Scheduled Jobs</t>
+          <t>Booking &gt; Booking Workbench &gt; Booked Invoice</t>
         </is>
       </c>
       <c r="I177" s="12" t="inlineStr"/>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>In the test environment the end date of PAR25 is set to yesterday.
-Data: TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-14 Masked quotation data</t>
         </is>
       </c>
       <c r="K177" s="12" t="inlineStr">
         <is>
-          <t>1. Run the job PACKAGE_VERSION_LIFECYCLE from Administration &gt; Scheduled Jobs.
-2. As mbs filter Products by Expired.</t>
+          <t>1. Accept the quotation, create the account and book the invoice (BRD-1 flow).
+2. Open the quotation, the account and the booked invoice.</t>
         </is>
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>PAR25 and its version are EXPIRED and tagged Expired; PKG_NEGOTIATE and PRODUCT_MAINTAIN holders are notified.</t>
+          <t>All three show the MTR10 version that priced the quotation.</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
@@ -25540,7 +25549,7 @@
       </c>
       <c r="N177" s="12" t="inlineStr">
         <is>
-          <t>CatalogVersionIT#packagesExpireAndRetireWithoutBeingDeleted</t>
+          <t>RatingSchemeIT#quotationAndAccountsCarryTheVersionAndSubmissionNeedsTheException</t>
         </is>
       </c>
       <c r="O177" s="27" t="inlineStr">
@@ -25556,7 +25565,7 @@
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-052.1-02</t>
+          <t>TC-PM-051.4-01</t>
         </is>
       </c>
       <c r="B178" s="12" t="inlineStr">
@@ -25566,17 +25575,17 @@
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-052</t>
+          <t>FR-PM-051</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>BRPM.006</t>
+          <t>BRPM.007</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
         <is>
-          <t>Quotation on an expired package</t>
+          <t>Quotation on a package with no version in force</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
@@ -25601,18 +25610,19 @@
       </c>
       <c r="J178" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-10 Package ending in 45 days</t>
+          <t>A packaged product whose only version is effective next month.
+Data: TD-PM-14 Masked quotation data</t>
         </is>
       </c>
       <c r="K178" s="12" t="inlineStr">
         <is>
-          <t>1. Quote PAR25.</t>
+          <t>1. Quote the product today.</t>
         </is>
       </c>
       <c r="L178" s="12" t="inlineStr">
         <is>
           <t>Refused.
-Message "Product PAR25 is EXPIRED and cannot be sold" (PRODUCT_NOT_SELLABLE).</t>
+Message "Package &lt;code&gt; has no released version in force on &lt;date&gt;" (PRODUCT_NOT_SELLABLE).</t>
         </is>
       </c>
       <c r="M178" s="12" t="inlineStr">
@@ -25620,11 +25630,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N178" s="12" t="inlineStr">
-        <is>
-          <t>CatalogVersionIT#packagesExpireAndRetireWithoutBeingDeleted</t>
-        </is>
-      </c>
+      <c r="N178" s="12" t="inlineStr"/>
       <c r="O178" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -25638,7 +25644,7 @@
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-052.2-01</t>
+          <t>TC-PM-051.1-02</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
@@ -25648,17 +25654,17 @@
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-052</t>
+          <t>FR-PM-051</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>BRPM.006</t>
+          <t>BRPM.007</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>Expired package history stays retrievable</t>
+          <t>Renewal and endorsement keep the version of the original account</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
@@ -25668,32 +25674,32 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Products</t>
+          <t>Product Maintenance &gt; Premium Calculator</t>
         </is>
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-11</t>
+          <t>SCR-PM-21</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-14 Masked quotation data</t>
         </is>
       </c>
       <c r="K179" s="12" t="inlineStr">
         <is>
-          <t>1. As auditor open PAR25 from the Expired filter; open its versions and a past request.</t>
+          <t>1. In the Premium Calculator choose purpose Renewal for an account sold on MTR10 version 1.</t>
         </is>
       </c>
       <c r="L179" s="12" t="inlineStr">
         <is>
-          <t>All versions, terms, documents and the request history open read only.</t>
+          <t>The premium uses version 1, not the version in force.</t>
         </is>
       </c>
       <c r="M179" s="12" t="inlineStr">
@@ -25701,7 +25707,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N179" s="12" t="inlineStr"/>
+      <c r="N179" s="12" t="inlineStr">
+        <is>
+          <t>RatingSchemeIT#renewalsAndEndorsementsUseTheirOwnVersion</t>
+        </is>
+      </c>
       <c r="O179" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -25715,7 +25725,7 @@
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-052.3-01</t>
+          <t>TC-PM-052.1-01</t>
         </is>
       </c>
       <c r="B180" s="12" t="inlineStr">
@@ -25735,39 +25745,40 @@
       </c>
       <c r="E180" s="12" t="inlineStr">
         <is>
-          <t>Marketing AO cannot list expired packages</t>
+          <t>Daily job expires a package whose end date passed</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>Security-access</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Administration &gt; Scheduled Jobs</t>
         </is>
       </c>
       <c r="I180" s="12" t="inlineStr"/>
       <c r="J180" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-10 Package ending in 45 days</t>
+          <t>In the test environment the end date of PAR25 is set to yesterday.
+Data: TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K180" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open Products (no Expired filter shown); call GET /api/v1/catalog/products?lifecycle=EXPIRED.</t>
+          <t>1. Run the job PACKAGE_VERSION_LIFECYCLE from Administration &gt; Scheduled Jobs.
+2. As mbs filter Products by Expired.</t>
         </is>
       </c>
       <c r="L180" s="12" t="inlineStr">
         <is>
-          <t>The filter is not offered; the call returns HTTP 403.
-Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
+          <t>PAR25 and its version are EXPIRED and tagged Expired; PKG_NEGOTIATE and PRODUCT_MAINTAIN holders are notified.</t>
         </is>
       </c>
       <c r="M180" s="12" t="inlineStr">
@@ -25777,7 +25788,7 @@
       </c>
       <c r="N180" s="12" t="inlineStr">
         <is>
-          <t>CatalogProductMaintenanceApiIT#permissionsFollowTheActionMatrix</t>
+          <t>CatalogVersionIT#packagesExpireAndRetireWithoutBeingDeleted</t>
         </is>
       </c>
       <c r="O180" s="27" t="inlineStr">
@@ -25793,47 +25804,47 @@
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-060.1-01</t>
+          <t>TC-PM-052.1-02</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>SC-PM-07</t>
+          <t>SC-PM-06</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-060</t>
+          <t>FR-PM-052</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>BRPM.017</t>
+          <t>BRPM.006</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>PAR25 in the Expiring tab</t>
+          <t>Quotation on an expired package</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Package Expiry</t>
+          <t>Quotation / Proposal &gt; New Quotation</t>
         </is>
       </c>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-10</t>
+          <t>SCR-PM-22</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
@@ -25843,12 +25854,13 @@
       </c>
       <c r="K181" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu open Package Expiry; Packages ending within (days) 60.</t>
+          <t>1. Quote PAR25.</t>
         </is>
       </c>
       <c r="L181" s="12" t="inlineStr">
         <is>
-          <t>PAR25 is listed with days left 45, its end date, anniversary and Renewal request None.</t>
+          <t>Refused.
+Message "Product PAR25 is EXPIRED and cannot be sold" (PRODUCT_NOT_SELLABLE).</t>
         </is>
       </c>
       <c r="M181" s="12" t="inlineStr">
@@ -25858,7 +25870,7 @@
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
-          <t>packageRequest.test.ts#splits the expiry list and colours the urgency; PackageLogicTest#theExpiryBucketAndTheNextTermFollowTheParameters</t>
+          <t>CatalogVersionIT#packagesExpireAndRetireWithoutBeingDeleted</t>
         </is>
       </c>
       <c r="O181" s="27" t="inlineStr">
@@ -25874,47 +25886,47 @@
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-060.1-02</t>
+          <t>TC-PM-052.2-01</t>
         </is>
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t>SC-PM-07</t>
+          <t>SC-PM-06</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-060</t>
+          <t>FR-PM-052</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>BRPM.017</t>
+          <t>BRPM.006</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr">
         <is>
-          <t>Days filter at 44 and 45</t>
+          <t>Expired package history stays retrievable</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Package Expiry</t>
+          <t>Product Maintenance &gt; Products</t>
         </is>
       </c>
       <c r="I182" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-10</t>
+          <t>SCR-PM-11</t>
         </is>
       </c>
       <c r="J182" s="12" t="inlineStr">
@@ -25924,12 +25936,12 @@
       </c>
       <c r="K182" s="12" t="inlineStr">
         <is>
-          <t>1. Set Packages ending within 44; then 45.</t>
+          <t>1. As auditor open PAR25 from the Expired filter; open its versions and a past request.</t>
         </is>
       </c>
       <c r="L182" s="12" t="inlineStr">
         <is>
-          <t>With 44 PAR25 is not listed; with 45 it is.</t>
+          <t>All versions, terms, documents and the request history open read only.</t>
         </is>
       </c>
       <c r="M182" s="12" t="inlineStr">
@@ -25951,60 +25963,59 @@
     <row r="183">
       <c r="A183" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-060.2-01</t>
+          <t>TC-PM-052.3-01</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>SC-PM-07</t>
+          <t>SC-PM-06</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-060</t>
+          <t>FR-PM-052</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>BRPM.017</t>
+          <t>BRPM.006</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr">
         <is>
-          <t>Expiry alert raised once per threshold</t>
+          <t>Marketing AO cannot list expired packages</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Security-access</t>
         </is>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; Scheduled Jobs</t>
+          <t>API call with the user's token (tester tool, for example Postman)</t>
         </is>
       </c>
       <c r="I183" s="12" t="inlineStr"/>
       <c r="J183" s="12" t="inlineStr">
         <is>
-          <t>PACKAGE_EXPIRY_NOTICE_DAYS 60, PACKAGE_EXPIRY_REMINDER_DAYS 30,7.
-Data: TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K183" s="12" t="inlineStr">
         <is>
-          <t>1. Run PACKAGE_EXPIRY_MONITOR twice on the same day.
-2. As tsu and mbs open the notification bell.</t>
+          <t>1. As ao open Products (no Expired filter shown); call GET /api/v1/catalog/products?lifecycle=EXPIRED.</t>
         </is>
       </c>
       <c r="L183" s="12" t="inlineStr">
         <is>
-          <t>One PACKAGE_EXPIRING alert for PAR25 at the 60-day threshold; the second run raises nothing new.</t>
+          <t>The filter is not offered; the call returns HTTP 403.
+Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
         </is>
       </c>
       <c r="M183" s="12" t="inlineStr">
@@ -26014,7 +26025,7 @@
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
-          <t>PackageExpiryIT#theMonitorAlertsAndDraftsOneRenewalRequestPrefilledFromTheVersion</t>
+          <t>CatalogProductMaintenanceApiIT#permissionsFollowTheActionMatrix</t>
         </is>
       </c>
       <c r="O183" s="27" t="inlineStr">
@@ -26030,7 +26041,7 @@
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-060.3-01</t>
+          <t>TC-PM-060.1-01</t>
         </is>
       </c>
       <c r="B184" s="12" t="inlineStr">
@@ -26050,12 +26061,12 @@
       </c>
       <c r="E184" s="12" t="inlineStr">
         <is>
-          <t>Generate Expiry List for a date range</t>
+          <t>PAR25 in the Expiring tab</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>Report-output</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G184" s="12" t="inlineStr">
@@ -26080,12 +26091,12 @@
       </c>
       <c r="K184" s="12" t="inlineStr">
         <is>
-          <t>1. Click Generate Expiry List; from today to today + 90 days; generate.</t>
+          <t>1. As tsu open Package Expiry; Packages ending within (days) 60.</t>
         </is>
       </c>
       <c r="L184" s="12" t="inlineStr">
         <is>
-          <t>The file lists the released packages ending in the range with product, version, end date, days left and renewal request.</t>
+          <t>PAR25 is listed with days left 45, its end date, anniversary and Renewal request None.</t>
         </is>
       </c>
       <c r="M184" s="12" t="inlineStr">
@@ -26093,7 +26104,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N184" s="12" t="inlineStr"/>
+      <c r="N184" s="12" t="inlineStr">
+        <is>
+          <t>packageRequest.test.ts#splits the expiry list and colours the urgency; PackageLogicTest#theExpiryBucketAndTheNextTermFollowTheParameters</t>
+        </is>
+      </c>
       <c r="O184" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26107,7 +26122,7 @@
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-060.3-02</t>
+          <t>TC-PM-060.1-02</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
@@ -26127,7 +26142,7 @@
       </c>
       <c r="E185" s="12" t="inlineStr">
         <is>
-          <t>Days filter outside 1-365</t>
+          <t>Days filter at 44 and 45</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
@@ -26157,12 +26172,12 @@
       </c>
       <c r="K185" s="12" t="inlineStr">
         <is>
-          <t>1. Enter 0; then 366.</t>
+          <t>1. Set Packages ending within 44; then 45.</t>
         </is>
       </c>
       <c r="L185" s="12" t="inlineStr">
         <is>
-          <t>Both values are refused on the field; 1 and 365 are accepted.</t>
+          <t>With 44 PAR25 is not listed; with 45 it is.</t>
         </is>
       </c>
       <c r="M185" s="12" t="inlineStr">
@@ -26184,7 +26199,7 @@
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-060.1-03</t>
+          <t>TC-PM-060.2-01</t>
         </is>
       </c>
       <c r="B186" s="12" t="inlineStr">
@@ -26204,39 +26219,40 @@
       </c>
       <c r="E186" s="12" t="inlineStr">
         <is>
-          <t>Marketing AO cannot open Package Expiry</t>
+          <t>Expiry alert raised once per threshold</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>Security-access</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Administration &gt; Scheduled Jobs</t>
         </is>
       </c>
       <c r="I186" s="12" t="inlineStr"/>
       <c r="J186" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-10 Package ending in 45 days</t>
+          <t>PACKAGE_EXPIRY_NOTICE_DAYS 60, PACKAGE_EXPIRY_REMINDER_DAYS 30,7.
+Data: TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K186" s="12" t="inlineStr">
         <is>
-          <t>1. As ao call GET /api/v1/product-maintenance/expiry.</t>
+          <t>1. Run PACKAGE_EXPIRY_MONITOR twice on the same day.
+2. As tsu and mbs open the notification bell.</t>
         </is>
       </c>
       <c r="L186" s="12" t="inlineStr">
         <is>
-          <t>HTTP 403; the screen is not in ao's menu.
-Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
+          <t>One PACKAGE_EXPIRING alert for PAR25 at the 60-day threshold; the second run raises nothing new.</t>
         </is>
       </c>
       <c r="M186" s="12" t="inlineStr">
@@ -26246,7 +26262,7 @@
       </c>
       <c r="N186" s="12" t="inlineStr">
         <is>
-          <t>ProductMaintenanceApiIT#permissionsAreEnforced</t>
+          <t>PackageExpiryIT#theMonitorAlertsAndDraftsOneRenewalRequestPrefilledFromTheVersion</t>
         </is>
       </c>
       <c r="O186" s="27" t="inlineStr">
@@ -26262,7 +26278,7 @@
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-061.1-01</t>
+          <t>TC-PM-060.3-01</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
@@ -26272,7 +26288,7 @@
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-061</t>
+          <t>FR-PM-060</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
@@ -26282,12 +26298,12 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>Generate a renewal request for PAR25</t>
+          <t>Generate Expiry List for a date range</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Report-output</t>
         </is>
       </c>
       <c r="G187" s="12" t="inlineStr">
@@ -26312,13 +26328,12 @@
       </c>
       <c r="K187" s="12" t="inlineStr">
         <is>
-          <t>1. Tick PAR25; click Generate Renewal Request.
-2. Open the new request.</t>
+          <t>1. Click Generate Expiry List; from today to today + 90 days; generate.</t>
         </is>
       </c>
       <c r="L187" s="12" t="inlineStr">
         <is>
-          <t>A RENEW request in DRAFT is created and its number shown; terms equal PAR25 version 1; package start = old end + 1 day with the same term length.</t>
+          <t>The file lists the released packages ending in the range with product, version, end date, days left and renewal request.</t>
         </is>
       </c>
       <c r="M187" s="12" t="inlineStr">
@@ -26326,11 +26341,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N187" s="12" t="inlineStr">
-        <is>
-          <t>PackageExpiryIT#theMonitorAlertsAndDraftsOneRenewalRequestPrefilledFromTheVersion</t>
-        </is>
-      </c>
+      <c r="N187" s="12" t="inlineStr"/>
       <c r="O187" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26344,7 +26355,7 @@
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-061.2-01</t>
+          <t>TC-PM-060.3-02</t>
         </is>
       </c>
       <c r="B188" s="12" t="inlineStr">
@@ -26354,7 +26365,7 @@
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-061</t>
+          <t>FR-PM-060</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
@@ -26364,12 +26375,12 @@
       </c>
       <c r="E188" s="12" t="inlineStr">
         <is>
-          <t>Second renewal request for the same package</t>
+          <t>Days filter outside 1-365</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="G188" s="12" t="inlineStr">
@@ -26394,12 +26405,12 @@
       </c>
       <c r="K188" s="12" t="inlineStr">
         <is>
-          <t>1. Tick PAR25 again (now in Renewal in Progress); click Generate Renewal Request.</t>
+          <t>1. Enter 0; then 366.</t>
         </is>
       </c>
       <c r="L188" s="12" t="inlineStr">
         <is>
-          <t>No second request is created; PAR25 shows the open request and its stage.</t>
+          <t>Both values are refused on the field; 1 and 365 are accepted.</t>
         </is>
       </c>
       <c r="M188" s="12" t="inlineStr">
@@ -26407,11 +26418,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N188" s="12" t="inlineStr">
-        <is>
-          <t>PackageExpiryIT#theMonitorAlertsAndDraftsOneRenewalRequestPrefilledFromTheVersion</t>
-        </is>
-      </c>
+      <c r="N188" s="12" t="inlineStr"/>
       <c r="O188" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26425,7 +26432,7 @@
     <row r="189">
       <c r="A189" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-061.3-01</t>
+          <t>TC-PM-060.1-03</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
@@ -26435,7 +26442,7 @@
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-061</t>
+          <t>FR-PM-060</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
@@ -26445,29 +26452,25 @@
       </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>Generate with no package selected</t>
+          <t>Marketing AO cannot open Package Expiry</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security-access</t>
         </is>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Package Expiry</t>
-        </is>
-      </c>
-      <c r="I189" s="12" t="inlineStr">
-        <is>
-          <t>SCR-PM-10</t>
-        </is>
-      </c>
+          <t>API call with the user's token (tester tool, for example Postman)</t>
+        </is>
+      </c>
+      <c r="I189" s="12" t="inlineStr"/>
       <c r="J189" s="12" t="inlineStr">
         <is>
           <t>Data: TD-PM-10 Package ending in 45 days</t>
@@ -26475,13 +26478,13 @@
       </c>
       <c r="K189" s="12" t="inlineStr">
         <is>
-          <t>1. Untick all; click Generate Renewal Request (API call with an empty list).</t>
+          <t>1. As ao call GET /api/v1/product-maintenance/expiry.</t>
         </is>
       </c>
       <c r="L189" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "Select the packages to renew" (PKG_RENEWAL_NONE).</t>
+          <t>HTTP 403; the screen is not in ao's menu.
+Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
         </is>
       </c>
       <c r="M189" s="12" t="inlineStr">
@@ -26489,7 +26492,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N189" s="12" t="inlineStr"/>
+      <c r="N189" s="12" t="inlineStr">
+        <is>
+          <t>ProductMaintenanceApiIT#permissionsAreEnforced</t>
+        </is>
+      </c>
       <c r="O189" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26503,7 +26510,7 @@
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-061.1-02</t>
+          <t>TC-PM-061.1-01</t>
         </is>
       </c>
       <c r="B190" s="12" t="inlineStr">
@@ -26523,25 +26530,29 @@
       </c>
       <c r="E190" s="12" t="inlineStr">
         <is>
-          <t>Automatic drafting when PACKAGE_RENEWAL_AUTODRAFT is on</t>
+          <t>Generate a renewal request for PAR25</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; System Parameters</t>
-        </is>
-      </c>
-      <c r="I190" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Package Expiry</t>
+        </is>
+      </c>
+      <c r="I190" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-10</t>
+        </is>
+      </c>
       <c r="J190" s="12" t="inlineStr">
         <is>
           <t>Data: TD-PM-10 Package ending in 45 days</t>
@@ -26549,12 +26560,13 @@
       </c>
       <c r="K190" s="12" t="inlineStr">
         <is>
-          <t>1. Set PACKAGE_RENEWAL_AUTODRAFT true; run PACKAGE_EXPIRY_MONITOR.</t>
+          <t>1. Tick PAR25; click Generate Renewal Request.
+2. Open the new request.</t>
         </is>
       </c>
       <c r="L190" s="12" t="inlineStr">
         <is>
-          <t>One RENEW request is drafted for each package at the notice period that has none.</t>
+          <t>A RENEW request in DRAFT is created and its number shown; terms equal PAR25 version 1; package start = old end + 1 day with the same term length.</t>
         </is>
       </c>
       <c r="M190" s="12" t="inlineStr">
@@ -26580,7 +26592,7 @@
     <row r="191">
       <c r="A191" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-070.1-01</t>
+          <t>TC-PM-061.2-01</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
@@ -26590,52 +26602,52 @@
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-070</t>
+          <t>FR-PM-061</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>BRPM.019</t>
+          <t>BRPM.017</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr">
         <is>
-          <t>Red tile for a request past its SLA</t>
+          <t>Second renewal request for the same package</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Product Maintenance Home</t>
+          <t>Product Maintenance &gt; Package Expiry</t>
         </is>
       </c>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-01</t>
+          <t>SCR-PM-10</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K191" s="12" t="inlineStr">
         <is>
-          <t>1. Open Product Maintenance Home.</t>
+          <t>1. Tick PAR25 again (now in Renewal in Progress); click Generate Renewal Request.</t>
         </is>
       </c>
       <c r="L191" s="12" t="inlineStr">
         <is>
-          <t>PKR-2026-900002 (FOR_TSU_REVIEW since 21-Sep, SLA 24 hours) is counted in a red tile.</t>
+          <t>No second request is created; PAR25 shows the open request and its stage.</t>
         </is>
       </c>
       <c r="M191" s="12" t="inlineStr">
@@ -26645,7 +26657,7 @@
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
-          <t>packageRequest.test.ts#builds the home tiles with SLA counts</t>
+          <t>PackageExpiryIT#theMonitorAlertsAndDraftsOneRenewalRequestPrefilledFromTheVersion</t>
         </is>
       </c>
       <c r="O191" s="27" t="inlineStr">
@@ -26661,7 +26673,7 @@
     <row r="192">
       <c r="A192" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-070.1-02</t>
+          <t>TC-PM-061.3-01</t>
         </is>
       </c>
       <c r="B192" s="12" t="inlineStr">
@@ -26671,53 +26683,53 @@
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-070</t>
+          <t>FR-PM-061</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>BRPM.019</t>
+          <t>BRPM.017</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
         <is>
-          <t>Amber at 80 % of the SLA</t>
+          <t>Generate with no package selected</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Product Maintenance Home</t>
+          <t>Product Maintenance &gt; Package Expiry</t>
         </is>
       </c>
       <c r="I192" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-01</t>
+          <t>SCR-PM-10</t>
         </is>
       </c>
       <c r="J192" s="12" t="inlineStr">
         <is>
-          <t>A request enters FOR_MKT_APPROVAL (SLA 24 hours); the test waits 19 hours 12 minutes, or the stage entry time is moved in the test database.
-Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K192" s="12" t="inlineStr">
         <is>
-          <t>1. Open the home page after 80 % of the SLA and again before 100 %.</t>
+          <t>1. Untick all; click Generate Renewal Request (API call with an empty list).</t>
         </is>
       </c>
       <c r="L192" s="12" t="inlineStr">
         <is>
-          <t>The request is counted amber at 80 % and red after 24 hours.</t>
+          <t>Refused.
+Message "Select the packages to renew" (PKG_RENEWAL_NONE).</t>
         </is>
       </c>
       <c r="M192" s="12" t="inlineStr">
@@ -26725,11 +26737,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N192" s="12" t="inlineStr">
-        <is>
-          <t>packageRequest.test.ts#classifies SLA and stage age</t>
-        </is>
-      </c>
+      <c r="N192" s="12" t="inlineStr"/>
       <c r="O192" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26743,7 +26751,7 @@
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-070.2-01</t>
+          <t>TC-PM-061.1-02</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
@@ -26753,52 +26761,48 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-070</t>
+          <t>FR-PM-061</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>BRPM.019</t>
+          <t>BRPM.017</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>Expiring in 30 days tile opens the filtered list</t>
+          <t>Automatic drafting when PACKAGE_RENEWAL_AUTODRAFT is on</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>Report-output</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Product Maintenance Home</t>
-        </is>
-      </c>
-      <c r="I193" s="12" t="inlineStr">
-        <is>
-          <t>SCR-PM-01</t>
-        </is>
-      </c>
+          <t>Administration &gt; System Parameters</t>
+        </is>
+      </c>
+      <c r="I193" s="12" t="inlineStr"/>
       <c r="J193" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K193" s="12" t="inlineStr">
         <is>
-          <t>1. Click the tile Expiring in 60 days; export the list.</t>
+          <t>1. Set PACKAGE_RENEWAL_AUTODRAFT true; run PACKAGE_EXPIRY_MONITOR.</t>
         </is>
       </c>
       <c r="L193" s="12" t="inlineStr">
         <is>
-          <t>Package Expiry opens filtered to 60 days with PAR25; the export is an Excel file with the same rows.</t>
+          <t>One RENEW request is drafted for each package at the notice period that has none.</t>
         </is>
       </c>
       <c r="M193" s="12" t="inlineStr">
@@ -26806,7 +26810,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N193" s="12" t="inlineStr"/>
+      <c r="N193" s="12" t="inlineStr">
+        <is>
+          <t>PackageExpiryIT#theMonitorAlertsAndDraftsOneRenewalRequestPrefilledFromTheVersion</t>
+        </is>
+      </c>
       <c r="O193" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26820,7 +26828,7 @@
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-070.3-01</t>
+          <t>TC-PM-070.1-01</t>
         </is>
       </c>
       <c r="B194" s="12" t="inlineStr">
@@ -26840,17 +26848,17 @@
       </c>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>Counts follow the user's access</t>
+          <t>Red tile for a request past its SLA</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>Security-access</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -26870,12 +26878,12 @@
       </c>
       <c r="K194" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao and open Product Maintenance Home.</t>
+          <t>1. Open Product Maintenance Home.</t>
         </is>
       </c>
       <c r="L194" s="12" t="inlineStr">
         <is>
-          <t>The tiles show only the stages ao can see; no Versions for validation tile.</t>
+          <t>PKR-2026-900002 (FOR_TSU_REVIEW since 21-Sep, SLA 24 hours) is counted in a red tile.</t>
         </is>
       </c>
       <c r="M194" s="12" t="inlineStr">
@@ -26885,7 +26893,7 @@
       </c>
       <c r="N194" s="12" t="inlineStr">
         <is>
-          <t>ProductMaintenanceApiIT#listEndpointsRespondOk</t>
+          <t>packageRequest.test.ts#builds the home tiles with SLA counts</t>
         </is>
       </c>
       <c r="O194" s="27" t="inlineStr">
@@ -26901,7 +26909,7 @@
     <row r="195">
       <c r="A195" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-070.3-02</t>
+          <t>TC-PM-070.1-02</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
@@ -26921,12 +26929,12 @@
       </c>
       <c r="E195" s="12" t="inlineStr">
         <is>
-          <t>A user without view permission cannot read the counts</t>
+          <t>Amber at 80 % of the SLA</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>Security-access</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="G195" s="12" t="inlineStr">
@@ -26936,24 +26944,28 @@
       </c>
       <c r="H195" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
-        </is>
-      </c>
-      <c r="I195" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Product Maintenance Home</t>
+        </is>
+      </c>
+      <c r="I195" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-01</t>
+        </is>
+      </c>
       <c r="J195" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
+          <t>A request enters FOR_MKT_APPROVAL (SLA 24 hours); the test waits 19 hours 12 minutes, or the stage entry time is moved in the test database.
+Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K195" s="12" t="inlineStr">
         <is>
-          <t>1. Call GET /api/v1/product-maintenance/counts with the token of a user without PRODUCT_VIEW and PKG_REPORT_VIEW.</t>
+          <t>1. Open the home page after 80 % of the SLA and again before 100 %.</t>
         </is>
       </c>
       <c r="L195" s="12" t="inlineStr">
         <is>
-          <t>HTTP 403.
-Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
+          <t>The request is counted amber at 80 % and red after 24 hours.</t>
         </is>
       </c>
       <c r="M195" s="12" t="inlineStr">
@@ -26961,7 +26973,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N195" s="12" t="inlineStr"/>
+      <c r="N195" s="12" t="inlineStr">
+        <is>
+          <t>packageRequest.test.ts#classifies SLA and stage age</t>
+        </is>
+      </c>
       <c r="O195" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -26975,7 +26991,7 @@
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.1-01</t>
+          <t>TC-PM-070.2-01</t>
         </is>
       </c>
       <c r="B196" s="12" t="inlineStr">
@@ -26985,17 +27001,17 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-071</t>
+          <t>FR-PM-070</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>BRPM.018, BRPM.017, BRPM.006</t>
+          <t>BRPM.019</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>Package Status Update Report for PKR-2026-900006</t>
+          <t>Expiring in 30 days tile opens the filtered list</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
@@ -27010,23 +27026,27 @@
       </c>
       <c r="H196" s="12" t="inlineStr">
         <is>
-          <t>Reports &gt; Report Centre (category New Business)</t>
-        </is>
-      </c>
-      <c r="I196" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Product Maintenance Home</t>
+        </is>
+      </c>
+      <c r="I196" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-01</t>
+        </is>
+      </c>
       <c r="J196" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-07 Released AMEND request; TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K196" s="12" t="inlineStr">
         <is>
-          <t>1. Run PM-PKG-STATUS with Request No. pkr-2026-900006.</t>
+          <t>1. Click the tile Expiring in 60 days; export the list.</t>
         </is>
       </c>
       <c r="L196" s="12" t="inlineStr">
         <is>
-          <t>One row for PKR-2026-900006 with type AMEND, stage RELEASED, version 2, rate, insurers and the last action; the parameters print in the header.</t>
+          <t>Package Expiry opens filtered to 60 days with PAR25; the export is an Excel file with the same rows.</t>
         </is>
       </c>
       <c r="M196" s="12" t="inlineStr">
@@ -27034,11 +27054,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N196" s="12" t="inlineStr">
-        <is>
-          <t>ProductMaintenanceApiIT#theProductMaintenanceReportsRunAndExportInEveryFormat</t>
-        </is>
-      </c>
+      <c r="N196" s="12" t="inlineStr"/>
       <c r="O196" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27052,7 +27068,7 @@
     <row r="197">
       <c r="A197" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.2-01</t>
+          <t>TC-PM-070.3-01</t>
         </is>
       </c>
       <c r="B197" s="12" t="inlineStr">
@@ -27062,48 +27078,52 @@
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-071</t>
+          <t>FR-PM-070</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>BRPM.018, BRPM.017, BRPM.006</t>
+          <t>BRPM.019</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>Export the three reports in every format</t>
+          <t>Counts follow the user's access</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>Report-output</t>
+          <t>Security-access</t>
         </is>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
         <is>
-          <t>Reports &gt; Report Centre (category New Business)</t>
-        </is>
-      </c>
-      <c r="I197" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Product Maintenance Home</t>
+        </is>
+      </c>
+      <c r="I197" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-01</t>
+        </is>
+      </c>
       <c r="J197" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-07 Released AMEND request; TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K197" s="12" t="inlineStr">
         <is>
-          <t>1. Run PM-PKG-STATUS (all), PM-PKG-EXPIRY (within 400 days) and PM-VERSION-HISTORY (all); export each to PDF, XLSX, ODS and CSV.</t>
+          <t>1. Log in as ao and open Product Maintenance Home.</t>
         </is>
       </c>
       <c r="L197" s="12" t="inlineStr">
         <is>
-          <t>Each export opens and holds the same rows as the screen.</t>
+          <t>The tiles show only the stages ao can see; no Versions for validation tile.</t>
         </is>
       </c>
       <c r="M197" s="12" t="inlineStr">
@@ -27113,7 +27133,7 @@
       </c>
       <c r="N197" s="12" t="inlineStr">
         <is>
-          <t>ProductMaintenanceApiIT#theProductMaintenanceReportsRunAndExportInEveryFormat</t>
+          <t>ProductMaintenanceApiIT#listEndpointsRespondOk</t>
         </is>
       </c>
       <c r="O197" s="27" t="inlineStr">
@@ -27129,7 +27149,7 @@
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.2-02</t>
+          <t>TC-PM-070.3-02</t>
         </is>
       </c>
       <c r="B198" s="12" t="inlineStr">
@@ -27139,22 +27159,22 @@
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-071</t>
+          <t>FR-PM-070</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>BRPM.018, BRPM.017, BRPM.006</t>
+          <t>BRPM.019</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
         <is>
-          <t>Save a variant of the expiry report</t>
+          <t>A user without view permission cannot read the counts</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Security-access</t>
         </is>
       </c>
       <c r="G198" s="12" t="inlineStr">
@@ -27164,23 +27184,24 @@
       </c>
       <c r="H198" s="12" t="inlineStr">
         <is>
-          <t>Reports &gt; Report Centre (category New Business)</t>
+          <t>API call with the user's token (tester tool, for example Postman)</t>
         </is>
       </c>
       <c r="I198" s="12" t="inlineStr"/>
       <c r="J198" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-07 Released AMEND request; TD-PM-10 Package ending in 45 days</t>
+          <t>Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K198" s="12" t="inlineStr">
         <is>
-          <t>1. Set Ending Within 90; Save as variant "Next quarter"; reopen the report and load the variant.</t>
+          <t>1. Call GET /api/v1/product-maintenance/counts with the token of a user without PRODUCT_VIEW and PKG_REPORT_VIEW.</t>
         </is>
       </c>
       <c r="L198" s="12" t="inlineStr">
         <is>
-          <t>The variant restores the parameter; the run is logged with user, parameters and time.</t>
+          <t>HTTP 403.
+Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
         </is>
       </c>
       <c r="M198" s="12" t="inlineStr">
@@ -27188,11 +27209,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N198" s="12" t="inlineStr">
-        <is>
-          <t>NbReportApiIT#aVariantIsSavedListedAndDeleted</t>
-        </is>
-      </c>
+      <c r="N198" s="12" t="inlineStr"/>
       <c r="O198" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27206,7 +27223,7 @@
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.3-01</t>
+          <t>TC-PM-071.1-01</t>
         </is>
       </c>
       <c r="B199" s="12" t="inlineStr">
@@ -27226,17 +27243,17 @@
       </c>
       <c r="E199" s="12" t="inlineStr">
         <is>
-          <t>Marketing AO cannot run the package reports</t>
+          <t>Package Status Update Report for PKR-2026-900006</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>Security-access</t>
+          <t>Report-output</t>
         </is>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -27252,13 +27269,12 @@
       </c>
       <c r="K199" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open Reports; look for the three reports; call the run endpoint of PM-PKG-STATUS.</t>
+          <t>1. Run PM-PKG-STATUS with Request No. pkr-2026-900006.</t>
         </is>
       </c>
       <c r="L199" s="12" t="inlineStr">
         <is>
-          <t>The reports are not listed; the call returns HTTP 403.
-Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
+          <t>One row for PKR-2026-900006 with type AMEND, stage RELEASED, version 2, rate, insurers and the last action; the parameters print in the header.</t>
         </is>
       </c>
       <c r="M199" s="12" t="inlineStr">
@@ -27266,7 +27282,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N199" s="12" t="inlineStr"/>
+      <c r="N199" s="12" t="inlineStr">
+        <is>
+          <t>ProductMaintenanceApiIT#theProductMaintenanceReportsRunAndExportInEveryFormat</t>
+        </is>
+      </c>
       <c r="O199" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27280,7 +27300,7 @@
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-071.3-02</t>
+          <t>TC-PM-071.2-01</t>
         </is>
       </c>
       <c r="B200" s="12" t="inlineStr">
@@ -27300,12 +27320,12 @@
       </c>
       <c r="E200" s="12" t="inlineStr">
         <is>
-          <t>Days parameter not a whole number</t>
+          <t>Export the three reports in every format</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Report-output</t>
         </is>
       </c>
       <c r="G200" s="12" t="inlineStr">
@@ -27326,13 +27346,12 @@
       </c>
       <c r="K200" s="12" t="inlineStr">
         <is>
-          <t>1. Run PM-PKG-EXPIRY with Ending Within "abc".</t>
+          <t>1. Run PM-PKG-STATUS (all), PM-PKG-EXPIRY (within 400 days) and PM-VERSION-HISTORY (all); export each to PDF, XLSX, ODS and CSV.</t>
         </is>
       </c>
       <c r="L200" s="12" t="inlineStr">
         <is>
-          <t>The run does not start.
-Message "Ending Within (days) has an invalid value 'abc'" (INVALID_REPORT_PARAMETERS).</t>
+          <t>Each export opens and holds the same rows as the screen.</t>
         </is>
       </c>
       <c r="M200" s="12" t="inlineStr">
@@ -27342,7 +27361,7 @@
       </c>
       <c r="N200" s="12" t="inlineStr">
         <is>
-          <t>ReportParametersTest</t>
+          <t>ProductMaintenanceApiIT#theProductMaintenanceReportsRunAndExportInEveryFormat</t>
         </is>
       </c>
       <c r="O200" s="27" t="inlineStr">
@@ -27358,7 +27377,7 @@
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-072.1-01</t>
+          <t>TC-PM-071.2-02</t>
         </is>
       </c>
       <c r="B201" s="12" t="inlineStr">
@@ -27368,17 +27387,17 @@
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-072</t>
+          <t>FR-PM-071</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>BRPM.022</t>
+          <t>BRPM.018, BRPM.017, BRPM.006</t>
         </is>
       </c>
       <c r="E201" s="12" t="inlineStr">
         <is>
-          <t>Notification on entry to FOR_TSU_REVIEW</t>
+          <t>Save a variant of the expiry report</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
@@ -27388,28 +27407,28 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
         <is>
-          <t>Notifications (bell icon in the page header)</t>
+          <t>Reports &gt; Report Centre (category New Business)</t>
         </is>
       </c>
       <c r="I201" s="12" t="inlineStr"/>
       <c r="J201" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-12 New CGL request keyed in the test</t>
+          <t>Data: TD-PM-07 Released AMEND request; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K201" s="12" t="inlineStr">
         <is>
-          <t>1. As mkttl approve a submitted request; as tsulead open the bell.</t>
+          <t>1. Set Ending Within 90; Save as variant "Next quarter"; reopen the report and load the variant.</t>
         </is>
       </c>
       <c r="L201" s="12" t="inlineStr">
         <is>
-          <t>One notification for the request; clicking it opens the request.</t>
+          <t>The variant restores the parameter; the run is logged with user, parameters and time.</t>
         </is>
       </c>
       <c r="M201" s="12" t="inlineStr">
@@ -27419,7 +27438,7 @@
       </c>
       <c r="N201" s="12" t="inlineStr">
         <is>
-          <t>MessagingIT#notificationsArePerUserAndCanBeMarkedRead</t>
+          <t>NbReportApiIT#aVariantIsSavedListedAndDeleted</t>
         </is>
       </c>
       <c r="O201" s="27" t="inlineStr">
@@ -27435,7 +27454,7 @@
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-072.1-02</t>
+          <t>TC-PM-071.3-01</t>
         </is>
       </c>
       <c r="B202" s="12" t="inlineStr">
@@ -27445,48 +27464,49 @@
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-072</t>
+          <t>FR-PM-071</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>BRPM.022</t>
+          <t>BRPM.018, BRPM.017, BRPM.006</t>
         </is>
       </c>
       <c r="E202" s="12" t="inlineStr">
         <is>
-          <t>E-mail copy when the preference is set</t>
+          <t>Marketing AO cannot run the package reports</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Security-access</t>
         </is>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
         <is>
-          <t>Broking Setup &gt; Outbound Messages</t>
+          <t>Reports &gt; Report Centre (category New Business)</t>
         </is>
       </c>
       <c r="I202" s="12" t="inlineStr"/>
       <c r="J202" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-12 New CGL request keyed in the test</t>
+          <t>Data: TD-PM-07 Released AMEND request; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K202" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu set the preference for stage entry to in-app and e-mail (Operations &gt; Notification Settings); trigger a stage entry for tsu.</t>
+          <t>1. As ao open Reports; look for the three reports; call the run endpoint of PM-PKG-STATUS.</t>
         </is>
       </c>
       <c r="L202" s="12" t="inlineStr">
         <is>
-          <t>tsu receives the in-app notification and an e-mail; with in-app only, no e-mail is sent.</t>
+          <t>The reports are not listed; the call returns HTTP 403.
+Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
         </is>
       </c>
       <c r="M202" s="12" t="inlineStr">
@@ -27494,11 +27514,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N202" s="12" t="inlineStr">
-        <is>
-          <t>OperationsFoundationApiIT#notificationPreferencesAreKeptPerUser</t>
-        </is>
-      </c>
+      <c r="N202" s="12" t="inlineStr"/>
       <c r="O202" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27512,7 +27528,7 @@
     <row r="203">
       <c r="A203" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-072.2-01</t>
+          <t>TC-PM-071.3-02</t>
         </is>
       </c>
       <c r="B203" s="12" t="inlineStr">
@@ -27522,48 +27538,49 @@
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-072</t>
+          <t>FR-PM-071</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>BRPM.022</t>
+          <t>BRPM.018, BRPM.017, BRPM.006</t>
         </is>
       </c>
       <c r="E203" s="12" t="inlineStr">
         <is>
-          <t>Release logged by the product master feed</t>
+          <t>Days parameter not a whole number</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
+          <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; Audit Trail</t>
+          <t>Reports &gt; Report Centre (category New Business)</t>
         </is>
       </c>
       <c r="I203" s="12" t="inlineStr"/>
       <c r="J203" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-12 New CGL request keyed in the test</t>
+          <t>Data: TD-PM-07 Released AMEND request; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
       <c r="K203" s="12" t="inlineStr">
         <is>
-          <t>1. Release a version (TC-PM-043.2-01); open the application log or Integration Events for the feed entry.</t>
+          <t>1. Run PM-PKG-EXPIRY with Ending Within "abc".</t>
         </is>
       </c>
       <c r="L203" s="12" t="inlineStr">
         <is>
-          <t>One entry with product, version and effective date; no external transport is called (PQ16).</t>
+          <t>The run does not start.
+Message "Ending Within (days) has an invalid value 'abc'" (INVALID_REPORT_PARAMETERS).</t>
         </is>
       </c>
       <c r="M203" s="12" t="inlineStr">
@@ -27571,7 +27588,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N203" s="12" t="inlineStr"/>
+      <c r="N203" s="12" t="inlineStr">
+        <is>
+          <t>ReportParametersTest</t>
+        </is>
+      </c>
       <c r="O203" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27585,7 +27606,7 @@
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-072.1-03</t>
+          <t>TC-PM-072.1-01</t>
         </is>
       </c>
       <c r="B204" s="12" t="inlineStr">
@@ -27605,17 +27626,17 @@
       </c>
       <c r="E204" s="12" t="inlineStr">
         <is>
-          <t>A user who is not a stage owner is not notified</t>
+          <t>Notification on entry to FOR_TSU_REVIEW</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+          <t>TSU_TL – TSU Team Lead (SIT/UAT user tsulead)</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -27631,12 +27652,12 @@
       </c>
       <c r="K204" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open the bell after the request of TC-PM-072.1-01 entered FOR_TSU_REVIEW.</t>
+          <t>1. As mkttl approve a submitted request; as tsulead open the bell.</t>
         </is>
       </c>
       <c r="L204" s="12" t="inlineStr">
         <is>
-          <t>ao, who is not an owner of FOR_TSU_REVIEW, has no notification for that stage entry.</t>
+          <t>One notification for the request; clicking it opens the request.</t>
         </is>
       </c>
       <c r="M204" s="12" t="inlineStr">
@@ -27646,7 +27667,7 @@
       </c>
       <c r="N204" s="12" t="inlineStr">
         <is>
-          <t>WorkflowServiceIT#queuesShowOnlyTheStagesOfTheUsersTeamAndSupportClaimAndAssignment</t>
+          <t>MessagingIT#notificationsArePerUserAndCanBeMarkedRead</t>
         </is>
       </c>
       <c r="O204" s="27" t="inlineStr">
@@ -27662,7 +27683,7 @@
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-073.1-01</t>
+          <t>TC-PM-072.1-02</t>
         </is>
       </c>
       <c r="B205" s="12" t="inlineStr">
@@ -27672,49 +27693,48 @@
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-073</t>
+          <t>FR-PM-072</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>BRPM.021</t>
+          <t>BRPM.022</t>
         </is>
       </c>
       <c r="E205" s="12" t="inlineStr">
         <is>
-          <t>MBS set-up without the ManCom sign-off through the API</t>
+          <t>E-mail copy when the preference is set</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Broking Setup &gt; Outbound Messages</t>
         </is>
       </c>
       <c r="I205" s="12" t="inlineStr"/>
       <c r="J205" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-05 UPDATE request at ManCom; TD-PM-02 Draft NEW generic request</t>
+          <t>Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="K205" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs call POST .../requests/{id}/setup on PKR-2026-900004 (FOR_MANCOM).</t>
+          <t>1. As tsu set the preference for stage entry to in-app and e-mail (Operations &gt; Notification Settings); trigger a stage entry for tsu.</t>
         </is>
       </c>
       <c r="L205" s="12" t="inlineStr">
         <is>
-          <t>Refused; the request stays in FOR_MANCOM.
-Message "MBS receives signed-off requirements only (BRPM.015)" (PKG_NOT_WITH_MBS).</t>
+          <t>tsu receives the in-app notification and an e-mail; with in-app only, no e-mail is sent.</t>
         </is>
       </c>
       <c r="M205" s="12" t="inlineStr">
@@ -27722,7 +27742,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N205" s="12" t="inlineStr"/>
+      <c r="N205" s="12" t="inlineStr">
+        <is>
+          <t>OperationsFoundationApiIT#notificationPreferencesAreKeptPerUser</t>
+        </is>
+      </c>
       <c r="O205" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27736,7 +27760,7 @@
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-073.1-02</t>
+          <t>TC-PM-072.2-01</t>
         </is>
       </c>
       <c r="B206" s="12" t="inlineStr">
@@ -27746,49 +27770,48 @@
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-073</t>
+          <t>FR-PM-072</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>BRPM.021</t>
+          <t>BRPM.022</t>
         </is>
       </c>
       <c r="E206" s="12" t="inlineStr">
         <is>
-          <t>A user without the stage permission cannot move the case</t>
+          <t>Release logged by the product master feed</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>Security-access</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Administration &gt; Audit Trail</t>
         </is>
       </c>
       <c r="I206" s="12" t="inlineStr"/>
       <c r="J206" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-05 UPDATE request at ManCom; TD-PM-02 Draft NEW generic request</t>
+          <t>Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="K206" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu call the workflow action approve on a request in FOR_MKT_APPROVAL.</t>
+          <t>1. Release a version (TC-PM-043.2-01); open the application log or Integration Events for the feed entry.</t>
         </is>
       </c>
       <c r="L206" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "You are not allowed to 'Approve and send to TSU'" (WORKFLOW_ACTION_NOT_PERMITTED).</t>
+          <t>One entry with product, version and effective date; no external transport is called (PQ16).</t>
         </is>
       </c>
       <c r="M206" s="12" t="inlineStr">
@@ -27796,11 +27819,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N206" s="12" t="inlineStr">
-        <is>
-          <t>ProductMaintenanceFoundationIT#requestCaseMovesThroughTheApprovalChain</t>
-        </is>
-      </c>
+      <c r="N206" s="12" t="inlineStr"/>
       <c r="O206" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27814,7 +27833,7 @@
     <row r="207">
       <c r="A207" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-073.2-01</t>
+          <t>TC-PM-072.1-03</t>
         </is>
       </c>
       <c r="B207" s="12" t="inlineStr">
@@ -27824,27 +27843,27 @@
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-073</t>
+          <t>FR-PM-072</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>BRPM.021</t>
+          <t>BRPM.022</t>
         </is>
       </c>
       <c r="E207" s="12" t="inlineStr">
         <is>
-          <t>SLA alert to the stage owners</t>
+          <t>A user who is not a stage owner is not notified</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -27855,17 +27874,17 @@
       <c r="I207" s="12" t="inlineStr"/>
       <c r="J207" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-05 UPDATE request at ManCom; TD-PM-02 Draft NEW generic request</t>
+          <t>Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="K207" s="12" t="inlineStr">
         <is>
-          <t>1. Leave PKR-2026-900002 in FOR_TSU_REVIEW beyond 24 hours; let the SLA check run; as tsulead open the bell.</t>
+          <t>1. As ao open the bell after the request of TC-PM-072.1-01 entered FOR_TSU_REVIEW.</t>
         </is>
       </c>
       <c r="L207" s="12" t="inlineStr">
         <is>
-          <t>tsulead has an SLA alert for PKR-2026-900002; the request is red on the home page.</t>
+          <t>ao, who is not an owner of FOR_TSU_REVIEW, has no notification for that stage entry.</t>
         </is>
       </c>
       <c r="M207" s="12" t="inlineStr">
@@ -27875,7 +27894,7 @@
       </c>
       <c r="N207" s="12" t="inlineStr">
         <is>
-          <t>PackageExpiryIT#theSlaParametersAreCopiedIntoTheWorkflowStages</t>
+          <t>WorkflowServiceIT#queuesShowOnlyTheStagesOfTheUsersTeamAndSupportClaimAndAssignment</t>
         </is>
       </c>
       <c r="O207" s="27" t="inlineStr">
@@ -27891,7 +27910,7 @@
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-073.3-01</t>
+          <t>TC-PM-073.1-01</t>
         </is>
       </c>
       <c r="B208" s="12" t="inlineStr">
@@ -27911,7 +27930,7 @@
       </c>
       <c r="E208" s="12" t="inlineStr">
         <is>
-          <t>Action not allowed in the stage</t>
+          <t>MBS set-up without the ManCom sign-off through the API</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
@@ -27921,7 +27940,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -27937,13 +27956,13 @@
       </c>
       <c r="K208" s="12" t="inlineStr">
         <is>
-          <t>1. Call the workflow action terms_final on PKR-2026-900001 (DRAFT).</t>
+          <t>1. As mbs call POST .../requests/{id}/setup on PKR-2026-900004 (FOR_MANCOM).</t>
         </is>
       </c>
       <c r="L208" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "'terms_final' is not allowed while PKR-2026-900001 is in stage Draft request" (WORKFLOW_TRANSITION_NOT_ALLOWED).</t>
+          <t>Refused; the request stays in FOR_MANCOM.
+Message "MBS receives signed-off requirements only (BRPM.015)" (PKG_NOT_WITH_MBS).</t>
         </is>
       </c>
       <c r="M208" s="12" t="inlineStr">
@@ -27951,11 +27970,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N208" s="12" t="inlineStr">
-        <is>
-          <t>ProductMaintenanceFoundationIT#workflowIsSeededWithOwnersAndValidTransitions</t>
-        </is>
-      </c>
+      <c r="N208" s="12" t="inlineStr"/>
       <c r="O208" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -27969,7 +27984,7 @@
     <row r="209">
       <c r="A209" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-073.2-02</t>
+          <t>TC-PM-073.1-02</t>
         </is>
       </c>
       <c r="B209" s="12" t="inlineStr">
@@ -27989,22 +28004,22 @@
       </c>
       <c r="E209" s="12" t="inlineStr">
         <is>
-          <t>A changed SLA parameter reaches the stage</t>
+          <t>A user without the stage permission cannot move the case</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Security-access</t>
         </is>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; System Parameters</t>
+          <t>API call with the user's token (tester tool, for example Postman)</t>
         </is>
       </c>
       <c r="I209" s="12" t="inlineStr"/>
@@ -28015,12 +28030,13 @@
       </c>
       <c r="K209" s="12" t="inlineStr">
         <is>
-          <t>1. Set PKG_SLA_NEGOTIATION to 96; run the daily job; open a request in NEGOTIATION.</t>
+          <t>1. As tsu call the workflow action approve on a request in FOR_MKT_APPROVAL.</t>
         </is>
       </c>
       <c r="L209" s="12" t="inlineStr">
         <is>
-          <t>The due time of the stage uses 96 hours.</t>
+          <t>Refused.
+Message "You are not allowed to 'Approve and send to TSU'" (WORKFLOW_ACTION_NOT_PERMITTED).</t>
         </is>
       </c>
       <c r="M209" s="12" t="inlineStr">
@@ -28030,7 +28046,7 @@
       </c>
       <c r="N209" s="12" t="inlineStr">
         <is>
-          <t>PackageExpiryIT#theSlaParametersAreCopiedIntoTheWorkflowStages</t>
+          <t>ProductMaintenanceFoundationIT#requestCaseMovesThroughTheApprovalChain</t>
         </is>
       </c>
       <c r="O209" s="27" t="inlineStr">
@@ -28046,63 +28062,58 @@
     <row r="210">
       <c r="A210" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.1-01</t>
+          <t>TC-PM-073.2-01</t>
         </is>
       </c>
       <c r="B210" s="12" t="inlineStr">
         <is>
-          <t>SC-PM-08</t>
+          <t>SC-PM-07</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-080</t>
+          <t>FR-PM-073</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>PMADD07, PMADD08</t>
+          <t>BRPM.021</t>
         </is>
       </c>
       <c r="E210" s="12" t="inlineStr">
         <is>
-          <t>New criterion authorised by badmin</t>
+          <t>SLA alert to the stage owners</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Incentive Criteria</t>
-        </is>
-      </c>
-      <c r="I210" s="12" t="inlineStr">
-        <is>
-          <t>SCR-PM-16</t>
-        </is>
-      </c>
+          <t>Notifications (bell icon in the page header)</t>
+        </is>
+      </c>
+      <c r="I210" s="12" t="inlineStr"/>
       <c r="J210" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-11 Catalogue and insurer panel</t>
+          <t>Data: TD-PM-05 UPDATE request at ManCom; TD-PM-02 Draft NEW generic request</t>
         </is>
       </c>
       <c r="K210" s="12" t="inlineStr">
         <is>
-          <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign (seed), value basis Fixed amount, value 500, effective from today; products MTR12; save.
-2. As badmin authorise it in My Approvals.</t>
+          <t>1. Leave PKR-2026-900002 in FOR_TSU_REVIEW beyond 24 hours; let the SLA check run; as tsulead open the bell.</t>
         </is>
       </c>
       <c r="L210" s="12" t="inlineStr">
         <is>
-          <t>Saved as Pending authorisation; after authorisation Active.</t>
+          <t>tsulead has an SLA alert for PKR-2026-900002; the request is red on the home page.</t>
         </is>
       </c>
       <c r="M210" s="12" t="inlineStr">
@@ -28112,7 +28123,7 @@
       </c>
       <c r="N210" s="12" t="inlineStr">
         <is>
-          <t>CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp; IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
+          <t>PackageExpiryIT#theSlaParametersAreCopiedIntoTheWorkflowStages</t>
         </is>
       </c>
       <c r="O210" s="27" t="inlineStr">
@@ -28128,27 +28139,27 @@
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.1-02</t>
+          <t>TC-PM-073.3-01</t>
         </is>
       </c>
       <c r="B211" s="12" t="inlineStr">
         <is>
-          <t>SC-PM-08</t>
+          <t>SC-PM-07</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-080</t>
+          <t>FR-PM-073</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>PMADD07, PMADD08</t>
+          <t>BRPM.021</t>
         </is>
       </c>
       <c r="E211" s="12" t="inlineStr">
         <is>
-          <t>The maker cannot authorise the criterion</t>
+          <t>Action not allowed in the stage</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
@@ -28158,33 +28169,29 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
+          <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
         <is>
-          <t>My Approvals</t>
-        </is>
-      </c>
-      <c r="I211" s="12" t="inlineStr">
-        <is>
-          <t>SCR-PM-22</t>
-        </is>
-      </c>
+          <t>API call with the user's token (tester tool, for example Postman)</t>
+        </is>
+      </c>
+      <c r="I211" s="12" t="inlineStr"/>
       <c r="J211" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-11 Catalogue and insurer panel</t>
+          <t>Data: TD-PM-05 UPDATE request at ManCom; TD-PM-02 Draft NEW generic request</t>
         </is>
       </c>
       <c r="K211" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs open My Approvals.</t>
+          <t>1. Call the workflow action terms_final on PKR-2026-900001 (DRAFT).</t>
         </is>
       </c>
       <c r="L211" s="12" t="inlineStr">
         <is>
-          <t>UAT1 is not offered to mbs; a direct authorise call is refused.
-Message "A record cannot be authorized by the user who maintained it" (MAKER_CHECKER_VIOLATION).</t>
+          <t>Refused.
+Message "'terms_final' is not allowed while PKR-2026-900001 is in stage Draft request" (WORKFLOW_TRANSITION_NOT_ALLOWED).</t>
         </is>
       </c>
       <c r="M211" s="12" t="inlineStr">
@@ -28194,7 +28201,7 @@
       </c>
       <c r="N211" s="12" t="inlineStr">
         <is>
-          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
+          <t>ProductMaintenanceFoundationIT#workflowIsSeededWithOwnersAndValidTransitions</t>
         </is>
       </c>
       <c r="O211" s="27" t="inlineStr">
@@ -28210,63 +28217,58 @@
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.2-01</t>
+          <t>TC-PM-073.2-02</t>
         </is>
       </c>
       <c r="B212" s="12" t="inlineStr">
         <is>
-          <t>SC-PM-08</t>
+          <t>SC-PM-07</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-080</t>
+          <t>FR-PM-073</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>PMADD07, PMADD08</t>
+          <t>BRPM.021</t>
         </is>
       </c>
       <c r="E212" s="12" t="inlineStr">
         <is>
-          <t>Criterion without products</t>
+          <t>A changed SLA parameter reaches the stage</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Incentive Criteria</t>
-        </is>
-      </c>
-      <c r="I212" s="12" t="inlineStr">
-        <is>
-          <t>SCR-PM-16</t>
-        </is>
-      </c>
+          <t>Administration &gt; System Parameters</t>
+        </is>
+      </c>
+      <c r="I212" s="12" t="inlineStr"/>
       <c r="J212" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-11 Catalogue and insurer panel</t>
+          <t>Data: TD-PM-05 UPDATE request at ManCom; TD-PM-02 Draft NEW generic request</t>
         </is>
       </c>
       <c r="K212" s="12" t="inlineStr">
         <is>
-          <t>1. New Criterion with every attribute but no product; save.</t>
+          <t>1. Set PKG_SLA_NEGOTIATION to 96; run the daily job; open a request in NEGOTIATION.</t>
         </is>
       </c>
       <c r="L212" s="12" t="inlineStr">
         <is>
-          <t>Not saved.
-Message "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED).</t>
+          <t>The due time of the stage uses 96 hours.</t>
         </is>
       </c>
       <c r="M212" s="12" t="inlineStr">
@@ -28276,7 +28278,7 @@
       </c>
       <c r="N212" s="12" t="inlineStr">
         <is>
-          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
+          <t>PackageExpiryIT#theSlaParametersAreCopiedIntoTheWorkflowStages</t>
         </is>
       </c>
       <c r="O212" s="27" t="inlineStr">
@@ -28292,7 +28294,7 @@
     <row r="213">
       <c r="A213" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.2-02</t>
+          <t>TC-PM-080.1-01</t>
         </is>
       </c>
       <c r="B213" s="12" t="inlineStr">
@@ -28312,12 +28314,12 @@
       </c>
       <c r="E213" s="12" t="inlineStr">
         <is>
-          <t>Criterion on a retired product</t>
+          <t>New criterion authorised by badmin</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="G213" s="12" t="inlineStr">
@@ -28342,13 +28344,13 @@
       </c>
       <c r="K213" s="12" t="inlineStr">
         <is>
-          <t>1. New Criterion on product MTR32 (retired in TC-PM-045.1-01).</t>
+          <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign (seed), value basis Fixed amount, value 500, effective from today; products MTR12; save.
+2. As badmin authorise it in My Approvals.</t>
         </is>
       </c>
       <c r="L213" s="12" t="inlineStr">
         <is>
-          <t>Not saved.
-Message "Product MTR32 is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE).</t>
+          <t>Saved as Pending authorisation; after authorisation Active.</t>
         </is>
       </c>
       <c r="M213" s="12" t="inlineStr">
@@ -28356,7 +28358,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N213" s="12" t="inlineStr"/>
+      <c r="N213" s="12" t="inlineStr">
+        <is>
+          <t>CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp; IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
+        </is>
+      </c>
       <c r="O213" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -28370,7 +28376,7 @@
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.2-03</t>
+          <t>TC-PM-080.1-02</t>
         </is>
       </c>
       <c r="B214" s="12" t="inlineStr">
@@ -28390,7 +28396,7 @@
       </c>
       <c r="E214" s="12" t="inlineStr">
         <is>
-          <t>Rate criterion without value</t>
+          <t>The maker cannot authorise the criterion</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
@@ -28405,12 +28411,12 @@
       </c>
       <c r="H214" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance &gt; Incentive Criteria</t>
+          <t>My Approvals</t>
         </is>
       </c>
       <c r="I214" s="12" t="inlineStr">
         <is>
-          <t>SCR-PM-16</t>
+          <t>SCR-PM-22</t>
         </is>
       </c>
       <c r="J214" s="12" t="inlineStr">
@@ -28420,13 +28426,13 @@
       </c>
       <c r="K214" s="12" t="inlineStr">
         <is>
-          <t>1. Value basis Rate, value empty; save.</t>
+          <t>1. As mbs open My Approvals.</t>
         </is>
       </c>
       <c r="L214" s="12" t="inlineStr">
         <is>
-          <t>Not saved.
-Message "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED).</t>
+          <t>UAT1 is not offered to mbs; a direct authorise call is refused.
+Message "A record cannot be authorized by the user who maintained it" (MAKER_CHECKER_VIOLATION).</t>
         </is>
       </c>
       <c r="M214" s="12" t="inlineStr">
@@ -28436,7 +28442,7 @@
       </c>
       <c r="N214" s="12" t="inlineStr">
         <is>
-          <t>productMaintenanceForms.test.ts#requires products, a value and logical dates</t>
+          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
         </is>
       </c>
       <c r="O214" s="27" t="inlineStr">
@@ -28452,7 +28458,7 @@
     <row r="215">
       <c r="A215" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.2-04</t>
+          <t>TC-PM-080.2-01</t>
         </is>
       </c>
       <c r="B215" s="12" t="inlineStr">
@@ -28472,7 +28478,7 @@
       </c>
       <c r="E215" s="12" t="inlineStr">
         <is>
-          <t>Rule parameters not valid JSON</t>
+          <t>Criterion without products</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
@@ -28502,13 +28508,13 @@
       </c>
       <c r="K215" s="12" t="inlineStr">
         <is>
-          <t>1. Value basis Rule, rule parameters "{minimumPremium 5000"; save.</t>
+          <t>1. New Criterion with every attribute but no product; save.</t>
         </is>
       </c>
       <c r="L215" s="12" t="inlineStr">
         <is>
           <t>Not saved.
-Message "The rule parameters must be valid JSON" (INCENTIVE_RULE_PARAMS_INVALID).</t>
+Message "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED).</t>
         </is>
       </c>
       <c r="M215" s="12" t="inlineStr">
@@ -28516,7 +28522,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N215" s="12" t="inlineStr"/>
+      <c r="N215" s="12" t="inlineStr">
+        <is>
+          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
+        </is>
+      </c>
       <c r="O215" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -28530,7 +28540,7 @@
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.2-05</t>
+          <t>TC-PM-080.2-02</t>
         </is>
       </c>
       <c r="B216" s="12" t="inlineStr">
@@ -28550,7 +28560,7 @@
       </c>
       <c r="E216" s="12" t="inlineStr">
         <is>
-          <t>Overlapping period for the same code</t>
+          <t>Criterion on a retired product</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
@@ -28580,13 +28590,13 @@
       </c>
       <c r="K216" s="12" t="inlineStr">
         <is>
-          <t>1. New Criterion with code CPC2 effective from today.</t>
+          <t>1. New Criterion on product MTR32 (retired in TC-PM-045.1-01).</t>
         </is>
       </c>
       <c r="L216" s="12" t="inlineStr">
         <is>
           <t>Not saved.
-Message "Criterion CPC2 already covers part of this period" (INCENTIVE_PERIOD_OVERLAP).</t>
+Message "Product MTR32 is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE).</t>
         </is>
       </c>
       <c r="M216" s="12" t="inlineStr">
@@ -28594,11 +28604,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N216" s="12" t="inlineStr">
-        <is>
-          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
-        </is>
-      </c>
+      <c r="N216" s="12" t="inlineStr"/>
       <c r="O216" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -28612,7 +28618,7 @@
     <row r="217">
       <c r="A217" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.3-01</t>
+          <t>TC-PM-080.2-03</t>
         </is>
       </c>
       <c r="B217" s="12" t="inlineStr">
@@ -28632,12 +28638,12 @@
       </c>
       <c r="E217" s="12" t="inlineStr">
         <is>
-          <t>Amend CPC2 through a successor</t>
+          <t>Rate criterion without value</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G217" s="12" t="inlineStr">
@@ -28662,13 +28668,13 @@
       </c>
       <c r="K217" s="12" t="inlineStr">
         <is>
-          <t>1. Open CPC2; click Amend; value 1.25, effective from next month; save.
-2. Check CPC2 before authorisation; authorise as badmin; check again.</t>
+          <t>1. Value basis Rate, value empty; save.</t>
         </is>
       </c>
       <c r="L217" s="12" t="inlineStr">
         <is>
-          <t>Before authorisation the old row stays Active; after authorisation the old row ends the day before the successor starts and the successor is Active.</t>
+          <t>Not saved.
+Message "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED).</t>
         </is>
       </c>
       <c r="M217" s="12" t="inlineStr">
@@ -28678,7 +28684,7 @@
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
-          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
+          <t>productMaintenanceForms.test.ts#requires products, a value and logical dates</t>
         </is>
       </c>
       <c r="O217" s="27" t="inlineStr">
@@ -28694,7 +28700,7 @@
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.3-02</t>
+          <t>TC-PM-080.2-04</t>
         </is>
       </c>
       <c r="B218" s="12" t="inlineStr">
@@ -28714,7 +28720,7 @@
       </c>
       <c r="E218" s="12" t="inlineStr">
         <is>
-          <t>Direct edit of an active criterion</t>
+          <t>Rule parameters not valid JSON</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
@@ -28744,13 +28750,13 @@
       </c>
       <c r="K218" s="12" t="inlineStr">
         <is>
-          <t>1. Call PUT /api/v1/catalog/incentive-criteria/{id} on the active CPC2.</t>
+          <t>1. Value basis Rule, rule parameters "{minimumPremium 5000"; save.</t>
         </is>
       </c>
       <c r="L218" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED).</t>
+          <t>Not saved.
+Message "The rule parameters must be valid JSON" (INCENTIVE_RULE_PARAMS_INVALID).</t>
         </is>
       </c>
       <c r="M218" s="12" t="inlineStr">
@@ -28772,7 +28778,7 @@
     <row r="219">
       <c r="A219" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.3-03</t>
+          <t>TC-PM-080.2-05</t>
         </is>
       </c>
       <c r="B219" s="12" t="inlineStr">
@@ -28792,12 +28798,12 @@
       </c>
       <c r="E219" s="12" t="inlineStr">
         <is>
-          <t>Deactivate a criterion</t>
+          <t>Overlapping period for the same code</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G219" s="12" t="inlineStr">
@@ -28822,12 +28828,13 @@
       </c>
       <c r="K219" s="12" t="inlineStr">
         <is>
-          <t>1. Open UAT1; click Deactivate; confirm.</t>
+          <t>1. New Criterion with code CPC2 effective from today.</t>
         </is>
       </c>
       <c r="L219" s="12" t="inlineStr">
         <is>
-          <t>UAT1 is Inactive with today as end date.</t>
+          <t>Not saved.
+Message "Criterion CPC2 already covers part of this period" (INCENTIVE_PERIOD_OVERLAP).</t>
         </is>
       </c>
       <c r="M219" s="12" t="inlineStr">
@@ -28837,7 +28844,7 @@
       </c>
       <c r="N219" s="12" t="inlineStr">
         <is>
-          <t>CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp</t>
+          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
         </is>
       </c>
       <c r="O219" s="27" t="inlineStr">
@@ -28853,7 +28860,7 @@
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-080.4-01</t>
+          <t>TC-PM-080.3-01</t>
         </is>
       </c>
       <c r="B220" s="12" t="inlineStr">
@@ -28873,12 +28880,12 @@
       </c>
       <c r="E220" s="12" t="inlineStr">
         <is>
-          <t>History of CPC2</t>
+          <t>Amend CPC2 through a successor</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="G220" s="12" t="inlineStr">
@@ -28903,12 +28910,13 @@
       </c>
       <c r="K220" s="12" t="inlineStr">
         <is>
-          <t>1. Open CPC2; History.</t>
+          <t>1. Open CPC2; click Amend; value 1.25, effective from next month; save.
+2. Check CPC2 before authorisation; authorise as badmin; check again.</t>
         </is>
       </c>
       <c r="L220" s="12" t="inlineStr">
         <is>
-          <t>Every version of CPC2 is listed with its values, dates, maker and authoriser, linked to its successor.</t>
+          <t>Before authorisation the old row stays Active; after authorisation the old row ends the day before the successor starts and the successor is Active.</t>
         </is>
       </c>
       <c r="M220" s="12" t="inlineStr">
@@ -28918,7 +28926,7 @@
       </c>
       <c r="N220" s="12" t="inlineStr">
         <is>
-          <t>CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp</t>
+          <t>IncentiveCriteriaIT#criteriaAreValidatedAuthorisedAmendedAndDeactivated</t>
         </is>
       </c>
       <c r="O220" s="27" t="inlineStr">
@@ -28934,7 +28942,7 @@
     <row r="221">
       <c r="A221" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-081.1-01</t>
+          <t>TC-PM-080.3-02</t>
         </is>
       </c>
       <c r="B221" s="12" t="inlineStr">
@@ -28944,7 +28952,7 @@
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-081</t>
+          <t>FR-PM-080</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
@@ -28954,12 +28962,12 @@
       </c>
       <c r="E221" s="12" t="inlineStr">
         <is>
-          <t>Booked invoice on MTR12 carries CPC2</t>
+          <t>Direct edit of an active criterion</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G221" s="12" t="inlineStr">
@@ -28969,24 +28977,28 @@
       </c>
       <c r="H221" s="12" t="inlineStr">
         <is>
-          <t>Booking &gt; Booking Workbench &gt; Booked Invoice</t>
-        </is>
-      </c>
-      <c r="I221" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Incentive Criteria</t>
+        </is>
+      </c>
+      <c r="I221" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-16</t>
+        </is>
+      </c>
       <c r="J221" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-14 Masked quotation data</t>
+          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
       <c r="K221" s="12" t="inlineStr">
         <is>
-          <t>1. Book an invoice on MTR12 that meets CPC2 (premium above PHP 5,000).
-2. Open the booked invoice.</t>
+          <t>1. Call PUT /api/v1/catalog/incentive-criteria/{id} on the active CPC2.</t>
         </is>
       </c>
       <c r="L221" s="12" t="inlineStr">
         <is>
-          <t>The invoice shows criteria code CPC2 and the incentive flag.</t>
+          <t>Refused.
+Message "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED).</t>
         </is>
       </c>
       <c r="M221" s="12" t="inlineStr">
@@ -28994,11 +29006,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N221" s="12" t="inlineStr">
-        <is>
-          <t>IncentiveCriteriaIT#bookingStampsTheMatchedCriteriaCodes</t>
-        </is>
-      </c>
+      <c r="N221" s="12" t="inlineStr"/>
       <c r="O221" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
@@ -29012,7 +29020,7 @@
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-081.1-02</t>
+          <t>TC-PM-080.3-03</t>
         </is>
       </c>
       <c r="B222" s="12" t="inlineStr">
@@ -29022,7 +29030,7 @@
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-081</t>
+          <t>FR-PM-080</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
@@ -29032,12 +29040,12 @@
       </c>
       <c r="E222" s="12" t="inlineStr">
         <is>
-          <t>Invoice on a product outside CPC2 has no code</t>
+          <t>Deactivate a criterion</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="G222" s="12" t="inlineStr">
@@ -29047,23 +29055,27 @@
       </c>
       <c r="H222" s="12" t="inlineStr">
         <is>
-          <t>Booking &gt; Booking Workbench &gt; Booked Invoice</t>
-        </is>
-      </c>
-      <c r="I222" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Incentive Criteria</t>
+        </is>
+      </c>
+      <c r="I222" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-16</t>
+        </is>
+      </c>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-14 Masked quotation data</t>
+          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
       <c r="K222" s="12" t="inlineStr">
         <is>
-          <t>1. Book an invoice on a non-package product.</t>
+          <t>1. Open UAT1; click Deactivate; confirm.</t>
         </is>
       </c>
       <c r="L222" s="12" t="inlineStr">
         <is>
-          <t>No criteria code and no incentive flag.</t>
+          <t>UAT1 is Inactive with today as end date.</t>
         </is>
       </c>
       <c r="M222" s="12" t="inlineStr">
@@ -29073,7 +29085,7 @@
       </c>
       <c r="N222" s="12" t="inlineStr">
         <is>
-          <t>IncentiveCriteriaIT#bookingStampsTheMatchedCriteriaCodes</t>
+          <t>CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp</t>
         </is>
       </c>
       <c r="O222" s="27" t="inlineStr">
@@ -29089,7 +29101,7 @@
     <row r="223">
       <c r="A223" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-081.2-01</t>
+          <t>TC-PM-080.4-01</t>
         </is>
       </c>
       <c r="B223" s="12" t="inlineStr">
@@ -29099,7 +29111,7 @@
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>FR-PM-081</t>
+          <t>FR-PM-080</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
@@ -29109,7 +29121,7 @@
       </c>
       <c r="E223" s="12" t="inlineStr">
         <is>
-          <t>Retirement flags the criteria of the product</t>
+          <t>History of CPC2</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
@@ -29124,24 +29136,27 @@
       </c>
       <c r="H223" s="12" t="inlineStr">
         <is>
-          <t>Notifications (bell icon in the page header)</t>
-        </is>
-      </c>
-      <c r="I223" s="12" t="inlineStr"/>
+          <t>Product Maintenance &gt; Incentive Criteria</t>
+        </is>
+      </c>
+      <c r="I223" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-16</t>
+        </is>
+      </c>
       <c r="J223" s="12" t="inlineStr">
         <is>
-          <t>A criterion active on MTR32 before its retirement.
-Data: TD-PM-09 Active incentive criterion; TD-PM-14 Masked quotation data</t>
+          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
       <c r="K223" s="12" t="inlineStr">
         <is>
-          <t>1. Retire MTR32 (TC-PM-045.1-01); as mbs open the bell and Incentive Criteria.</t>
+          <t>1. Open CPC2; History.</t>
         </is>
       </c>
       <c r="L223" s="12" t="inlineStr">
         <is>
-          <t>Alert INCENTIVE_PRODUCT_INACTIVE names the criterion and MTR32; the criterion is still listed.</t>
+          <t>Every version of CPC2 is listed with its values, dates, maker and authoriser, linked to its successor.</t>
         </is>
       </c>
       <c r="M223" s="12" t="inlineStr">
@@ -29151,7 +29166,7 @@
       </c>
       <c r="N223" s="12" t="inlineStr">
         <is>
-          <t>IncentiveCriteriaIT#criteriaOfAPackageThatIsNoLongerSoldAreFlagged</t>
+          <t>CatalogProductMaintenanceApiIT#coveragesClausesIncentivesAndExceptionsAreMaintainedOverHttp</t>
         </is>
       </c>
       <c r="O223" s="27" t="inlineStr">
@@ -29167,7 +29182,7 @@
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-081.3-01</t>
+          <t>TC-PM-081.1-01</t>
         </is>
       </c>
       <c r="B224" s="12" t="inlineStr">
@@ -29187,17 +29202,17 @@
       </c>
       <c r="E224" s="12" t="inlineStr">
         <is>
-          <t>Former booking incentive rule cannot be changed</t>
+          <t>Booked invoice on MTR12 carries CPC2</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -29213,13 +29228,13 @@
       </c>
       <c r="K224" s="12" t="inlineStr">
         <is>
-          <t>1. Open Booking &gt; Booking Setup, incentive rules; try to edit a rule.</t>
+          <t>1. Book an invoice on MTR12 that meets CPC2 (premium above PHP 5,000).
+2. Open the booked invoice.</t>
         </is>
       </c>
       <c r="L224" s="12" t="inlineStr">
         <is>
-          <t>Refused.
-Message "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN).</t>
+          <t>The invoice shows criteria code CPC2 and the incentive flag.</t>
         </is>
       </c>
       <c r="M224" s="12" t="inlineStr">
@@ -29245,51 +29260,284 @@
     <row r="225">
       <c r="A225" s="12" t="inlineStr">
         <is>
+          <t>TC-PM-081.1-02</t>
+        </is>
+      </c>
+      <c r="B225" s="12" t="inlineStr">
+        <is>
+          <t>SC-PM-08</t>
+        </is>
+      </c>
+      <c r="C225" s="12" t="inlineStr">
+        <is>
+          <t>FR-PM-081</t>
+        </is>
+      </c>
+      <c r="D225" s="12" t="inlineStr">
+        <is>
+          <t>PMADD07, PMADD08</t>
+        </is>
+      </c>
+      <c r="E225" s="12" t="inlineStr">
+        <is>
+          <t>Invoice on a product outside CPC2 has no code</t>
+        </is>
+      </c>
+      <c r="F225" s="12" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G225" s="12" t="inlineStr">
+        <is>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
+        </is>
+      </c>
+      <c r="H225" s="12" t="inlineStr">
+        <is>
+          <t>Booking &gt; Booking Workbench &gt; Booked Invoice</t>
+        </is>
+      </c>
+      <c r="I225" s="12" t="inlineStr"/>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-14 Masked quotation data</t>
+        </is>
+      </c>
+      <c r="K225" s="12" t="inlineStr">
+        <is>
+          <t>1. Book an invoice on a non-package product.</t>
+        </is>
+      </c>
+      <c r="L225" s="12" t="inlineStr">
+        <is>
+          <t>No criteria code and no incentive flag.</t>
+        </is>
+      </c>
+      <c r="M225" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N225" s="12" t="inlineStr">
+        <is>
+          <t>IncentiveCriteriaIT#bookingStampsTheMatchedCriteriaCodes</t>
+        </is>
+      </c>
+      <c r="O225" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P225" s="12" t="n"/>
+      <c r="Q225" s="12" t="n"/>
+      <c r="R225" s="28" t="n"/>
+      <c r="S225" s="12" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-081.2-01</t>
+        </is>
+      </c>
+      <c r="B226" s="12" t="inlineStr">
+        <is>
+          <t>SC-PM-08</t>
+        </is>
+      </c>
+      <c r="C226" s="12" t="inlineStr">
+        <is>
+          <t>FR-PM-081</t>
+        </is>
+      </c>
+      <c r="D226" s="12" t="inlineStr">
+        <is>
+          <t>PMADD07, PMADD08</t>
+        </is>
+      </c>
+      <c r="E226" s="12" t="inlineStr">
+        <is>
+          <t>Retirement flags the criteria of the product</t>
+        </is>
+      </c>
+      <c r="F226" s="12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G226" s="12" t="inlineStr">
+        <is>
+          <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
+        </is>
+      </c>
+      <c r="H226" s="12" t="inlineStr">
+        <is>
+          <t>Notifications (bell icon in the page header)</t>
+        </is>
+      </c>
+      <c r="I226" s="12" t="inlineStr"/>
+      <c r="J226" s="12" t="inlineStr">
+        <is>
+          <t>A criterion active on MTR32 before its retirement.
+Data: TD-PM-09 Active incentive criterion; TD-PM-14 Masked quotation data</t>
+        </is>
+      </c>
+      <c r="K226" s="12" t="inlineStr">
+        <is>
+          <t>1. Retire MTR32 (TC-PM-045.1-01); as mbs open the bell and Incentive Criteria.</t>
+        </is>
+      </c>
+      <c r="L226" s="12" t="inlineStr">
+        <is>
+          <t>Alert INCENTIVE_PRODUCT_INACTIVE names the criterion and MTR32; the criterion is still listed.</t>
+        </is>
+      </c>
+      <c r="M226" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N226" s="12" t="inlineStr">
+        <is>
+          <t>IncentiveCriteriaIT#criteriaOfAPackageThatIsNoLongerSoldAreFlagged</t>
+        </is>
+      </c>
+      <c r="O226" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P226" s="12" t="n"/>
+      <c r="Q226" s="12" t="n"/>
+      <c r="R226" s="28" t="n"/>
+      <c r="S226" s="12" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-081.3-01</t>
+        </is>
+      </c>
+      <c r="B227" s="12" t="inlineStr">
+        <is>
+          <t>SC-PM-08</t>
+        </is>
+      </c>
+      <c r="C227" s="12" t="inlineStr">
+        <is>
+          <t>FR-PM-081</t>
+        </is>
+      </c>
+      <c r="D227" s="12" t="inlineStr">
+        <is>
+          <t>PMADD07, PMADD08</t>
+        </is>
+      </c>
+      <c r="E227" s="12" t="inlineStr">
+        <is>
+          <t>Former booking incentive rule cannot be changed</t>
+        </is>
+      </c>
+      <c r="F227" s="12" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G227" s="12" t="inlineStr">
+        <is>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
+        </is>
+      </c>
+      <c r="H227" s="12" t="inlineStr">
+        <is>
+          <t>Booking &gt; Booking Workbench &gt; Booked Invoice</t>
+        </is>
+      </c>
+      <c r="I227" s="12" t="inlineStr"/>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t>Data: TD-PM-09 Active incentive criterion; TD-PM-14 Masked quotation data</t>
+        </is>
+      </c>
+      <c r="K227" s="12" t="inlineStr">
+        <is>
+          <t>1. Open Booking &gt; Booking Setup, incentive rules; try to edit a rule.</t>
+        </is>
+      </c>
+      <c r="L227" s="12" t="inlineStr">
+        <is>
+          <t>Refused.
+Message "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN).</t>
+        </is>
+      </c>
+      <c r="M227" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N227" s="12" t="inlineStr">
+        <is>
+          <t>IncentiveCriteriaIT#bookingStampsTheMatchedCriteriaCodes</t>
+        </is>
+      </c>
+      <c r="O227" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P227" s="12" t="n"/>
+      <c r="Q227" s="12" t="n"/>
+      <c r="R227" s="28" t="n"/>
+      <c r="S227" s="12" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="12" t="inlineStr">
+        <is>
           <t>TC-PM-SCR-01</t>
         </is>
       </c>
-      <c r="B225" s="12" t="inlineStr"/>
-      <c r="C225" s="12" t="inlineStr">
+      <c r="B228" s="12" t="inlineStr"/>
+      <c r="C228" s="12" t="inlineStr">
         <is>
           <t>FR-PM-070</t>
         </is>
       </c>
-      <c r="D225" s="12" t="inlineStr">
+      <c r="D228" s="12" t="inlineStr">
         <is>
           <t>BRPM.019</t>
         </is>
       </c>
-      <c r="E225" s="12" t="inlineStr">
+      <c r="E228" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-01 Product Maintenance Home matches the signed specification</t>
         </is>
       </c>
-      <c r="F225" s="12" t="inlineStr">
+      <c r="F228" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G225" s="12" t="inlineStr">
+      <c r="G228" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H225" s="12" t="inlineStr">
+      <c r="H228" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Product Maintenance Home</t>
         </is>
       </c>
-      <c r="I225" s="12" t="inlineStr">
+      <c r="I228" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-01</t>
         </is>
       </c>
-      <c r="J225" s="12" t="inlineStr">
+      <c r="J228" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K225" s="12" t="inlineStr">
+      <c r="K228" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Product Maintenance Home.
@@ -29297,77 +29545,77 @@
 4. Check the buttons offered to the persona and when each is enabled.</t>
         </is>
       </c>
-      <c r="L225" s="12" t="inlineStr">
+      <c r="L228" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-01 Product Maintenance Home of the FRS.
 Fields in this order: 1 Drafts / For Approval / TSU Review / Negotiation / ManCom / With MBS / For Validation / Released (Tile, mandatory -); 2 Within 30 days / Within 60 days / Within 90 days (Tile, mandatory -); 3 Versions for validation (Tile, mandatory -); 4 Advisories pending (Tile, mandatory -); 5 Comparative outputs this week (Tile, mandatory -); 6 Package Expiry (Tile, mandatory -).
 Actions: New Package Request; A stage tile; An expiry tile.</t>
         </is>
       </c>
-      <c r="M225" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N225" s="12" t="inlineStr"/>
-      <c r="O225" s="27" t="inlineStr">
+      <c r="M228" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N228" s="12" t="inlineStr"/>
+      <c r="O228" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P225" s="12" t="n"/>
-      <c r="Q225" s="12" t="n"/>
-      <c r="R225" s="28" t="n"/>
-      <c r="S225" s="12" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="12" t="inlineStr">
+      <c r="P228" s="12" t="n"/>
+      <c r="Q228" s="12" t="n"/>
+      <c r="R228" s="28" t="n"/>
+      <c r="S228" s="12" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-02</t>
         </is>
       </c>
-      <c r="B226" s="12" t="inlineStr"/>
-      <c r="C226" s="12" t="inlineStr">
+      <c r="B229" s="12" t="inlineStr"/>
+      <c r="C229" s="12" t="inlineStr">
         <is>
           <t>FR-PM-024</t>
         </is>
       </c>
-      <c r="D226" s="12" t="inlineStr">
+      <c r="D229" s="12" t="inlineStr">
         <is>
           <t>BRPM.011</t>
         </is>
       </c>
-      <c r="E226" s="12" t="inlineStr">
+      <c r="E229" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-02 Package Requests matches the signed specification</t>
         </is>
       </c>
-      <c r="F226" s="12" t="inlineStr">
+      <c r="F229" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G226" s="12" t="inlineStr">
+      <c r="G229" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H226" s="12" t="inlineStr">
+      <c r="H229" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests</t>
         </is>
       </c>
-      <c r="I226" s="12" t="inlineStr">
+      <c r="I229" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-02</t>
         </is>
       </c>
-      <c r="J226" s="12" t="inlineStr">
+      <c r="J229" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K226" s="12" t="inlineStr">
+      <c r="K229" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests.
@@ -29375,77 +29623,77 @@
 4. Check the buttons offered to the persona and when each is enabled.</t>
         </is>
       </c>
-      <c r="L226" s="12" t="inlineStr">
+      <c r="L229" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-02 Package Requests of the FRS.
 Fields in this order: 1 Drafts / For Approval / TSU Review / Negotiation / ManCom / With MBS / For Validation / Released / Closed (Tab, mandatory -); 2 Search Request No. (Text, mandatory N); 3 Only My Requests (Check box, mandatory N); 4 Request type (Drop-down, mandatory N); 5 Request No. (Column, mandatory -); 6 Type (Column, mandatory -); 7 Scope (Column, mandatory -); 8 Client / Programme (Column, mandatory -); 9 Line (Column, mandatory -); 10 Product (Column, mandatory -); 11 Stage (Column, mandatory -); 12 In Stage (Column, mandatory -); 13 Assignee (Column, mandatory -).
 Actions: Package Expiry; New Package Request; Assign; Filters; Open a row.</t>
         </is>
       </c>
-      <c r="M226" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N226" s="12" t="inlineStr"/>
-      <c r="O226" s="27" t="inlineStr">
+      <c r="M229" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N229" s="12" t="inlineStr"/>
+      <c r="O229" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P226" s="12" t="n"/>
-      <c r="Q226" s="12" t="n"/>
-      <c r="R226" s="28" t="n"/>
-      <c r="S226" s="12" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="12" t="inlineStr">
+      <c r="P229" s="12" t="n"/>
+      <c r="Q229" s="12" t="n"/>
+      <c r="R229" s="28" t="n"/>
+      <c r="S229" s="12" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-03</t>
         </is>
       </c>
-      <c r="B227" s="12" t="inlineStr"/>
-      <c r="C227" s="12" t="inlineStr">
+      <c r="B230" s="12" t="inlineStr"/>
+      <c r="C230" s="12" t="inlineStr">
         <is>
           <t>FR-PM-020</t>
         </is>
       </c>
-      <c r="D227" s="12" t="inlineStr">
+      <c r="D230" s="12" t="inlineStr">
         <is>
           <t>BRPM.008, BRPM.011</t>
         </is>
       </c>
-      <c r="E227" s="12" t="inlineStr">
+      <c r="E230" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-03 New Package Request and Edit Package Request matches the signed specification</t>
         </is>
       </c>
-      <c r="F227" s="12" t="inlineStr">
+      <c r="F230" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G227" s="12" t="inlineStr">
+      <c r="G230" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H227" s="12" t="inlineStr">
+      <c r="H230" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › New Package Request</t>
         </is>
       </c>
-      <c r="I227" s="12" t="inlineStr">
+      <c r="I230" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-03</t>
         </is>
       </c>
-      <c r="J227" s="12" t="inlineStr">
+      <c r="J230" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K227" s="12" t="inlineStr">
+      <c r="K230" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › New Package Request.
@@ -29454,7 +29702,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L227" s="12" t="inlineStr">
+      <c r="L230" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-03 New Package Request and Edit Package Request of the FRS.
 Fields in this order: 1 Request type (Drop-down, mandatory Y); 2 Scope (Drop-down, mandatory Y); 3 Package / programme name (Text, mandatory Y); 4 Client or prospect (Look-up, mandatory Cond.: client-specific package); 5 Product line (Drop-down, mandatory Y); 6 Cover type / subtype (Drop-down, mandatory Cond.: New package); 7 Package product (Drop-down, mandatory Cond.: every type except New package); 8 Reason (Drop-down, mandatory Y); 9 Comment on the reason (Text, mandatory N); 10 Negotiate with the insurers (Check box, mandatory N); 11 Market segments (Check boxes, mandatory N); 12 Heading / Details (Text, mandatory Cond.: sections or coverages before submission); 13 Coverage code (Text, mandatory Cond.: sections or coverages before submission); 14 Included (Check box, mandatory N); 15 Limit (Number, mandatory N); 16 Deductible (Text, mandatory N); 17 Requested rate % (Number, mandatory N); 18 Minimum premium (Number, mandatory N); 19 Commission % (Number, mandatory N); 20 Package TSI limit (Number, mandatory N); 21 Effective from (Date, mandatory N); 22 Package start (Date, mandatory N); 23 Package end (Date, mandatory Cond.: before submission (not for Retire)); 24 Anniversary (Date, mandatory N); 25 Insurer check boxes (Check boxes, mandatory Cond.: at least one when the insurers are approached); 26 Documents panel (Upload, mandatory N).
@@ -29462,70 +29710,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M227" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N227" s="12" t="inlineStr"/>
-      <c r="O227" s="27" t="inlineStr">
+      <c r="M230" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N230" s="12" t="inlineStr"/>
+      <c r="O230" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P227" s="12" t="n"/>
-      <c r="Q227" s="12" t="n"/>
-      <c r="R227" s="28" t="n"/>
-      <c r="S227" s="12" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="12" t="inlineStr">
+      <c r="P230" s="12" t="n"/>
+      <c r="Q230" s="12" t="n"/>
+      <c r="R230" s="28" t="n"/>
+      <c r="S230" s="12" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-04</t>
         </is>
       </c>
-      <c r="B228" s="12" t="inlineStr"/>
-      <c r="C228" s="12" t="inlineStr">
+      <c r="B231" s="12" t="inlineStr"/>
+      <c r="C231" s="12" t="inlineStr">
         <is>
           <t>FR-PM-021</t>
         </is>
       </c>
-      <c r="D228" s="12" t="inlineStr">
+      <c r="D231" s="12" t="inlineStr">
         <is>
           <t>BRPM.008, BRPM.021</t>
         </is>
       </c>
-      <c r="E228" s="12" t="inlineStr">
+      <c r="E231" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-04 Package Request record matches the signed specification</t>
         </is>
       </c>
-      <c r="F228" s="12" t="inlineStr">
+      <c r="F231" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G228" s="12" t="inlineStr">
+      <c r="G231" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H228" s="12" t="inlineStr">
+      <c r="H231" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I228" s="12" t="inlineStr">
+      <c r="I231" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-04</t>
         </is>
       </c>
-      <c r="J228" s="12" t="inlineStr">
+      <c r="J231" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K228" s="12" t="inlineStr">
+      <c r="K231" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
@@ -29534,7 +29782,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L228" s="12" t="inlineStr">
+      <c r="L231" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-04 Package Request record of the FRS.
 Fields in this order: 1 Request (Reference chip, mandatory -); 2 Stage pill (Pill, mandatory -); 3 Scope and negotiation tags (Tag, mandatory -); 4 Request type (Fact, mandatory -); 5 Client / programme (Fact, mandatory -); 6 Line / product (Fact, mandatory -); 7 Scheme rate (Fact, mandatory -); 8 Package term (Fact, mandatory -); 9 Target insurers / Chosen insurers (Fact, mandatory -); 10 Status strip (Panel, mandatory -); 11 Type / Scope / Client / Line / cover type / Market segments / Reason / Negotiation / TSU recommendation (Detail, mandatory -); 12 Submitted / Marketing approval / TSU recommendation / TSU Head approval / Terms final / Requirements to ManCom / MBS set-up / Released (Detail, mandatory -); 13 Sections, coverages, rate scheme, dates and insurers (Read-only view, mandatory -); 14 Stage / From Stage / Action / By / Date and Time / Remarks / Duration in Stage (Table, mandatory -); 15 Changed / By / Rev. / Outcome / Rate % / Remarks (Table, mandatory -); 16 Documents panel (Table and upload, mandatory -); 17 Sent e-mails (Table, mandatory -).
@@ -29542,70 +29790,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M228" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N228" s="12" t="inlineStr"/>
-      <c r="O228" s="27" t="inlineStr">
+      <c r="M231" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N231" s="12" t="inlineStr"/>
+      <c r="O231" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P228" s="12" t="n"/>
-      <c r="Q228" s="12" t="n"/>
-      <c r="R228" s="28" t="n"/>
-      <c r="S228" s="12" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="12" t="inlineStr">
+      <c r="P231" s="12" t="n"/>
+      <c r="Q231" s="12" t="n"/>
+      <c r="R231" s="28" t="n"/>
+      <c r="S231" s="12" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-05</t>
         </is>
       </c>
-      <c r="B229" s="12" t="inlineStr"/>
-      <c r="C229" s="12" t="inlineStr">
+      <c r="B232" s="12" t="inlineStr"/>
+      <c r="C232" s="12" t="inlineStr">
         <is>
           <t>FR-PM-030</t>
         </is>
       </c>
-      <c r="D229" s="12" t="inlineStr">
+      <c r="D232" s="12" t="inlineStr">
         <is>
           <t>BRPM.012</t>
         </is>
       </c>
-      <c r="E229" s="12" t="inlineStr">
+      <c r="E232" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-05 Package Request record: Negotiation tab matches the signed specification</t>
         </is>
       </c>
-      <c r="F229" s="12" t="inlineStr">
+      <c r="F232" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G229" s="12" t="inlineStr">
+      <c r="G232" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H229" s="12" t="inlineStr">
+      <c r="H232" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I229" s="12" t="inlineStr">
+      <c r="I232" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-05</t>
         </is>
       </c>
-      <c r="J229" s="12" t="inlineStr">
+      <c r="J232" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K229" s="12" t="inlineStr">
+      <c r="K232" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
@@ -29614,7 +29862,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L229" s="12" t="inlineStr">
+      <c r="L232" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-05 Package Request record: Negotiation tab of the FRS.
 Fields in this order: 1 Round n · slip number (Card title, mandatory -); 2 Round status pill and Locked tag (Pill, mandatory -); 3 Round note (Text, mandatory -); 4 Insurer check boxes (Check boxes, mandatory Y (at least one)); 5 Notes to the insurers (Text, mandatory N); 6 Insurer (Column, mandatory -); 7 Outcome (Column, mandatory -); 8 Rate % / Minimum / Conditions / Valid Until (Column, mandatory -); 9 Rev. (Column, mandatory -); 10 Outcome (Drop-down, mandatory Y); 11 Rate % (Number, mandatory Cond.: an offer (accepted, approved with changes, counter-proposal)); 12 Minimum premium (Number, mandatory N); 13 Valid until (Date, mandatory N); 14 Deductible per coverage (Text, mandatory N); 15 Conditions and warranties (Text, mandatory N); 16 Remarks (Text, mandatory N); 17 Response document (File, mandatory N); 18 Offer check box (Check box, mandatory Y (at least one)); 19 Role (Drop-down, mandatory Y); 20 Share % (Number, mandatory Cond.: co-insurance (lead and participants)); 21 Comment (Text, mandatory N); 22 Insurer check boxes (Check boxes, mandatory Y (at least one)); 23 What changes in this round (Text, mandatory N).
@@ -29622,70 +29870,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M229" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N229" s="12" t="inlineStr"/>
-      <c r="O229" s="27" t="inlineStr">
+      <c r="M232" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N232" s="12" t="inlineStr"/>
+      <c r="O232" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P229" s="12" t="n"/>
-      <c r="Q229" s="12" t="n"/>
-      <c r="R229" s="28" t="n"/>
-      <c r="S229" s="12" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="12" t="inlineStr">
+      <c r="P232" s="12" t="n"/>
+      <c r="Q232" s="12" t="n"/>
+      <c r="R232" s="28" t="n"/>
+      <c r="S232" s="12" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-06</t>
         </is>
       </c>
-      <c r="B230" s="12" t="inlineStr"/>
-      <c r="C230" s="12" t="inlineStr">
+      <c r="B233" s="12" t="inlineStr"/>
+      <c r="C233" s="12" t="inlineStr">
         <is>
           <t>FR-PM-034</t>
         </is>
       </c>
-      <c r="D230" s="12" t="inlineStr">
+      <c r="D233" s="12" t="inlineStr">
         <is>
           <t>BRPM.014, BRPM.013</t>
         </is>
       </c>
-      <c r="E230" s="12" t="inlineStr">
+      <c r="E233" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-06 Package Request record: Comparative tab matches the signed specification</t>
         </is>
       </c>
-      <c r="F230" s="12" t="inlineStr">
+      <c r="F233" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G230" s="12" t="inlineStr">
+      <c r="G233" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H230" s="12" t="inlineStr">
+      <c r="H233" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I230" s="12" t="inlineStr">
+      <c r="I233" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-06</t>
         </is>
       </c>
-      <c r="J230" s="12" t="inlineStr">
+      <c r="J233" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K230" s="12" t="inlineStr">
+      <c r="K233" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
@@ -29694,7 +29942,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L230" s="12" t="inlineStr">
+      <c r="L233" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-06 Package Request record: Comparative tab of the FRS.
 Fields in this order: 1 Insurer (Column, mandatory -); 2 Outcome / Rate % / Minimum / Coverages / Deductibles / Conditions (Column, mandatory -); 3 Output (Column, mandatory -); 4 Status (Column, mandatory -); 5 Fields (Column, mandatory -); 6 Generated (Column, mandatory -); 7 SHA-256 (Column, mandatory -); 8 Title (Text, mandatory Y); 9 Fields shown (Check boxes, mandatory Y (at least one)); 10 Insurers shown (Check boxes, mandatory Y (at least one)).
@@ -29702,70 +29950,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M230" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N230" s="12" t="inlineStr"/>
-      <c r="O230" s="27" t="inlineStr">
+      <c r="M233" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N233" s="12" t="inlineStr"/>
+      <c r="O233" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P230" s="12" t="n"/>
-      <c r="Q230" s="12" t="n"/>
-      <c r="R230" s="28" t="n"/>
-      <c r="S230" s="12" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="12" t="inlineStr">
+      <c r="P233" s="12" t="n"/>
+      <c r="Q233" s="12" t="n"/>
+      <c r="R233" s="28" t="n"/>
+      <c r="S233" s="12" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-07</t>
         </is>
       </c>
-      <c r="B231" s="12" t="inlineStr"/>
-      <c r="C231" s="12" t="inlineStr">
+      <c r="B234" s="12" t="inlineStr"/>
+      <c r="C234" s="12" t="inlineStr">
         <is>
           <t>FR-PM-040</t>
         </is>
       </c>
-      <c r="D231" s="12" t="inlineStr">
+      <c r="D234" s="12" t="inlineStr">
         <is>
           <t>BRPM.015</t>
         </is>
       </c>
-      <c r="E231" s="12" t="inlineStr">
+      <c r="E234" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-07 Package Request record: Requirements &amp; Sign-off tab matches the signed specification</t>
         </is>
       </c>
-      <c r="F231" s="12" t="inlineStr">
+      <c r="F234" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G231" s="12" t="inlineStr">
+      <c r="G234" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H231" s="12" t="inlineStr">
+      <c r="H234" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I231" s="12" t="inlineStr">
+      <c r="I234" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-07</t>
         </is>
       </c>
-      <c r="J231" s="12" t="inlineStr">
+      <c r="J234" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K231" s="12" t="inlineStr">
+      <c r="K234" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
@@ -29774,7 +30022,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L231" s="12" t="inlineStr">
+      <c r="L234" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-07 Package Request record: Requirements &amp; Sign-off tab of the FRS.
 Fields in this order: 1 Checklist (Checklist, mandatory -); 2 Scheme rate % (Number, mandatory Cond.: or a rate for every insurer); 3 Minimum premium / Commission % / Package TSI limit (Number, mandatory N); 4 Computation basis (Text, mandatory Y); 5 Effective from (Date, mandatory Y); 6 Package start / Anniversary (Date, mandatory N); 7 Package end (Date, mandatory Y); 8 Sections, coverages, rate scheme, dates and insurers (Read-only view, mandatory -); 9 Reference / Decision / By / On / Comment (Table, mandatory -).
@@ -29782,70 +30030,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M231" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N231" s="12" t="inlineStr"/>
-      <c r="O231" s="27" t="inlineStr">
+      <c r="M234" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N234" s="12" t="inlineStr"/>
+      <c r="O234" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P231" s="12" t="n"/>
-      <c r="Q231" s="12" t="n"/>
-      <c r="R231" s="28" t="n"/>
-      <c r="S231" s="12" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="12" t="inlineStr">
+      <c r="P234" s="12" t="n"/>
+      <c r="Q234" s="12" t="n"/>
+      <c r="R234" s="28" t="n"/>
+      <c r="S234" s="12" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-08</t>
         </is>
       </c>
-      <c r="B232" s="12" t="inlineStr"/>
-      <c r="C232" s="12" t="inlineStr">
+      <c r="B235" s="12" t="inlineStr"/>
+      <c r="C235" s="12" t="inlineStr">
         <is>
           <t>FR-PM-042</t>
         </is>
       </c>
-      <c r="D232" s="12" t="inlineStr">
+      <c r="D235" s="12" t="inlineStr">
         <is>
           <t>BRPM.015</t>
         </is>
       </c>
-      <c r="E232" s="12" t="inlineStr">
+      <c r="E235" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-08 Package Request record: Set-up and Advisories tabs matches the signed specification</t>
         </is>
       </c>
-      <c r="F232" s="12" t="inlineStr">
+      <c r="F235" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G232" s="12" t="inlineStr">
+      <c r="G235" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H232" s="12" t="inlineStr">
+      <c r="H235" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I232" s="12" t="inlineStr">
+      <c r="I235" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-08</t>
         </is>
       </c>
-      <c r="J232" s="12" t="inlineStr">
+      <c r="J235" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K232" s="12" t="inlineStr">
+      <c r="K235" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
@@ -29854,7 +30102,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L232" s="12" t="inlineStr">
+      <c r="L235" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-08 Package Request record: Set-up and Advisories tabs of the FRS.
 Fields in this order: 1 Risk code of the new package (Text, mandatory Cond.: New package); 2 Product name (Text, mandatory N); 3 Change summary (Text, mandatory N); 4 Comment (Text, mandatory N); 5 Product / Version / Request stage (Detail, mandatory -); 6 Advisory card (Card, mandatory -); 7 Supporting documents checklist (Checklist, mandatory -); 8 Recipient groups (Check boxes, mandatory Y (at least one)); 9 E-mail to (optional) (Text, mandatory N); 10 Subject (Text, mandatory Y); 11 Text (Text, mandatory Y).
@@ -29862,70 +30110,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M232" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N232" s="12" t="inlineStr"/>
-      <c r="O232" s="27" t="inlineStr">
+      <c r="M235" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N235" s="12" t="inlineStr"/>
+      <c r="O235" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P232" s="12" t="n"/>
-      <c r="Q232" s="12" t="n"/>
-      <c r="R232" s="28" t="n"/>
-      <c r="S232" s="12" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="12" t="inlineStr">
+      <c r="P235" s="12" t="n"/>
+      <c r="Q235" s="12" t="n"/>
+      <c r="R235" s="28" t="n"/>
+      <c r="S235" s="12" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-09</t>
         </is>
       </c>
-      <c r="B233" s="12" t="inlineStr"/>
-      <c r="C233" s="12" t="inlineStr">
+      <c r="B236" s="12" t="inlineStr"/>
+      <c r="C236" s="12" t="inlineStr">
         <is>
           <t>FR-PM-024</t>
         </is>
       </c>
-      <c r="D233" s="12" t="inlineStr">
+      <c r="D236" s="12" t="inlineStr">
         <is>
           <t>BRPM.011</t>
         </is>
       </c>
-      <c r="E233" s="12" t="inlineStr">
+      <c r="E236" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-09 TSU Workbench matches the signed specification</t>
         </is>
       </c>
-      <c r="F233" s="12" t="inlineStr">
+      <c r="F236" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G233" s="12" t="inlineStr">
+      <c r="G236" s="12" t="inlineStr">
         <is>
           <t>TSU – TSU Officer (SIT/UAT user tsu)</t>
         </is>
       </c>
-      <c r="H233" s="12" t="inlineStr">
+      <c r="H236" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › TSU Workbench</t>
         </is>
       </c>
-      <c r="I233" s="12" t="inlineStr">
+      <c r="I236" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-09</t>
         </is>
       </c>
-      <c r="J233" s="12" t="inlineStr">
+      <c r="J236" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K233" s="12" t="inlineStr">
+      <c r="K236" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as tsu.
 2. Open Client &amp; Policy › Product Maintenance › TSU Workbench.
@@ -29933,77 +30181,77 @@
 4. Check the buttons offered to the persona and when each is enabled.</t>
         </is>
       </c>
-      <c r="L233" s="12" t="inlineStr">
+      <c r="L236" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-09 TSU Workbench of the FRS.
 Fields in this order: 1 Stage tiles (Tile, mandatory -); 2 Reference (Column, mandatory -); 3 Description (Column, mandatory -); 4 Stage (Column, mandatory -); 5 From (Column, mandatory -); 6 In Stage (Column, mandatory -); 7 Due (Column, mandatory -); 8 Assignee (Column, mandatory -).
 Actions: A stage tile; Claim; Assign; Open a row.</t>
         </is>
       </c>
-      <c r="M233" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N233" s="12" t="inlineStr"/>
-      <c r="O233" s="27" t="inlineStr">
+      <c r="M236" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N236" s="12" t="inlineStr"/>
+      <c r="O236" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P233" s="12" t="n"/>
-      <c r="Q233" s="12" t="n"/>
-      <c r="R233" s="28" t="n"/>
-      <c r="S233" s="12" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="12" t="inlineStr">
+      <c r="P236" s="12" t="n"/>
+      <c r="Q236" s="12" t="n"/>
+      <c r="R236" s="28" t="n"/>
+      <c r="S236" s="12" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-10</t>
         </is>
       </c>
-      <c r="B234" s="12" t="inlineStr"/>
-      <c r="C234" s="12" t="inlineStr">
+      <c r="B237" s="12" t="inlineStr"/>
+      <c r="C237" s="12" t="inlineStr">
         <is>
           <t>FR-PM-060</t>
         </is>
       </c>
-      <c r="D234" s="12" t="inlineStr">
+      <c r="D237" s="12" t="inlineStr">
         <is>
           <t>BRPM.017</t>
         </is>
       </c>
-      <c r="E234" s="12" t="inlineStr">
+      <c r="E237" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-10 Package Expiry matches the signed specification</t>
         </is>
       </c>
-      <c r="F234" s="12" t="inlineStr">
+      <c r="F237" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G234" s="12" t="inlineStr">
+      <c r="G237" s="12" t="inlineStr">
         <is>
           <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
-      <c r="H234" s="12" t="inlineStr">
+      <c r="H237" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Expiry</t>
         </is>
       </c>
-      <c r="I234" s="12" t="inlineStr">
+      <c r="I237" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-10</t>
         </is>
       </c>
-      <c r="J234" s="12" t="inlineStr">
+      <c r="J237" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K234" s="12" t="inlineStr">
+      <c r="K237" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mkttl.
 2. Open Client &amp; Policy › Product Maintenance › Package Expiry.
@@ -30011,77 +30259,77 @@
 4. Check the buttons offered to the persona and when each is enabled.</t>
         </is>
       </c>
-      <c r="L234" s="12" t="inlineStr">
+      <c r="L237" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-10 Package Expiry of the FRS.
 Fields in this order: 1 Expiring / Renewal in Progress / Expired (Tab, mandatory -); 2 Package (Column, mandatory -); 3 Package End (Column, mandatory -); 4 Days Left (Column, mandatory -); 5 Anniversary (Column, mandatory -); 6 Renewal Request (Column, mandatory -); 7 Packages ending within (days) (Number, mandatory Y).
 Actions: Generate Expiry List; Generate Renewal Request.</t>
         </is>
       </c>
-      <c r="M234" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N234" s="12" t="inlineStr"/>
-      <c r="O234" s="27" t="inlineStr">
+      <c r="M237" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N237" s="12" t="inlineStr"/>
+      <c r="O237" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P234" s="12" t="n"/>
-      <c r="Q234" s="12" t="n"/>
-      <c r="R234" s="28" t="n"/>
-      <c r="S234" s="12" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="12" t="inlineStr">
+      <c r="P237" s="12" t="n"/>
+      <c r="Q237" s="12" t="n"/>
+      <c r="R237" s="28" t="n"/>
+      <c r="S237" s="12" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-11</t>
         </is>
       </c>
-      <c r="B235" s="12" t="inlineStr"/>
-      <c r="C235" s="12" t="inlineStr">
+      <c r="B238" s="12" t="inlineStr"/>
+      <c r="C238" s="12" t="inlineStr">
         <is>
           <t>FR-PM-010</t>
         </is>
       </c>
-      <c r="D235" s="12" t="inlineStr">
+      <c r="D238" s="12" t="inlineStr">
         <is>
           <t>PMADD01</t>
         </is>
       </c>
-      <c r="E235" s="12" t="inlineStr">
+      <c r="E238" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-11 Products matches the signed specification</t>
         </is>
       </c>
-      <c r="F235" s="12" t="inlineStr">
+      <c r="F238" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G235" s="12" t="inlineStr">
+      <c r="G238" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H235" s="12" t="inlineStr">
+      <c r="H238" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Products</t>
         </is>
       </c>
-      <c r="I235" s="12" t="inlineStr">
+      <c r="I238" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-11</t>
         </is>
       </c>
-      <c r="J235" s="12" t="inlineStr">
+      <c r="J238" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K235" s="12" t="inlineStr">
+      <c r="K238" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Products.
@@ -30090,7 +30338,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L235" s="12" t="inlineStr">
+      <c r="L238" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-11 Products of the FRS.
 Fields in this order: 1 Products / Field rules / Document rules / TSU routing (Tab, mandatory -); 2 Search (Text, mandatory N); 3 Product line (Drop-down, mandatory N); 4 Package (Drop-down, mandatory N); 5 Market segment (Drop-down, mandatory N); 6 Lifecycle (Drop-down, mandatory N); 7 Active only (Check box, mandatory N); 8 Code / Name / Line (Column, mandatory -); 9 Package (Column, mandatory -); 10 Version (Column, mandatory -); 11 Segments (Column, mandatory -); 12 Rate % / Min. Premium (Column, mandatory -); 13 Status (Column, mandatory -); 14 Code (Text, mandatory Y); 15 Name (Text, mandatory Y); 16 Product line (Drop-down, mandatory Y); 17 Cover type (Drop-down, mandatory Cond.: package product); 18 Placement after (Drop-down, mandatory Y); 19 TSU review (Drop-down, mandatory N); 20 Default rate % (Number, mandatory N); 21 Default commission % (Number, mandatory Y); 22 Minimum premium (Number, mandatory Y); 23 Package TSI limit (Number, mandatory N); 24 Maximum term (years) (Number, mandatory Cond.: multi-year term allowed); 25 Package product (fixed cover) / Fleet (several vehicles) / Mortgage / loan related / Direct payment to insurer allowed / Multi-year term allowed / Free First Year eligible (Check box, mandatory N); 26 Market segments (none = all) (Check boxes, mandatory N); 27 Applies to / Level / Field / Key / Mandatory / Status (Column, mandatory -); 28 Applies to / Document / Before Submission / Status (Column, mandatory -); 29 Priority / Code / Description / Criteria / TSI Above / Status (Column, mandatory -).
@@ -30098,70 +30346,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M235" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N235" s="12" t="inlineStr"/>
-      <c r="O235" s="27" t="inlineStr">
+      <c r="M238" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N238" s="12" t="inlineStr"/>
+      <c r="O238" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P235" s="12" t="n"/>
-      <c r="Q235" s="12" t="n"/>
-      <c r="R235" s="28" t="n"/>
-      <c r="S235" s="12" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="12" t="inlineStr">
+      <c r="P238" s="12" t="n"/>
+      <c r="Q238" s="12" t="n"/>
+      <c r="R238" s="28" t="n"/>
+      <c r="S238" s="12" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-12</t>
         </is>
       </c>
-      <c r="B236" s="12" t="inlineStr"/>
-      <c r="C236" s="12" t="inlineStr">
+      <c r="B239" s="12" t="inlineStr"/>
+      <c r="C239" s="12" t="inlineStr">
         <is>
           <t>FR-PM-050</t>
         </is>
       </c>
-      <c r="D236" s="12" t="inlineStr">
+      <c r="D239" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E236" s="12" t="inlineStr">
+      <c r="E239" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-12 Product record matches the signed specification</t>
         </is>
       </c>
-      <c r="F236" s="12" t="inlineStr">
+      <c r="F239" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G236" s="12" t="inlineStr">
+      <c r="G239" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H236" s="12" t="inlineStr">
+      <c r="H239" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Products › Product</t>
         </is>
       </c>
-      <c r="I236" s="12" t="inlineStr">
+      <c r="I239" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-12</t>
         </is>
       </c>
-      <c r="J236" s="12" t="inlineStr">
+      <c r="J239" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K236" s="12" t="inlineStr">
+      <c r="K239" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Products › Product.
@@ -30170,7 +30418,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L236" s="12" t="inlineStr">
+      <c r="L239" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-12 Product record of the FRS.
 Fields in this order: 1 Risk code (Reference chip, mandatory -); 2 Lifecycle and record status pills (Pill, mandatory -); 3 Package and version tags (Tag, mandatory -); 4 Line › Type / Current Version / Rate % / Package End / TSU Review (Fact, mandatory -); 5 Version / Status / Effective From / Effective To / Rate % / Package End / Request / Validated By / Change (Column, mandatory -); 6 What changes (Text, mandatory Y); 7 Line / Cover type / Risk items / Rating / Package / Package TSI limit / Fleet / Market segments / Mortgage related / Direct payment allowed / Multi-year / Free First Year / Placement after / Default rate % / Default commission % / Minimum premium / TSU review (Detail, mandatory -); 8 Level / Field / Key / Mandatory / Check / From (Column, mandatory -); 9 Documents required before submission (List, mandatory -); 10 Applies to (Drop-down, mandatory Y); 11 Level (Drop-down, mandatory N); 12 Field key / Label (Text, mandatory Y); 13 Check (Drop-down, mandatory N); 14 List of values / Minimum / Maximum / Pattern (Text / Number, mandatory Cond.: by check); 15 Document type (Drop-down, mandatory Y); 16 Mandatory (Check box, mandatory N).
@@ -30178,70 +30426,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M236" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N236" s="12" t="inlineStr"/>
-      <c r="O236" s="27" t="inlineStr">
+      <c r="M239" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N239" s="12" t="inlineStr"/>
+      <c r="O239" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P236" s="12" t="n"/>
-      <c r="Q236" s="12" t="n"/>
-      <c r="R236" s="28" t="n"/>
-      <c r="S236" s="12" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="12" t="inlineStr">
+      <c r="P239" s="12" t="n"/>
+      <c r="Q239" s="12" t="n"/>
+      <c r="R239" s="28" t="n"/>
+      <c r="S239" s="12" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-13</t>
         </is>
       </c>
-      <c r="B237" s="12" t="inlineStr"/>
-      <c r="C237" s="12" t="inlineStr">
+      <c r="B240" s="12" t="inlineStr"/>
+      <c r="C240" s="12" t="inlineStr">
         <is>
           <t>FR-PM-043</t>
         </is>
       </c>
-      <c r="D237" s="12" t="inlineStr">
+      <c r="D240" s="12" t="inlineStr">
         <is>
           <t>PMADD06, BRPM.015</t>
         </is>
       </c>
-      <c r="E237" s="12" t="inlineStr">
+      <c r="E240" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-13 Package Version matches the signed specification</t>
         </is>
       </c>
-      <c r="F237" s="12" t="inlineStr">
+      <c r="F240" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G237" s="12" t="inlineStr">
+      <c r="G240" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H237" s="12" t="inlineStr">
+      <c r="H240" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Product › Package Version</t>
         </is>
       </c>
-      <c r="I237" s="12" t="inlineStr">
+      <c r="I240" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-13</t>
         </is>
       </c>
-      <c r="J237" s="12" t="inlineStr">
+      <c r="J240" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K237" s="12" t="inlineStr">
+      <c r="K240" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Product › Package Version.
@@ -30250,7 +30498,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L237" s="12" t="inlineStr">
+      <c r="L240" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-13 Package Version of the FRS.
 Fields in this order: 1 Product / Version (Reference chip, mandatory -); 2 Version status pill (Pill, mandatory -); 3 Request tag (Tag, mandatory -); 4 Effective / Package End / Rate % / Set Up By / ManCom Ref. (Fact, mandatory -); 5 Package Rate % (Number, mandatory Cond.: or a rate for every insurer); 6 Minimum Premium (Number, mandatory Y); 7 Commission % (Number, mandatory Y); 8 Package TSI Limit (Number, mandatory N); 9 Effective From (Date, mandatory Y); 10 Package Start (Date, mandatory N); 11 Package End (Date, mandatory N); 12 Anniversary (Date, mandatory N); 13 Change Summary (Text, mandatory N); 14 ManCom Sign-off Reference (Text, mandatory N); 15 Computation Basis (Text, mandatory N); 16 Coverage (Column, mandatory Y (at least one included)); 17 Included / Optional (Check box, mandatory N); 18 Limit / Deductible (Number, mandatory N); 19 Add coverage (Drop-down, mandatory N); 20 Insurer (Column, mandatory N); 21 Role (Drop-down, mandatory Y); 22 Share % (Number, mandatory Cond.: lead and participants); 23 Rate % (Number, mandatory Cond.: when there is no package rate); 24 Minimum Premium (Number, mandatory N); 25 Add insurer (Drop-down, mandatory N); 26 Insurer / Coverage (Column, mandatory Y (every pair)); 27 Covered (Check box, mandatory N); 28 Limit / Deductible / Deductible Wording (Number / Text, mandatory N); 29 Clauses (Multi-select, mandatory N); 30 Hierarchy complete: cover type and basic coverage / Every panel insurer has terms for each included coverage / Rates and minimum premiums match the signed-off terms / Dates and package term are correct / Test premium reviewed (Check box, mandatory Y (all five)); 31 Validated by, date and test premium (Detail, mandatory -); 32 Return reason / Comment (Drop-down / Text, mandatory Y (reason)).
@@ -30258,70 +30506,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M237" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N237" s="12" t="inlineStr"/>
-      <c r="O237" s="27" t="inlineStr">
+      <c r="M240" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N240" s="12" t="inlineStr"/>
+      <c r="O240" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P237" s="12" t="n"/>
-      <c r="Q237" s="12" t="n"/>
-      <c r="R237" s="28" t="n"/>
-      <c r="S237" s="12" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="12" t="inlineStr">
+      <c r="P240" s="12" t="n"/>
+      <c r="Q240" s="12" t="n"/>
+      <c r="R240" s="28" t="n"/>
+      <c r="S240" s="12" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-14</t>
         </is>
       </c>
-      <c r="B238" s="12" t="inlineStr"/>
-      <c r="C238" s="12" t="inlineStr">
+      <c r="B241" s="12" t="inlineStr"/>
+      <c r="C241" s="12" t="inlineStr">
         <is>
           <t>FR-PM-043</t>
         </is>
       </c>
-      <c r="D238" s="12" t="inlineStr">
+      <c r="D241" s="12" t="inlineStr">
         <is>
           <t>PMADD06, BRPM.015</t>
         </is>
       </c>
-      <c r="E238" s="12" t="inlineStr">
+      <c r="E241" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-14 Validation Queue matches the signed specification</t>
         </is>
       </c>
-      <c r="F238" s="12" t="inlineStr">
+      <c r="F241" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G238" s="12" t="inlineStr">
+      <c r="G241" s="12" t="inlineStr">
         <is>
           <t>TSU_HEAD – TSU Head (SIT/UAT user tsuhead)</t>
         </is>
       </c>
-      <c r="H238" s="12" t="inlineStr">
+      <c r="H241" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Validation Queue</t>
         </is>
       </c>
-      <c r="I238" s="12" t="inlineStr">
+      <c r="I241" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-14</t>
         </is>
       </c>
-      <c r="J238" s="12" t="inlineStr">
+      <c r="J241" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K238" s="12" t="inlineStr">
+      <c r="K241" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as tsuhead.
 2. Open Client &amp; Policy › Product Maintenance › Validation Queue.
@@ -30330,7 +30578,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L238" s="12" t="inlineStr">
+      <c r="L241" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-14 Validation Queue of the FRS.
 Fields in this order: 1 Search Product (Text, mandatory N); 2 Product / Name / Version / Status (Column, mandatory -); 3 Effective From (Column, mandatory -); 4 Request (Column, mandatory -); 5 Submitted By / Submitted (Column, mandatory -); 6 Age (days) (Column, mandatory -).
@@ -30338,70 +30586,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M238" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N238" s="12" t="inlineStr"/>
-      <c r="O238" s="27" t="inlineStr">
+      <c r="M241" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N241" s="12" t="inlineStr"/>
+      <c r="O241" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P238" s="12" t="n"/>
-      <c r="Q238" s="12" t="n"/>
-      <c r="R238" s="28" t="n"/>
-      <c r="S238" s="12" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="12" t="inlineStr">
+      <c r="P241" s="12" t="n"/>
+      <c r="Q241" s="12" t="n"/>
+      <c r="R241" s="28" t="n"/>
+      <c r="S241" s="12" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-15</t>
         </is>
       </c>
-      <c r="B239" s="12" t="inlineStr"/>
-      <c r="C239" s="12" t="inlineStr">
+      <c r="B242" s="12" t="inlineStr"/>
+      <c r="C242" s="12" t="inlineStr">
         <is>
           <t>FR-PM-010</t>
         </is>
       </c>
-      <c r="D239" s="12" t="inlineStr">
+      <c r="D242" s="12" t="inlineStr">
         <is>
           <t>PMADD01</t>
         </is>
       </c>
-      <c r="E239" s="12" t="inlineStr">
+      <c r="E242" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-15 Coverages &amp; Clauses matches the signed specification</t>
         </is>
       </c>
-      <c r="F239" s="12" t="inlineStr">
+      <c r="F242" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G239" s="12" t="inlineStr">
+      <c r="G242" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H239" s="12" t="inlineStr">
+      <c r="H242" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Coverages &amp; Clauses</t>
         </is>
       </c>
-      <c r="I239" s="12" t="inlineStr">
+      <c r="I242" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-15</t>
         </is>
       </c>
-      <c r="J239" s="12" t="inlineStr">
+      <c r="J242" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K239" s="12" t="inlineStr">
+      <c r="K242" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Coverages &amp; Clauses.
@@ -30410,7 +30658,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L239" s="12" t="inlineStr">
+      <c r="L242" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-15 Coverages &amp; Clauses of the FRS.
 Fields in this order: 1 Coverages &amp; Perils / Clause Library (Tab, mandatory -); 2 Product line (Drop-down, mandatory N); 3 Line / Code / Name / Kind / Basic / Status (Column, mandatory -); 4 Code / Kind / Title / Line / Effective / Until / Status (Column, mandatory -); 5 Product line (Drop-down, mandatory Y); 6 Code (Text, mandatory Y); 7 Name (Text, mandatory Y); 8 Kind (Drop-down, mandatory Y); 9 Display order (Number, mandatory N); 10 Basic coverage (Check box, mandatory N); 11 Code (Text, mandatory Y); 12 Kind (Drop-down, mandatory Y); 13 Product line (Drop-down, mandatory N); 14 Title (Text, mandatory Y); 15 Effective from / Effective to (Date, mandatory Y (from)); 16 Wording (Text, mandatory Y).
@@ -30418,70 +30666,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M239" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N239" s="12" t="inlineStr"/>
-      <c r="O239" s="27" t="inlineStr">
+      <c r="M242" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N242" s="12" t="inlineStr"/>
+      <c r="O242" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P239" s="12" t="n"/>
-      <c r="Q239" s="12" t="n"/>
-      <c r="R239" s="28" t="n"/>
-      <c r="S239" s="12" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="12" t="inlineStr">
+      <c r="P242" s="12" t="n"/>
+      <c r="Q242" s="12" t="n"/>
+      <c r="R242" s="28" t="n"/>
+      <c r="S242" s="12" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-16</t>
         </is>
       </c>
-      <c r="B240" s="12" t="inlineStr"/>
-      <c r="C240" s="12" t="inlineStr">
+      <c r="B243" s="12" t="inlineStr"/>
+      <c r="C243" s="12" t="inlineStr">
         <is>
           <t>FR-PM-080</t>
         </is>
       </c>
-      <c r="D240" s="12" t="inlineStr">
+      <c r="D243" s="12" t="inlineStr">
         <is>
           <t>PMADD07, PMADD08</t>
         </is>
       </c>
-      <c r="E240" s="12" t="inlineStr">
+      <c r="E243" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-16 Incentive Criteria matches the signed specification</t>
         </is>
       </c>
-      <c r="F240" s="12" t="inlineStr">
+      <c r="F243" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G240" s="12" t="inlineStr">
+      <c r="G243" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H240" s="12" t="inlineStr">
+      <c r="H243" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Incentive Criteria</t>
         </is>
       </c>
-      <c r="I240" s="12" t="inlineStr">
+      <c r="I243" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-16</t>
         </is>
       </c>
-      <c r="J240" s="12" t="inlineStr">
+      <c r="J243" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K240" s="12" t="inlineStr">
+      <c r="K243" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Incentive Criteria.
@@ -30490,7 +30738,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L240" s="12" t="inlineStr">
+      <c r="L243" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-16 Incentive Criteria of the FRS.
 Fields in this order: 1 Current / Pending Authorization / History (Tab, mandatory -); 2 Search Criterion or Product (Text, mandatory N); 3 Code / Name / Type / Value / Products / From / Until / Status (Column, mandatory -); 4 Code (Text, mandatory Y); 5 Name (Text, mandatory Y); 6 Incentive type (Drop-down, mandatory Y); 7 Value basis (Drop-down, mandatory Y); 8 Value (Number, mandatory Cond.: rate or fixed amount); 9 Effective from (Date, mandatory Y); 10 Effective to (Date, mandatory N); 11 Rule parameters (JSON) (Text, mandatory N); 12 Description (Text, mandatory N); 13 Products matrix (Drop-down and rows, mandatory Y (at least one)).
@@ -30498,70 +30746,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M240" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N240" s="12" t="inlineStr"/>
-      <c r="O240" s="27" t="inlineStr">
+      <c r="M243" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N243" s="12" t="inlineStr"/>
+      <c r="O243" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P240" s="12" t="n"/>
-      <c r="Q240" s="12" t="n"/>
-      <c r="R240" s="28" t="n"/>
-      <c r="S240" s="12" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="12" t="inlineStr">
+      <c r="P243" s="12" t="n"/>
+      <c r="Q243" s="12" t="n"/>
+      <c r="R243" s="28" t="n"/>
+      <c r="S243" s="12" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-17</t>
         </is>
       </c>
-      <c r="B241" s="12" t="inlineStr"/>
-      <c r="C241" s="12" t="inlineStr">
+      <c r="B244" s="12" t="inlineStr"/>
+      <c r="C244" s="12" t="inlineStr">
         <is>
           <t>FR-PM-014</t>
         </is>
       </c>
-      <c r="D241" s="12" t="inlineStr">
+      <c r="D244" s="12" t="inlineStr">
         <is>
           <t>PMADD02</t>
         </is>
       </c>
-      <c r="E241" s="12" t="inlineStr">
+      <c r="E244" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-17 Insurers matches the signed specification</t>
         </is>
       </c>
-      <c r="F241" s="12" t="inlineStr">
+      <c r="F244" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G241" s="12" t="inlineStr">
+      <c r="G244" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H241" s="12" t="inlineStr">
+      <c r="H244" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Insurers</t>
         </is>
       </c>
-      <c r="I241" s="12" t="inlineStr">
+      <c r="I244" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-17</t>
         </is>
       </c>
-      <c r="J241" s="12" t="inlineStr">
+      <c r="J244" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K241" s="12" t="inlineStr">
+      <c r="K244" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Insurers.
@@ -30570,7 +30818,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L241" s="12" t="inlineStr">
+      <c r="L244" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-17 Insurers of the FRS.
 Fields in this order: 1 Code (Column, mandatory -); 2 Name (Column, mandatory -); 3 Accredited Until (Column, mandatory -); 4 Placement / Placement e-mails (Column, mandatory -); 5 Credit Days (Column, mandatory -); 6 Status (Column, mandatory -); 7 Partner code (Text, mandatory Y); 8 Name / Short name (Text, mandatory Y (name)); 9 IC accreditation no. / Accredited until (Text / Date, mandatory N); 10 Placement channel (Drop-down, mandatory Y); 11 Placement e-mails (Text, mandatory N (needed to send quotation slips and placement slips)); 12 Credit days (Number, mandatory N); 13 TIN / Address / E-mail / Phone (Text, mandatory N).
@@ -30578,70 +30826,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M241" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N241" s="12" t="inlineStr"/>
-      <c r="O241" s="27" t="inlineStr">
+      <c r="M244" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N244" s="12" t="inlineStr"/>
+      <c r="O244" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P241" s="12" t="n"/>
-      <c r="Q241" s="12" t="n"/>
-      <c r="R241" s="28" t="n"/>
-      <c r="S241" s="12" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="12" t="inlineStr">
+      <c r="P244" s="12" t="n"/>
+      <c r="Q244" s="12" t="n"/>
+      <c r="R244" s="28" t="n"/>
+      <c r="S244" s="12" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-18</t>
         </is>
       </c>
-      <c r="B242" s="12" t="inlineStr"/>
-      <c r="C242" s="12" t="inlineStr">
+      <c r="B245" s="12" t="inlineStr"/>
+      <c r="C245" s="12" t="inlineStr">
         <is>
           <t>FR-PM-014</t>
         </is>
       </c>
-      <c r="D242" s="12" t="inlineStr">
+      <c r="D245" s="12" t="inlineStr">
         <is>
           <t>PMADD02</t>
         </is>
       </c>
-      <c r="E242" s="12" t="inlineStr">
+      <c r="E245" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-18 Insurer record matches the signed specification</t>
         </is>
       </c>
-      <c r="F242" s="12" t="inlineStr">
+      <c r="F245" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G242" s="12" t="inlineStr">
+      <c r="G245" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H242" s="12" t="inlineStr">
+      <c r="H245" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Insurers › Insurer</t>
         </is>
       </c>
-      <c r="I242" s="12" t="inlineStr">
+      <c r="I245" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-18</t>
         </is>
       </c>
-      <c r="J242" s="12" t="inlineStr">
+      <c r="J245" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K242" s="12" t="inlineStr">
+      <c r="K245" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Insurers › Insurer.
@@ -30650,7 +30898,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L242" s="12" t="inlineStr">
+      <c r="L245" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-18 Insurer record of the FRS.
 Fields in this order: 1 Partner code / Short name / IC accreditation / Accredited until / Placement channel / Placement e-mails / Credit days / Maker / Authorized by (Detail, mandatory -); 2 Code / Name / City / LGT % / Placement e-mail / Status (Column, mandatory -); 3 Product / Commission % / From / To / Status (Column, mandatory -); 4 Code / Name (Text, mandatory Y); 5 City (Text, mandatory N); 6 LGT % (Number, mandatory Y); 7 Placement e-mail (Text, mandatory N); 8 Product (Drop-down, mandatory N); 9 Commission % (Number, mandatory Y); 10 Effective from / Effective to (Date, mandatory Y (from)).
@@ -30658,70 +30906,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M242" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N242" s="12" t="inlineStr"/>
-      <c r="O242" s="27" t="inlineStr">
+      <c r="M245" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N245" s="12" t="inlineStr"/>
+      <c r="O245" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P242" s="12" t="n"/>
-      <c r="Q242" s="12" t="n"/>
-      <c r="R242" s="28" t="n"/>
-      <c r="S242" s="12" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="12" t="inlineStr">
+      <c r="P245" s="12" t="n"/>
+      <c r="Q245" s="12" t="n"/>
+      <c r="R245" s="28" t="n"/>
+      <c r="S245" s="12" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-19</t>
         </is>
       </c>
-      <c r="B243" s="12" t="inlineStr"/>
-      <c r="C243" s="12" t="inlineStr">
+      <c r="B246" s="12" t="inlineStr"/>
+      <c r="C246" s="12" t="inlineStr">
         <is>
           <t>FR-PM-051</t>
         </is>
       </c>
-      <c r="D243" s="12" t="inlineStr">
+      <c r="D246" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E243" s="12" t="inlineStr">
+      <c r="E246" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-19 Rates &amp; Taxes matches the signed specification</t>
         </is>
       </c>
-      <c r="F243" s="12" t="inlineStr">
+      <c r="F246" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G243" s="12" t="inlineStr">
+      <c r="G246" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H243" s="12" t="inlineStr">
+      <c r="H246" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Rates &amp; Taxes</t>
         </is>
       </c>
-      <c r="I243" s="12" t="inlineStr">
+      <c r="I246" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-19</t>
         </is>
       </c>
-      <c r="J243" s="12" t="inlineStr">
+      <c r="J246" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K243" s="12" t="inlineStr">
+      <c r="K246" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Rates &amp; Taxes.
@@ -30730,7 +30978,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L243" s="12" t="inlineStr">
+      <c r="L246" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-19 Rates &amp; Taxes of the FRS.
 Fields in this order: 1 Taxes &amp; factors / Short-period table / BI / PD limits (Tab, mandatory -); 2 Rate / Line / % / From / To / Status (Column, mandatory -); 3 Months Covered (up To) / % of Annual Premium / From / To / Status (Column, mandatory -); 4 Coverage / Limit / Premium / From / To / Status (Column, mandatory -); 5 Rate (Drop-down, mandatory Y); 6 Line code (Text, mandatory N); 7 Rate % / % of annual premium (Number, mandatory Y); 8 Months covered (Number, mandatory Y (short-period table)); 9 Coverage / Limit / Premium (Drop-down / Number, mandatory Y (limit table)); 10 Effective from / Effective to (Date, mandatory Y (from)).
@@ -30738,62 +30986,62 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M243" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N243" s="12" t="inlineStr"/>
-      <c r="O243" s="27" t="inlineStr">
+      <c r="M246" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N246" s="12" t="inlineStr"/>
+      <c r="O246" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P243" s="12" t="n"/>
-      <c r="Q243" s="12" t="n"/>
-      <c r="R243" s="28" t="n"/>
-      <c r="S243" s="12" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="12" t="inlineStr">
+      <c r="P246" s="12" t="n"/>
+      <c r="Q246" s="12" t="n"/>
+      <c r="R246" s="28" t="n"/>
+      <c r="S246" s="12" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-20</t>
         </is>
       </c>
-      <c r="B244" s="12" t="inlineStr"/>
-      <c r="C244" s="12" t="inlineStr"/>
-      <c r="D244" s="12" t="inlineStr"/>
-      <c r="E244" s="12" t="inlineStr">
+      <c r="B247" s="12" t="inlineStr"/>
+      <c r="C247" s="12" t="inlineStr"/>
+      <c r="D247" s="12" t="inlineStr"/>
+      <c r="E247" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-20 Sales Organisation matches the signed specification</t>
         </is>
       </c>
-      <c r="F244" s="12" t="inlineStr">
+      <c r="F247" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G244" s="12" t="inlineStr">
+      <c r="G247" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H244" s="12" t="inlineStr">
+      <c r="H247" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Sales Organisation</t>
         </is>
       </c>
-      <c r="I244" s="12" t="inlineStr">
+      <c r="I247" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-20</t>
         </is>
       </c>
-      <c r="J244" s="12" t="inlineStr">
+      <c r="J247" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K244" s="12" t="inlineStr">
+      <c r="K247" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Sales Organisation.
@@ -30802,7 +31050,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L244" s="12" t="inlineStr">
+      <c r="L247" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-20 Sales Organisation of the FRS.
 Fields in this order: 1 Unit line (Tree, mandatory -); 2 Account officer line (Tree, mandatory -); 3 Level (Drop-down, mandatory Y); 4 Code / Name (Text, mandatory Y); 5 Cost center (Text, mandatory N); 6 Parent (Drop-down, mandatory Cond.: department and team); 7 Team (Drop-down, mandatory Y); 8 User name (Text, mandatory Y).
@@ -30810,70 +31058,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M244" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N244" s="12" t="inlineStr"/>
-      <c r="O244" s="27" t="inlineStr">
+      <c r="M247" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N247" s="12" t="inlineStr"/>
+      <c r="O247" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P244" s="12" t="n"/>
-      <c r="Q244" s="12" t="n"/>
-      <c r="R244" s="28" t="n"/>
-      <c r="S244" s="12" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="12" t="inlineStr">
+      <c r="P247" s="12" t="n"/>
+      <c r="Q247" s="12" t="n"/>
+      <c r="R247" s="28" t="n"/>
+      <c r="S247" s="12" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-21</t>
         </is>
       </c>
-      <c r="B245" s="12" t="inlineStr"/>
-      <c r="C245" s="12" t="inlineStr">
+      <c r="B248" s="12" t="inlineStr"/>
+      <c r="C248" s="12" t="inlineStr">
         <is>
           <t>FR-PM-051</t>
         </is>
       </c>
-      <c r="D245" s="12" t="inlineStr">
+      <c r="D248" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E245" s="12" t="inlineStr">
+      <c r="E248" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-21 Premium Calculator matches the signed specification</t>
         </is>
       </c>
-      <c r="F245" s="12" t="inlineStr">
+      <c r="F248" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G245" s="12" t="inlineStr">
+      <c r="G248" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H245" s="12" t="inlineStr">
+      <c r="H248" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Premium Calculator</t>
         </is>
       </c>
-      <c r="I245" s="12" t="inlineStr">
+      <c r="I248" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-21</t>
         </is>
       </c>
-      <c r="J245" s="12" t="inlineStr">
+      <c r="J248" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K245" s="12" t="inlineStr">
+      <c r="K248" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Premium Calculator.
@@ -30882,7 +31130,7 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L245" s="12" t="inlineStr">
+      <c r="L248" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-21 Premium Calculator of the FRS.
 Fields in this order: 1 Product (Drop-down, mandatory Y); 2 Insurer (Drop-down, mandatory N); 3 Insurer branch (LGT) (Drop-down, mandatory N); 4 Period basis (Drop-down, mandatory N); 5 From / To (Date, mandatory Cond.: pro-rata or short period); 6 Commission % override (Number, mandatory N); 7 Package version (Drop-down, mandatory N); 8 Endorsement (remaining term, may return premium) (Check box, mandatory N); 9 Multi-year own damage factor (Check box, mandatory N); 10 Item / Sum insured (Text / Number, mandatory Y (a sum insured for at least one item)); 11 Rate % (Number, mandatory N); 12 Excess BI limit / PD limit (Number, mandatory N); 13 Version line (Banner, mandatory -); 14 Sum insured / Net premium / Gross premium / Commission (Figure, mandatory -); 15 Component / Basis / Amount (Table, mandatory -).
@@ -30890,70 +31138,70 @@
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M245" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N245" s="12" t="inlineStr"/>
-      <c r="O245" s="27" t="inlineStr">
+      <c r="M248" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N248" s="12" t="inlineStr"/>
+      <c r="O248" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P245" s="12" t="n"/>
-      <c r="Q245" s="12" t="n"/>
-      <c r="R245" s="28" t="n"/>
-      <c r="S245" s="12" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="12" t="inlineStr">
+      <c r="P248" s="12" t="n"/>
+      <c r="Q248" s="12" t="n"/>
+      <c r="R248" s="28" t="n"/>
+      <c r="S248" s="12" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="12" t="inlineStr">
         <is>
           <t>TC-PM-SCR-22</t>
         </is>
       </c>
-      <c r="B246" s="12" t="inlineStr"/>
-      <c r="C246" s="12" t="inlineStr">
+      <c r="B249" s="12" t="inlineStr"/>
+      <c r="C249" s="12" t="inlineStr">
         <is>
           <t>FR-PM-051</t>
         </is>
       </c>
-      <c r="D246" s="12" t="inlineStr">
+      <c r="D249" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E246" s="12" t="inlineStr">
+      <c r="E249" s="12" t="inlineStr">
         <is>
           <t>Screen SCR-PM-22 Quotation: package rate scheme and rate exception matches the signed specification</t>
         </is>
       </c>
-      <c r="F246" s="12" t="inlineStr">
+      <c r="F249" s="12" t="inlineStr">
         <is>
           <t>Screen</t>
         </is>
       </c>
-      <c r="G246" s="12" t="inlineStr">
+      <c r="G249" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H246" s="12" t="inlineStr">
+      <c r="H249" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Quotation / Proposal › Quotations › Quotation</t>
         </is>
       </c>
-      <c r="I246" s="12" t="inlineStr">
+      <c r="I249" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-22</t>
         </is>
       </c>
-      <c r="J246" s="12" t="inlineStr">
+      <c r="J249" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K246" s="12" t="inlineStr">
+      <c r="K249" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Quotation / Proposal › Quotations › Quotation.
@@ -30962,161 +31210,161 @@
 5. Leave one mandatory field blank or enter an invalid value, and save.</t>
         </is>
       </c>
-      <c r="L246" s="12" t="inlineStr">
+      <c r="L249" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-22 Quotation: package rate scheme and rate exception of the FRS.
-Fields in this order: 1 Version line (Banner, mandatory -); 2 Exceptions (Rows, mandatory -); 3 Item rate % (Number, mandatory Y); 4 Valid until (Date, mandatory N); 5 Reason (Text, mandatory Y).
-Actions: Request Rate Exception; Decision in My Approvals.
+Fields in this order: 1 Version line (Banner, mandatory -); 2 Exceptions (Rows, mandatory -); 3 Item rate % (Number, mandatory Y); 4 Valid until (Date, mandatory N); 5 Reason (Text, mandatory Y); 6 Package (Fact, mandatory -); 7 Requested rate (Fact, mandatory -); 8 Scheme in force (Fact, mandatory -); 9 Quotation (Fact, mandatory -); 10 Requested by (Fact, mandatory -); 11 Reason for the exception (Text, mandatory -); 12 Decision (Detail, mandatory -); 13 Comment (Text, mandatory N); 14 Reason for the rejection (Text, mandatory Y).
+Actions: Request Rate Exception; Open from My Approvals; Approve; Reject.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
-      <c r="M246" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N246" s="12" t="inlineStr"/>
-      <c r="O246" s="27" t="inlineStr">
+      <c r="M249" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N249" s="12" t="inlineStr"/>
+      <c r="O249" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P246" s="12" t="n"/>
-      <c r="Q246" s="12" t="n"/>
-      <c r="R246" s="28" t="n"/>
-      <c r="S246" s="12" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="12" t="inlineStr">
+      <c r="P249" s="12" t="n"/>
+      <c r="Q249" s="12" t="n"/>
+      <c r="R249" s="28" t="n"/>
+      <c r="S249" s="12" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-01</t>
         </is>
       </c>
-      <c r="B247" s="12" t="inlineStr"/>
-      <c r="C247" s="12" t="inlineStr">
+      <c r="B250" s="12" t="inlineStr"/>
+      <c r="C250" s="12" t="inlineStr">
         <is>
           <t>FR-PM-024</t>
         </is>
       </c>
-      <c r="D247" s="12" t="inlineStr">
+      <c r="D250" s="12" t="inlineStr">
         <is>
           <t>BRPM.011</t>
         </is>
       </c>
-      <c r="E247" s="12" t="inlineStr">
+      <c r="E250" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Requests (SCR-PM-02)</t>
         </is>
       </c>
-      <c r="F247" s="12" t="inlineStr">
+      <c r="F250" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G247" s="12" t="inlineStr">
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H247" s="12" t="inlineStr">
+      <c r="H250" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests</t>
         </is>
       </c>
-      <c r="I247" s="12" t="inlineStr">
+      <c r="I250" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-02</t>
         </is>
       </c>
-      <c r="J247" s="12" t="inlineStr">
+      <c r="J250" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K247" s="12" t="inlineStr">
+      <c r="K250" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L247" s="12" t="inlineStr">
+      <c r="L250" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-001: "Select requests of one stage"</t>
         </is>
       </c>
-      <c r="M247" s="12" t="inlineStr">
+      <c r="M250" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N247" s="12" t="inlineStr"/>
-      <c r="O247" s="27" t="inlineStr">
+      <c r="N250" s="12" t="inlineStr"/>
+      <c r="O250" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P247" s="12" t="n"/>
-      <c r="Q247" s="12" t="n"/>
-      <c r="R247" s="28" t="n"/>
-      <c r="S247" s="12" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="12" t="inlineStr">
+      <c r="P250" s="12" t="n"/>
+      <c r="Q250" s="12" t="n"/>
+      <c r="R250" s="28" t="n"/>
+      <c r="S250" s="12" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-02</t>
         </is>
       </c>
-      <c r="B248" s="12" t="inlineStr"/>
-      <c r="C248" s="12" t="inlineStr">
+      <c r="B251" s="12" t="inlineStr"/>
+      <c r="C251" s="12" t="inlineStr">
         <is>
           <t>FR-PM-020</t>
         </is>
       </c>
-      <c r="D248" s="12" t="inlineStr">
+      <c r="D251" s="12" t="inlineStr">
         <is>
           <t>BRPM.008, BRPM.011</t>
         </is>
       </c>
-      <c r="E248" s="12" t="inlineStr">
+      <c r="E251" s="12" t="inlineStr">
         <is>
           <t>Messages of New Package Request and Edit Package Request (SCR-PM-03)</t>
         </is>
       </c>
-      <c r="F248" s="12" t="inlineStr">
+      <c r="F251" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G248" s="12" t="inlineStr">
+      <c r="G251" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H248" s="12" t="inlineStr">
+      <c r="H251" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › New Package Request</t>
         </is>
       </c>
-      <c r="I248" s="12" t="inlineStr">
+      <c r="I251" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-03</t>
         </is>
       </c>
-      <c r="J248" s="12" t="inlineStr">
+      <c r="J251" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K248" s="12" t="inlineStr">
+      <c r="K251" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › New Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L248" s="12" t="inlineStr">
+      <c r="L251" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-004: "Enter a code for every coverage or remove the line"
@@ -31138,77 +31386,77 @@
 MSG-PM-021: "Select the package product of the &lt;type&gt; request" (PKG_REQUEST_INCOMPLETE)</t>
         </is>
       </c>
-      <c r="M248" s="12" t="inlineStr">
+      <c r="M251" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N248" s="12" t="inlineStr"/>
-      <c r="O248" s="27" t="inlineStr">
+      <c r="N251" s="12" t="inlineStr"/>
+      <c r="O251" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P248" s="12" t="n"/>
-      <c r="Q248" s="12" t="n"/>
-      <c r="R248" s="28" t="n"/>
-      <c r="S248" s="12" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="12" t="inlineStr">
+      <c r="P251" s="12" t="n"/>
+      <c r="Q251" s="12" t="n"/>
+      <c r="R251" s="28" t="n"/>
+      <c r="S251" s="12" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-03</t>
         </is>
       </c>
-      <c r="B249" s="12" t="inlineStr"/>
-      <c r="C249" s="12" t="inlineStr">
+      <c r="B252" s="12" t="inlineStr"/>
+      <c r="C252" s="12" t="inlineStr">
         <is>
           <t>FR-PM-021</t>
         </is>
       </c>
-      <c r="D249" s="12" t="inlineStr">
+      <c r="D252" s="12" t="inlineStr">
         <is>
           <t>BRPM.008, BRPM.021</t>
         </is>
       </c>
-      <c r="E249" s="12" t="inlineStr">
+      <c r="E252" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Request record: stage actions (SCR-PM-04)</t>
         </is>
       </c>
-      <c r="F249" s="12" t="inlineStr">
+      <c r="F252" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G249" s="12" t="inlineStr">
+      <c r="G252" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H249" s="12" t="inlineStr">
+      <c r="H252" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I249" s="12" t="inlineStr">
+      <c r="I252" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-04</t>
         </is>
       </c>
-      <c r="J249" s="12" t="inlineStr">
+      <c r="J252" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K249" s="12" t="inlineStr">
+      <c r="K252" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L249" s="12" t="inlineStr">
+      <c r="L252" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-025: "Package version not found: &lt;product code&gt;" (NOT_FOUND)
@@ -31218,81 +31466,81 @@
 MSG-PM-029: "Write the recommendation for the TSU Head" (PKG_RECOMMENDATION_REQUIRED)
 MSG-PM-030: "Complete the request: &lt;missing&gt;" (PKG_REQUEST_INCOMPLETE)
 MSG-PM-031: "Select the request type and the package scope" (PKG_REQUEST_INCOMPLETE)
-MSG-PM-032: "Request &lt;request no&gt; cannot be changed while &lt;status&gt;" (PKG_REQUEST_NOT_EDITABLE)
+MSG-PM-032: "Request &lt;request no&gt; cannot be changed at the stage &lt;label&gt;" (PKG_REQUEST_NOT_EDITABLE)
 MSG-PM-033: "The type of a request cannot change" (PKG_TYPE_FIXED)</t>
         </is>
       </c>
-      <c r="M249" s="12" t="inlineStr">
+      <c r="M252" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N249" s="12" t="inlineStr"/>
-      <c r="O249" s="27" t="inlineStr">
+      <c r="N252" s="12" t="inlineStr"/>
+      <c r="O252" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P249" s="12" t="n"/>
-      <c r="Q249" s="12" t="n"/>
-      <c r="R249" s="28" t="n"/>
-      <c r="S249" s="12" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="12" t="inlineStr">
+      <c r="P252" s="12" t="n"/>
+      <c r="Q252" s="12" t="n"/>
+      <c r="R252" s="28" t="n"/>
+      <c r="S252" s="12" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-04</t>
         </is>
       </c>
-      <c r="B250" s="12" t="inlineStr"/>
-      <c r="C250" s="12" t="inlineStr">
+      <c r="B253" s="12" t="inlineStr"/>
+      <c r="C253" s="12" t="inlineStr">
         <is>
           <t>FR-PM-030</t>
         </is>
       </c>
-      <c r="D250" s="12" t="inlineStr">
+      <c r="D253" s="12" t="inlineStr">
         <is>
           <t>BRPM.012</t>
         </is>
       </c>
-      <c r="E250" s="12" t="inlineStr">
+      <c r="E253" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Request record: Negotiation tab (SCR-PM-05)</t>
         </is>
       </c>
-      <c r="F250" s="12" t="inlineStr">
+      <c r="F253" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G250" s="12" t="inlineStr">
+      <c r="G253" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H250" s="12" t="inlineStr">
+      <c r="H253" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I250" s="12" t="inlineStr">
+      <c r="I253" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-05</t>
         </is>
       </c>
-      <c r="J250" s="12" t="inlineStr">
+      <c r="J253" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K250" s="12" t="inlineStr">
+      <c r="K253" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L250" s="12" t="inlineStr">
+      <c r="L253" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-036: "Enter the rate offered"
@@ -31304,7 +31552,7 @@
 MSG-PM-046: "Negotiation round not found: &lt;"/latest"&gt;" (NOT_FOUND)
 MSG-PM-047: "Negotiation round not found: &lt;round no&gt;" (NOT_FOUND)
 MSG-PM-048: "Rates and amounts cannot be negative" (PKG_AMOUNT_NEGATIVE)
-MSG-PM-049: "&lt;insurer code&gt; did not offer terms in this round" (PKG_INSURER_NOT_OFFERED)
+MSG-PM-049: "The insurer chosen did not offer terms in this round" (PKG_INSURER_NOT_OFFERED)
 MSG-PM-050: "Unknown role &lt;given&gt;" (PKG_INSURER_ROLE_INVALID)
 MSG-PM-051: "Enter the rate offered by &lt;insurer name&gt; (&lt;outcome&gt;)" (PKG_RESPONSE_RATE_REQUIRED)
 MSG-PM-052: "Round &lt;round no&gt; is closed: key in the latest round" (PKG_ROUND_CLOSED)
@@ -31323,77 +31571,77 @@
 MSG-PM-065: "The file could not be read" (UPLOAD_FAILED)</t>
         </is>
       </c>
-      <c r="M250" s="12" t="inlineStr">
+      <c r="M253" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N250" s="12" t="inlineStr"/>
-      <c r="O250" s="27" t="inlineStr">
+      <c r="N253" s="12" t="inlineStr"/>
+      <c r="O253" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P250" s="12" t="n"/>
-      <c r="Q250" s="12" t="n"/>
-      <c r="R250" s="28" t="n"/>
-      <c r="S250" s="12" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="12" t="inlineStr">
+      <c r="P253" s="12" t="n"/>
+      <c r="Q253" s="12" t="n"/>
+      <c r="R253" s="28" t="n"/>
+      <c r="S253" s="12" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-05</t>
         </is>
       </c>
-      <c r="B251" s="12" t="inlineStr"/>
-      <c r="C251" s="12" t="inlineStr">
+      <c r="B254" s="12" t="inlineStr"/>
+      <c r="C254" s="12" t="inlineStr">
         <is>
           <t>FR-PM-034</t>
         </is>
       </c>
-      <c r="D251" s="12" t="inlineStr">
+      <c r="D254" s="12" t="inlineStr">
         <is>
           <t>BRPM.014, BRPM.013</t>
         </is>
       </c>
-      <c r="E251" s="12" t="inlineStr">
+      <c r="E254" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Request record: Comparative tab (SCR-PM-06)</t>
         </is>
       </c>
-      <c r="F251" s="12" t="inlineStr">
+      <c r="F254" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G251" s="12" t="inlineStr">
+      <c r="G254" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H251" s="12" t="inlineStr">
+      <c r="H254" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I251" s="12" t="inlineStr">
+      <c r="I254" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-06</t>
         </is>
       </c>
-      <c r="J251" s="12" t="inlineStr">
+      <c r="J254" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K251" s="12" t="inlineStr">
+      <c r="K254" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L251" s="12" t="inlineStr">
+      <c r="L254" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-070: "Unknown comparative field(s): &lt;unknown&gt;" (COMPARATIVE_FIELD_UNKNOWN)
@@ -31404,77 +31652,77 @@
 MSG-PM-075: "Comparative output not found: &lt;output id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
-      <c r="M251" s="12" t="inlineStr">
+      <c r="M254" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N251" s="12" t="inlineStr"/>
-      <c r="O251" s="27" t="inlineStr">
+      <c r="N254" s="12" t="inlineStr"/>
+      <c r="O254" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P251" s="12" t="n"/>
-      <c r="Q251" s="12" t="n"/>
-      <c r="R251" s="28" t="n"/>
-      <c r="S251" s="12" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="12" t="inlineStr">
+      <c r="P254" s="12" t="n"/>
+      <c r="Q254" s="12" t="n"/>
+      <c r="R254" s="28" t="n"/>
+      <c r="S254" s="12" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-06</t>
         </is>
       </c>
-      <c r="B252" s="12" t="inlineStr"/>
-      <c r="C252" s="12" t="inlineStr">
+      <c r="B255" s="12" t="inlineStr"/>
+      <c r="C255" s="12" t="inlineStr">
         <is>
           <t>FR-PM-040</t>
         </is>
       </c>
-      <c r="D252" s="12" t="inlineStr">
+      <c r="D255" s="12" t="inlineStr">
         <is>
           <t>BRPM.015</t>
         </is>
       </c>
-      <c r="E252" s="12" t="inlineStr">
+      <c r="E255" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Request record: Requirements &amp; Sign-off tab (SCR-PM-07)</t>
         </is>
       </c>
-      <c r="F252" s="12" t="inlineStr">
+      <c r="F255" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G252" s="12" t="inlineStr">
+      <c r="G255" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H252" s="12" t="inlineStr">
+      <c r="H255" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I252" s="12" t="inlineStr">
+      <c r="I255" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-07</t>
         </is>
       </c>
-      <c r="J252" s="12" t="inlineStr">
+      <c r="J255" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K252" s="12" t="inlineStr">
+      <c r="K255" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L252" s="12" t="inlineStr">
+      <c r="L255" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-078: "The package end date must be after the effective date" (PKG_DATES_INVALID)
@@ -31482,77 +31730,77 @@
 MSG-PM-080: "Complete the requirements: &lt;missing&gt;" (REQUIREMENTS_INCOMPLETE)</t>
         </is>
       </c>
-      <c r="M252" s="12" t="inlineStr">
+      <c r="M255" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N252" s="12" t="inlineStr"/>
-      <c r="O252" s="27" t="inlineStr">
+      <c r="N255" s="12" t="inlineStr"/>
+      <c r="O255" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P252" s="12" t="n"/>
-      <c r="Q252" s="12" t="n"/>
-      <c r="R252" s="28" t="n"/>
-      <c r="S252" s="12" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="12" t="inlineStr">
+      <c r="P255" s="12" t="n"/>
+      <c r="Q255" s="12" t="n"/>
+      <c r="R255" s="28" t="n"/>
+      <c r="S255" s="12" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-07</t>
         </is>
       </c>
-      <c r="B253" s="12" t="inlineStr"/>
-      <c r="C253" s="12" t="inlineStr">
+      <c r="B256" s="12" t="inlineStr"/>
+      <c r="C256" s="12" t="inlineStr">
         <is>
           <t>FR-PM-042</t>
         </is>
       </c>
-      <c r="D253" s="12" t="inlineStr">
+      <c r="D256" s="12" t="inlineStr">
         <is>
           <t>BRPM.015</t>
         </is>
       </c>
-      <c r="E253" s="12" t="inlineStr">
+      <c r="E256" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Request record: Set-up and Advisories tabs (SCR-PM-08)</t>
         </is>
       </c>
-      <c r="F253" s="12" t="inlineStr">
+      <c r="F256" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G253" s="12" t="inlineStr">
+      <c r="G256" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H253" s="12" t="inlineStr">
+      <c r="H256" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Requests › Package Request</t>
         </is>
       </c>
-      <c r="I253" s="12" t="inlineStr">
+      <c r="I256" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-08</t>
         </is>
       </c>
-      <c r="J253" s="12" t="inlineStr">
+      <c r="J256" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K253" s="12" t="inlineStr">
+      <c r="K256" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L253" s="12" t="inlineStr">
+      <c r="L256" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-083: "The advisory was already sent" (ADVISORY_ALREADY_SENT)
@@ -31564,7 +31812,7 @@
 MSG-PM-089: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
 MSG-PM-090: "Insurer &lt;insurer code&gt; has terms but is not on the package" (PACKAGE_TERM_INSURER_UNKNOWN)
 MSG-PM-091: "A retirement request retires the package; it has no version to set up" (PKG_REQUEST_TYPE_MISMATCH)
-MSG-PM-092: "Only a RETIRE request retires the package" (PKG_REQUEST_TYPE_MISMATCH)
+MSG-PM-092: "Only a request to retire the package can retire it" (PKG_REQUEST_TYPE_MISMATCH)
 MSG-PM-093: "Enter the product code" (PRODUCT_CODE_REQUIRED)
 MSG-PM-094: "Enter the risk code of the new package" (PRODUCT_CODE_REQUIRED)
 MSG-PM-095: "Product &lt;product code&gt; is &lt;lifecycle status&gt; already" (PRODUCT_NOT_ACTIVE)
@@ -31574,77 +31822,77 @@
 MSG-PM-099: "The content is for product &lt;product code&gt;" (VERSION_PRODUCT_MISMATCH)</t>
         </is>
       </c>
-      <c r="M253" s="12" t="inlineStr">
+      <c r="M256" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N253" s="12" t="inlineStr"/>
-      <c r="O253" s="27" t="inlineStr">
+      <c r="N256" s="12" t="inlineStr"/>
+      <c r="O256" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P253" s="12" t="n"/>
-      <c r="Q253" s="12" t="n"/>
-      <c r="R253" s="28" t="n"/>
-      <c r="S253" s="12" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="12" t="inlineStr">
+      <c r="P256" s="12" t="n"/>
+      <c r="Q256" s="12" t="n"/>
+      <c r="R256" s="28" t="n"/>
+      <c r="S256" s="12" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-08</t>
         </is>
       </c>
-      <c r="B254" s="12" t="inlineStr"/>
-      <c r="C254" s="12" t="inlineStr">
+      <c r="B257" s="12" t="inlineStr"/>
+      <c r="C257" s="12" t="inlineStr">
         <is>
           <t>FR-PM-060</t>
         </is>
       </c>
-      <c r="D254" s="12" t="inlineStr">
+      <c r="D257" s="12" t="inlineStr">
         <is>
           <t>BRPM.017</t>
         </is>
       </c>
-      <c r="E254" s="12" t="inlineStr">
+      <c r="E257" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Expiry (SCR-PM-10)</t>
         </is>
       </c>
-      <c r="F254" s="12" t="inlineStr">
+      <c r="F257" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G254" s="12" t="inlineStr">
+      <c r="G257" s="12" t="inlineStr">
         <is>
           <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
-      <c r="H254" s="12" t="inlineStr">
+      <c r="H257" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Package Expiry</t>
         </is>
       </c>
-      <c r="I254" s="12" t="inlineStr">
+      <c r="I257" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-10</t>
         </is>
       </c>
-      <c r="J254" s="12" t="inlineStr">
+      <c r="J257" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K254" s="12" t="inlineStr">
+      <c r="K257" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mkttl.
 2. Open Client &amp; Policy › Product Maintenance › Package Expiry.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L254" s="12" t="inlineStr">
+      <c r="L257" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-102: "Select the company" (COMPANY_REQUIRED)
@@ -31652,77 +31900,77 @@
 MSG-PM-104: "Select the packages to renew" (PKG_RENEWAL_NONE)</t>
         </is>
       </c>
-      <c r="M254" s="12" t="inlineStr">
+      <c r="M257" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N254" s="12" t="inlineStr"/>
-      <c r="O254" s="27" t="inlineStr">
+      <c r="N257" s="12" t="inlineStr"/>
+      <c r="O257" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P254" s="12" t="n"/>
-      <c r="Q254" s="12" t="n"/>
-      <c r="R254" s="28" t="n"/>
-      <c r="S254" s="12" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="12" t="inlineStr">
+      <c r="P257" s="12" t="n"/>
+      <c r="Q257" s="12" t="n"/>
+      <c r="R257" s="28" t="n"/>
+      <c r="S257" s="12" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-09</t>
         </is>
       </c>
-      <c r="B255" s="12" t="inlineStr"/>
-      <c r="C255" s="12" t="inlineStr">
+      <c r="B258" s="12" t="inlineStr"/>
+      <c r="C258" s="12" t="inlineStr">
         <is>
           <t>FR-PM-010</t>
         </is>
       </c>
-      <c r="D255" s="12" t="inlineStr">
+      <c r="D258" s="12" t="inlineStr">
         <is>
           <t>PMADD01</t>
         </is>
       </c>
-      <c r="E255" s="12" t="inlineStr">
+      <c r="E258" s="12" t="inlineStr">
         <is>
           <t>Messages of Products and the product dialog (SCR-PM-11)</t>
         </is>
       </c>
-      <c r="F255" s="12" t="inlineStr">
+      <c r="F258" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G255" s="12" t="inlineStr">
+      <c r="G258" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H255" s="12" t="inlineStr">
+      <c r="H258" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Products</t>
         </is>
       </c>
-      <c r="I255" s="12" t="inlineStr">
+      <c r="I258" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-11</t>
         </is>
       </c>
-      <c r="J255" s="12" t="inlineStr">
+      <c r="J258" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K255" s="12" t="inlineStr">
+      <c r="K258" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Products.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L255" s="12" t="inlineStr">
+      <c r="L258" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-107: "The risk-code pattern is not a valid regular expression" (CODE_PATTERN_INVALID)
@@ -31742,77 +31990,77 @@
 MSG-PM-121: "The maximum term must be between 1 and 10 years" (PRODUCT_TERM_INVALID)</t>
         </is>
       </c>
-      <c r="M255" s="12" t="inlineStr">
+      <c r="M258" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N255" s="12" t="inlineStr"/>
-      <c r="O255" s="27" t="inlineStr">
+      <c r="N258" s="12" t="inlineStr"/>
+      <c r="O258" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P255" s="12" t="n"/>
-      <c r="Q255" s="12" t="n"/>
-      <c r="R255" s="28" t="n"/>
-      <c r="S255" s="12" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="12" t="inlineStr">
+      <c r="P258" s="12" t="n"/>
+      <c r="Q258" s="12" t="n"/>
+      <c r="R258" s="28" t="n"/>
+      <c r="S258" s="12" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-10</t>
         </is>
       </c>
-      <c r="B256" s="12" t="inlineStr"/>
-      <c r="C256" s="12" t="inlineStr">
+      <c r="B259" s="12" t="inlineStr"/>
+      <c r="C259" s="12" t="inlineStr">
         <is>
           <t>FR-PM-050</t>
         </is>
       </c>
-      <c r="D256" s="12" t="inlineStr">
+      <c r="D259" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E256" s="12" t="inlineStr">
+      <c r="E259" s="12" t="inlineStr">
         <is>
           <t>Messages of Product record: versions and rules (SCR-PM-12)</t>
         </is>
       </c>
-      <c r="F256" s="12" t="inlineStr">
+      <c r="F259" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G256" s="12" t="inlineStr">
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H256" s="12" t="inlineStr">
+      <c r="H259" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Products › Product</t>
         </is>
       </c>
-      <c r="I256" s="12" t="inlineStr">
+      <c r="I259" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-12</t>
         </is>
       </c>
-      <c r="J256" s="12" t="inlineStr">
+      <c r="J259" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K256" s="12" t="inlineStr">
+      <c r="K259" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Products › Product.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L256" s="12" t="inlineStr">
+      <c r="L259" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-122: "Describe the change"
@@ -31823,77 +32071,77 @@
 MSG-PM-131: "Rules for every product use the scope code '*'" (RULE_SCOPE_INVALID)</t>
         </is>
       </c>
-      <c r="M256" s="12" t="inlineStr">
+      <c r="M259" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N256" s="12" t="inlineStr"/>
-      <c r="O256" s="27" t="inlineStr">
+      <c r="N259" s="12" t="inlineStr"/>
+      <c r="O259" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P256" s="12" t="n"/>
-      <c r="Q256" s="12" t="n"/>
-      <c r="R256" s="28" t="n"/>
-      <c r="S256" s="12" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="12" t="inlineStr">
+      <c r="P259" s="12" t="n"/>
+      <c r="Q259" s="12" t="n"/>
+      <c r="R259" s="28" t="n"/>
+      <c r="S259" s="12" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-11</t>
         </is>
       </c>
-      <c r="B257" s="12" t="inlineStr"/>
-      <c r="C257" s="12" t="inlineStr">
+      <c r="B260" s="12" t="inlineStr"/>
+      <c r="C260" s="12" t="inlineStr">
         <is>
           <t>FR-PM-043</t>
         </is>
       </c>
-      <c r="D257" s="12" t="inlineStr">
+      <c r="D260" s="12" t="inlineStr">
         <is>
           <t>PMADD06, BRPM.015</t>
         </is>
       </c>
-      <c r="E257" s="12" t="inlineStr">
+      <c r="E260" s="12" t="inlineStr">
         <is>
           <t>Messages of Package Version (SCR-PM-13)</t>
         </is>
       </c>
-      <c r="F257" s="12" t="inlineStr">
+      <c r="F260" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G257" s="12" t="inlineStr">
+      <c r="G260" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H257" s="12" t="inlineStr">
+      <c r="H260" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Product › Package Version</t>
         </is>
       </c>
-      <c r="I257" s="12" t="inlineStr">
+      <c r="I260" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-13</t>
         </is>
       </c>
-      <c r="J257" s="12" t="inlineStr">
+      <c r="J260" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K257" s="12" t="inlineStr">
+      <c r="K260" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Product › Package Version.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L257" s="12" t="inlineStr">
+      <c r="L260" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-133: "Correct the highlighted fields"
@@ -31921,77 +32169,77 @@
 MSG-PM-159: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
         </is>
       </c>
-      <c r="M257" s="12" t="inlineStr">
+      <c r="M260" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N257" s="12" t="inlineStr"/>
-      <c r="O257" s="27" t="inlineStr">
+      <c r="N260" s="12" t="inlineStr"/>
+      <c r="O260" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P257" s="12" t="n"/>
-      <c r="Q257" s="12" t="n"/>
-      <c r="R257" s="28" t="n"/>
-      <c r="S257" s="12" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="12" t="inlineStr">
+      <c r="P260" s="12" t="n"/>
+      <c r="Q260" s="12" t="n"/>
+      <c r="R260" s="28" t="n"/>
+      <c r="S260" s="12" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-12</t>
         </is>
       </c>
-      <c r="B258" s="12" t="inlineStr"/>
-      <c r="C258" s="12" t="inlineStr">
+      <c r="B261" s="12" t="inlineStr"/>
+      <c r="C261" s="12" t="inlineStr">
         <is>
           <t>FR-PM-010</t>
         </is>
       </c>
-      <c r="D258" s="12" t="inlineStr">
+      <c r="D261" s="12" t="inlineStr">
         <is>
           <t>PMADD01</t>
         </is>
       </c>
-      <c r="E258" s="12" t="inlineStr">
+      <c r="E261" s="12" t="inlineStr">
         <is>
           <t>Messages of Coverages &amp; Clauses (SCR-PM-15)</t>
         </is>
       </c>
-      <c r="F258" s="12" t="inlineStr">
+      <c r="F261" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G258" s="12" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H258" s="12" t="inlineStr">
+      <c r="H261" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Coverages &amp; Clauses</t>
         </is>
       </c>
-      <c r="I258" s="12" t="inlineStr">
+      <c r="I261" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-15</t>
         </is>
       </c>
-      <c r="J258" s="12" t="inlineStr">
+      <c r="J261" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K258" s="12" t="inlineStr">
+      <c r="K261" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Coverages &amp; Clauses.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L258" s="12" t="inlineStr">
+      <c r="L261" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-162: "Enter the effective date"
@@ -32007,77 +32255,77 @@
 MSG-PM-174: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
-      <c r="M258" s="12" t="inlineStr">
+      <c r="M261" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N258" s="12" t="inlineStr"/>
-      <c r="O258" s="27" t="inlineStr">
+      <c r="N261" s="12" t="inlineStr"/>
+      <c r="O261" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P258" s="12" t="n"/>
-      <c r="Q258" s="12" t="n"/>
-      <c r="R258" s="28" t="n"/>
-      <c r="S258" s="12" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="12" t="inlineStr">
+      <c r="P261" s="12" t="n"/>
+      <c r="Q261" s="12" t="n"/>
+      <c r="R261" s="28" t="n"/>
+      <c r="S261" s="12" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-13</t>
         </is>
       </c>
-      <c r="B259" s="12" t="inlineStr"/>
-      <c r="C259" s="12" t="inlineStr">
+      <c r="B262" s="12" t="inlineStr"/>
+      <c r="C262" s="12" t="inlineStr">
         <is>
           <t>FR-PM-080</t>
         </is>
       </c>
-      <c r="D259" s="12" t="inlineStr">
+      <c r="D262" s="12" t="inlineStr">
         <is>
           <t>PMADD07, PMADD08</t>
         </is>
       </c>
-      <c r="E259" s="12" t="inlineStr">
+      <c r="E262" s="12" t="inlineStr">
         <is>
           <t>Messages of Incentive Criteria (SCR-PM-16)</t>
         </is>
       </c>
-      <c r="F259" s="12" t="inlineStr">
+      <c r="F262" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G259" s="12" t="inlineStr">
+      <c r="G262" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H259" s="12" t="inlineStr">
+      <c r="H262" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Incentive Criteria</t>
         </is>
       </c>
-      <c r="I259" s="12" t="inlineStr">
+      <c r="I262" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-16</t>
         </is>
       </c>
-      <c r="J259" s="12" t="inlineStr">
+      <c r="J262" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K259" s="12" t="inlineStr">
+      <c r="K262" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Incentive Criteria.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L259" s="12" t="inlineStr">
+      <c r="L262" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-177: "Enter the name"
@@ -32100,77 +32348,77 @@
 MSG-PM-194: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
-      <c r="M259" s="12" t="inlineStr">
+      <c r="M262" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N259" s="12" t="inlineStr"/>
-      <c r="O259" s="27" t="inlineStr">
+      <c r="N262" s="12" t="inlineStr"/>
+      <c r="O262" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P259" s="12" t="n"/>
-      <c r="Q259" s="12" t="n"/>
-      <c r="R259" s="28" t="n"/>
-      <c r="S259" s="12" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="12" t="inlineStr">
+      <c r="P262" s="12" t="n"/>
+      <c r="Q262" s="12" t="n"/>
+      <c r="R262" s="28" t="n"/>
+      <c r="S262" s="12" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-14</t>
         </is>
       </c>
-      <c r="B260" s="12" t="inlineStr"/>
-      <c r="C260" s="12" t="inlineStr">
+      <c r="B263" s="12" t="inlineStr"/>
+      <c r="C263" s="12" t="inlineStr">
         <is>
           <t>FR-PM-014</t>
         </is>
       </c>
-      <c r="D260" s="12" t="inlineStr">
+      <c r="D263" s="12" t="inlineStr">
         <is>
           <t>PMADD02</t>
         </is>
       </c>
-      <c r="E260" s="12" t="inlineStr">
+      <c r="E263" s="12" t="inlineStr">
         <is>
           <t>Messages of Insurers (SCR-PM-17)</t>
         </is>
       </c>
-      <c r="F260" s="12" t="inlineStr">
+      <c r="F263" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G260" s="12" t="inlineStr">
+      <c r="G263" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H260" s="12" t="inlineStr">
+      <c r="H263" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Insurers</t>
         </is>
       </c>
-      <c r="I260" s="12" t="inlineStr">
+      <c r="I263" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-17</t>
         </is>
       </c>
-      <c r="J260" s="12" t="inlineStr">
+      <c r="J263" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K260" s="12" t="inlineStr">
+      <c r="K263" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Insurers.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L260" s="12" t="inlineStr">
+      <c r="L263" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-197: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
@@ -32186,77 +32434,77 @@
 MSG-PM-207: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
         </is>
       </c>
-      <c r="M260" s="12" t="inlineStr">
+      <c r="M263" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N260" s="12" t="inlineStr"/>
-      <c r="O260" s="27" t="inlineStr">
+      <c r="N263" s="12" t="inlineStr"/>
+      <c r="O263" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P260" s="12" t="n"/>
-      <c r="Q260" s="12" t="n"/>
-      <c r="R260" s="28" t="n"/>
-      <c r="S260" s="12" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="12" t="inlineStr">
+      <c r="P263" s="12" t="n"/>
+      <c r="Q263" s="12" t="n"/>
+      <c r="R263" s="28" t="n"/>
+      <c r="S263" s="12" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-15</t>
         </is>
       </c>
-      <c r="B261" s="12" t="inlineStr"/>
-      <c r="C261" s="12" t="inlineStr">
+      <c r="B264" s="12" t="inlineStr"/>
+      <c r="C264" s="12" t="inlineStr">
         <is>
           <t>FR-PM-051</t>
         </is>
       </c>
-      <c r="D261" s="12" t="inlineStr">
+      <c r="D264" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E261" s="12" t="inlineStr">
+      <c r="E264" s="12" t="inlineStr">
         <is>
           <t>Messages of Rates &amp; Taxes (SCR-PM-19)</t>
         </is>
       </c>
-      <c r="F261" s="12" t="inlineStr">
+      <c r="F264" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G261" s="12" t="inlineStr">
+      <c r="G264" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H261" s="12" t="inlineStr">
+      <c r="H264" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Rates &amp; Taxes</t>
         </is>
       </c>
-      <c r="I261" s="12" t="inlineStr">
+      <c r="I264" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-19</t>
         </is>
       </c>
-      <c r="J261" s="12" t="inlineStr">
+      <c r="J264" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K261" s="12" t="inlineStr">
+      <c r="K264" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Rates &amp; Taxes.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L261" s="12" t="inlineStr">
+      <c r="L264" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-211: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
@@ -32268,69 +32516,69 @@
 MSG-PM-217: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
         </is>
       </c>
-      <c r="M261" s="12" t="inlineStr">
+      <c r="M264" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N261" s="12" t="inlineStr"/>
-      <c r="O261" s="27" t="inlineStr">
+      <c r="N264" s="12" t="inlineStr"/>
+      <c r="O264" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P261" s="12" t="n"/>
-      <c r="Q261" s="12" t="n"/>
-      <c r="R261" s="28" t="n"/>
-      <c r="S261" s="12" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="12" t="inlineStr">
+      <c r="P264" s="12" t="n"/>
+      <c r="Q264" s="12" t="n"/>
+      <c r="R264" s="28" t="n"/>
+      <c r="S264" s="12" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-16</t>
         </is>
       </c>
-      <c r="B262" s="12" t="inlineStr"/>
-      <c r="C262" s="12" t="inlineStr"/>
-      <c r="D262" s="12" t="inlineStr"/>
-      <c r="E262" s="12" t="inlineStr">
+      <c r="B265" s="12" t="inlineStr"/>
+      <c r="C265" s="12" t="inlineStr"/>
+      <c r="D265" s="12" t="inlineStr"/>
+      <c r="E265" s="12" t="inlineStr">
         <is>
           <t>Messages of Sales Organisation (SCR-PM-20)</t>
         </is>
       </c>
-      <c r="F262" s="12" t="inlineStr">
+      <c r="F265" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G262" s="12" t="inlineStr">
+      <c r="G265" s="12" t="inlineStr">
         <is>
           <t>MBS – Marketing Business Services (SIT/UAT user mbs)</t>
         </is>
       </c>
-      <c r="H262" s="12" t="inlineStr">
+      <c r="H265" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Sales Organisation</t>
         </is>
       </c>
-      <c r="I262" s="12" t="inlineStr">
+      <c r="I265" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-20</t>
         </is>
       </c>
-      <c r="J262" s="12" t="inlineStr">
+      <c r="J265" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K262" s="12" t="inlineStr">
+      <c r="K265" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as mbs.
 2. Open Client &amp; Policy › Product Maintenance › Sales Organisation.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L262" s="12" t="inlineStr">
+      <c r="L265" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-219: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
@@ -32342,77 +32590,77 @@
 MSG-PM-225: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
         </is>
       </c>
-      <c r="M262" s="12" t="inlineStr">
+      <c r="M265" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N262" s="12" t="inlineStr"/>
-      <c r="O262" s="27" t="inlineStr">
+      <c r="N265" s="12" t="inlineStr"/>
+      <c r="O265" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="P262" s="12" t="n"/>
-      <c r="Q262" s="12" t="n"/>
-      <c r="R262" s="28" t="n"/>
-      <c r="S262" s="12" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="12" t="inlineStr">
+      <c r="P265" s="12" t="n"/>
+      <c r="Q265" s="12" t="n"/>
+      <c r="R265" s="28" t="n"/>
+      <c r="S265" s="12" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="12" t="inlineStr">
         <is>
           <t>TC-PM-MSG-17</t>
         </is>
       </c>
-      <c r="B263" s="12" t="inlineStr"/>
-      <c r="C263" s="12" t="inlineStr">
+      <c r="B266" s="12" t="inlineStr"/>
+      <c r="C266" s="12" t="inlineStr">
         <is>
           <t>FR-PM-051</t>
         </is>
       </c>
-      <c r="D263" s="12" t="inlineStr">
+      <c r="D266" s="12" t="inlineStr">
         <is>
           <t>BRPM.007</t>
         </is>
       </c>
-      <c r="E263" s="12" t="inlineStr">
+      <c r="E266" s="12" t="inlineStr">
         <is>
           <t>Messages of Premium Calculator (SCR-PM-21); pricing of quotations and accounts</t>
         </is>
       </c>
-      <c r="F263" s="12" t="inlineStr">
+      <c r="F266" s="12" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="G263" s="12" t="inlineStr">
+      <c r="G266" s="12" t="inlineStr">
         <is>
           <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
-      <c r="H263" s="12" t="inlineStr">
+      <c r="H266" s="12" t="inlineStr">
         <is>
           <t>Client &amp; Policy › Product Maintenance › Premium Calculator</t>
         </is>
       </c>
-      <c r="I263" s="12" t="inlineStr">
+      <c r="I266" s="12" t="inlineStr">
         <is>
           <t>SCR-PM-21</t>
         </is>
       </c>
-      <c r="J263" s="12" t="inlineStr">
+      <c r="J266" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
         </is>
       </c>
-      <c r="K263" s="12" t="inlineStr">
+      <c r="K266" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
 2. Open Client &amp; Policy › Product Maintenance › Premium Calculator.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
-      <c r="L263" s="12" t="inlineStr">
+      <c r="L266" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-226: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
@@ -32429,223 +32677,6 @@
 MSG-PM-237: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
-      <c r="M263" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N263" s="12" t="inlineStr"/>
-      <c r="O263" s="27" t="inlineStr">
-        <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="P263" s="12" t="n"/>
-      <c r="Q263" s="12" t="n"/>
-      <c r="R263" s="28" t="n"/>
-      <c r="S263" s="12" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="12" t="inlineStr">
-        <is>
-          <t>TC-PM-MSG-18</t>
-        </is>
-      </c>
-      <c r="B264" s="12" t="inlineStr"/>
-      <c r="C264" s="12" t="inlineStr">
-        <is>
-          <t>FR-PM-051</t>
-        </is>
-      </c>
-      <c r="D264" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.007</t>
-        </is>
-      </c>
-      <c r="E264" s="12" t="inlineStr">
-        <is>
-          <t>Messages of Quotation: package rate scheme and rate exception (SCR-PM-22)</t>
-        </is>
-      </c>
-      <c r="F264" s="12" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="G264" s="12" t="inlineStr">
-        <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
-        </is>
-      </c>
-      <c r="H264" s="12" t="inlineStr">
-        <is>
-          <t>Client &amp; Policy › Quotation / Proposal › Quotations › Quotation</t>
-        </is>
-      </c>
-      <c r="I264" s="12" t="inlineStr">
-        <is>
-          <t>SCR-PM-22</t>
-        </is>
-      </c>
-      <c r="J264" s="12" t="inlineStr">
-        <is>
-          <t>Seed data of the SIT environment.</t>
-        </is>
-      </c>
-      <c r="K264" s="12" t="inlineStr">
-        <is>
-          <t>1. Sign in as ao.
-2. Open Client &amp; Policy › Quotation / Proposal › Quotations › Quotation.
-3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
-        </is>
-      </c>
-      <c r="L264" s="12" t="inlineStr">
-        <is>
-          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-238: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
-MSG-PM-239: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
-MSG-PM-240: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
-MSG-PM-241: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
-MSG-PM-242: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-243: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)</t>
-        </is>
-      </c>
-      <c r="M264" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N264" s="12" t="inlineStr"/>
-      <c r="O264" s="27" t="inlineStr">
-        <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="P264" s="12" t="n"/>
-      <c r="Q264" s="12" t="n"/>
-      <c r="R264" s="28" t="n"/>
-      <c r="S264" s="12" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="12" t="inlineStr">
-        <is>
-          <t>TC-PM-MSG-19</t>
-        </is>
-      </c>
-      <c r="B265" s="12" t="inlineStr"/>
-      <c r="C265" s="12" t="inlineStr"/>
-      <c r="D265" s="12" t="inlineStr"/>
-      <c r="E265" s="12" t="inlineStr">
-        <is>
-          <t>Messages of Authorize and Deactivate on every product master (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="F265" s="12" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="G265" s="12" t="inlineStr">
-        <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
-        </is>
-      </c>
-      <c r="H265" s="12" t="inlineStr">
-        <is>
-          <t>Any Product Maintenance record</t>
-        </is>
-      </c>
-      <c r="I265" s="12" t="inlineStr"/>
-      <c r="J265" s="12" t="inlineStr">
-        <is>
-          <t>Seed data of the SIT environment.</t>
-        </is>
-      </c>
-      <c r="K265" s="12" t="inlineStr">
-        <is>
-          <t>1. Sign in as ao.
-2. Open Any Product Maintenance record.
-3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
-        </is>
-      </c>
-      <c r="L265" s="12" t="inlineStr">
-        <is>
-          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-244: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="M265" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N265" s="12" t="inlineStr"/>
-      <c r="O265" s="27" t="inlineStr">
-        <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="P265" s="12" t="n"/>
-      <c r="Q265" s="12" t="n"/>
-      <c r="R265" s="28" t="n"/>
-      <c r="S265" s="12" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="12" t="inlineStr">
-        <is>
-          <t>TC-PM-MSG-20</t>
-        </is>
-      </c>
-      <c r="B266" s="12" t="inlineStr"/>
-      <c r="C266" s="12" t="inlineStr"/>
-      <c r="D266" s="12" t="inlineStr"/>
-      <c r="E266" s="12" t="inlineStr">
-        <is>
-          <t>Messages of Every screen (Common screen elements)</t>
-        </is>
-      </c>
-      <c r="F266" s="12" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="G266" s="12" t="inlineStr">
-        <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
-        </is>
-      </c>
-      <c r="H266" s="12" t="inlineStr">
-        <is>
-          <t>Any Product Maintenance record</t>
-        </is>
-      </c>
-      <c r="I266" s="12" t="inlineStr"/>
-      <c r="J266" s="12" t="inlineStr">
-        <is>
-          <t>Seed data of the SIT environment.</t>
-        </is>
-      </c>
-      <c r="K266" s="12" t="inlineStr">
-        <is>
-          <t>1. Sign in as ao.
-2. Open Any Product Maintenance record.
-3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
-        </is>
-      </c>
-      <c r="L266" s="12" t="inlineStr">
-        <is>
-          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-245: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-PM-246: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-PM-248: "An unexpected error occurred. Quote reference &lt;reference&gt; to support." (INTERNAL_ERROR)
-MSG-PM-249: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-PM-250: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-PM-251: "The request body is not valid JSON or has fields of the wrong type" (MALFORMED_REQUEST)
-MSG-PM-253: "No such endpoint: &lt;resource path&gt;" (NOT_FOUND)
-MSG-PM-254: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-PM-255: "Invalid request" (VALIDATION_FAILED)</t>
-        </is>
-      </c>
       <c r="M266" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -32665,15 +32696,23 @@
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-MSG-21</t>
+          <t>TC-PM-MSG-18</t>
         </is>
       </c>
       <c r="B267" s="12" t="inlineStr"/>
-      <c r="C267" s="12" t="inlineStr"/>
-      <c r="D267" s="12" t="inlineStr"/>
+      <c r="C267" s="12" t="inlineStr">
+        <is>
+          <t>FR-PM-051</t>
+        </is>
+      </c>
+      <c r="D267" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.007</t>
+        </is>
+      </c>
       <c r="E267" s="12" t="inlineStr">
         <is>
-          <t>Messages of Several screens</t>
+          <t>Messages of Quotation: package rate scheme and rate exception (SCR-PM-22)</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
@@ -32688,10 +32727,14 @@
       </c>
       <c r="H267" s="12" t="inlineStr">
         <is>
-          <t>Any Product Maintenance record</t>
-        </is>
-      </c>
-      <c r="I267" s="12" t="inlineStr"/>
+          <t>Client &amp; Policy › Quotation / Proposal › Quotations › Quotation</t>
+        </is>
+      </c>
+      <c r="I267" s="12" t="inlineStr">
+        <is>
+          <t>SCR-PM-22</t>
+        </is>
+      </c>
       <c r="J267" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
@@ -32700,15 +32743,21 @@
       <c r="K267" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
-2. Open Any Product Maintenance record.
+2. Open Client &amp; Policy › Quotation / Proposal › Quotations › Quotation.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
       <c r="L267" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-247: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-252: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-239: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-240: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
+MSG-PM-241: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
+MSG-PM-242: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
+MSG-PM-243: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
+MSG-PM-244: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-245: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-246: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="M267" s="12" t="inlineStr">
@@ -32727,12 +32776,216 @@
       <c r="R267" s="28" t="n"/>
       <c r="S267" s="12" t="n"/>
     </row>
+    <row r="268">
+      <c r="A268" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-MSG-19</t>
+        </is>
+      </c>
+      <c r="B268" s="12" t="inlineStr"/>
+      <c r="C268" s="12" t="inlineStr"/>
+      <c r="D268" s="12" t="inlineStr"/>
+      <c r="E268" s="12" t="inlineStr">
+        <is>
+          <t>Messages of Authorize and Deactivate on every product master (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="F268" s="12" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="G268" s="12" t="inlineStr">
+        <is>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+        </is>
+      </c>
+      <c r="H268" s="12" t="inlineStr">
+        <is>
+          <t>Any Product Maintenance record</t>
+        </is>
+      </c>
+      <c r="I268" s="12" t="inlineStr"/>
+      <c r="J268" s="12" t="inlineStr">
+        <is>
+          <t>Seed data of the SIT environment.</t>
+        </is>
+      </c>
+      <c r="K268" s="12" t="inlineStr">
+        <is>
+          <t>1. Sign in as ao.
+2. Open Any Product Maintenance record.
+3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
+        </is>
+      </c>
+      <c r="L268" s="12" t="inlineStr">
+        <is>
+          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
+MSG-PM-247: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="M268" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N268" s="12" t="inlineStr"/>
+      <c r="O268" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P268" s="12" t="n"/>
+      <c r="Q268" s="12" t="n"/>
+      <c r="R268" s="28" t="n"/>
+      <c r="S268" s="12" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-MSG-20</t>
+        </is>
+      </c>
+      <c r="B269" s="12" t="inlineStr"/>
+      <c r="C269" s="12" t="inlineStr"/>
+      <c r="D269" s="12" t="inlineStr"/>
+      <c r="E269" s="12" t="inlineStr">
+        <is>
+          <t>Messages of Every screen (Common screen elements)</t>
+        </is>
+      </c>
+      <c r="F269" s="12" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="G269" s="12" t="inlineStr">
+        <is>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+        </is>
+      </c>
+      <c r="H269" s="12" t="inlineStr">
+        <is>
+          <t>Any Product Maintenance record</t>
+        </is>
+      </c>
+      <c r="I269" s="12" t="inlineStr"/>
+      <c r="J269" s="12" t="inlineStr">
+        <is>
+          <t>Seed data of the SIT environment.</t>
+        </is>
+      </c>
+      <c r="K269" s="12" t="inlineStr">
+        <is>
+          <t>1. Sign in as ao.
+2. Open Any Product Maintenance record.
+3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
+        </is>
+      </c>
+      <c r="L269" s="12" t="inlineStr">
+        <is>
+          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
+MSG-PM-248: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-PM-249: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-PM-251: "An unexpected error occurred. Quote reference &lt;reference&gt; to support." (INTERNAL_ERROR)
+MSG-PM-253: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-PM-254: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-PM-255: "The request body is not valid JSON or has fields of the wrong type" (MALFORMED_REQUEST)
+MSG-PM-257: "No such endpoint: &lt;resource path&gt;" (NOT_FOUND)
+MSG-PM-260: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-PM-261: "Invalid request" (VALIDATION_FAILED)</t>
+        </is>
+      </c>
+      <c r="M269" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N269" s="12" t="inlineStr"/>
+      <c r="O269" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P269" s="12" t="n"/>
+      <c r="Q269" s="12" t="n"/>
+      <c r="R269" s="28" t="n"/>
+      <c r="S269" s="12" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-MSG-21</t>
+        </is>
+      </c>
+      <c r="B270" s="12" t="inlineStr"/>
+      <c r="C270" s="12" t="inlineStr"/>
+      <c r="D270" s="12" t="inlineStr"/>
+      <c r="E270" s="12" t="inlineStr">
+        <is>
+          <t>Messages of Several screens</t>
+        </is>
+      </c>
+      <c r="F270" s="12" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="G270" s="12" t="inlineStr">
+        <is>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+        </is>
+      </c>
+      <c r="H270" s="12" t="inlineStr">
+        <is>
+          <t>Any Product Maintenance record</t>
+        </is>
+      </c>
+      <c r="I270" s="12" t="inlineStr"/>
+      <c r="J270" s="12" t="inlineStr">
+        <is>
+          <t>Seed data of the SIT environment.</t>
+        </is>
+      </c>
+      <c r="K270" s="12" t="inlineStr">
+        <is>
+          <t>1. Sign in as ao.
+2. Open Any Product Maintenance record.
+3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
+        </is>
+      </c>
+      <c r="L270" s="12" t="inlineStr">
+        <is>
+          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
+MSG-PM-250: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-252: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-256: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-258: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
+MSG-PM-259: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
+        </is>
+      </c>
+      <c r="M270" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N270" s="12" t="inlineStr"/>
+      <c r="O270" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P270" s="12" t="n"/>
+      <c r="Q270" s="12" t="n"/>
+      <c r="R270" s="28" t="n"/>
+      <c r="S270" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:S267"/>
+  <autoFilter ref="A4:S270"/>
   <mergeCells count="1">
     <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O767">
+  <conditionalFormatting sqref="O5:O770">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -32746,19 +32999,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:S767">
+  <conditionalFormatting sqref="A5:S770">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="F5:F767" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
+    <dataValidation sqref="F5:F770" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
       <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M767" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="M5:M770" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O767" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="O5:O770" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -34118,16 +34371,16 @@
         <v>4</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J34" s="27" t="inlineStr">
         <is>
@@ -34762,16 +35015,16 @@
         <v>8</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J50" s="27" t="inlineStr">
         <is>
@@ -36331,11 +36584,11 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-010.4-01, TC-PM-010.4-02, TC-PM-012.1-01, TC-PM-012.2-01, TC-PM-012.3-01, TC-PM-014.3-01, TC-PM-043.2-02, TC-PM-045.2-01, TC-PM-051.1-01, TC-PM-051.2-01, TC-PM-051.2-02, TC-PM-051.2-03, TC-PM-051.4-01, TC-PM-052.1-02, TC-PM-080.1-02, TC-PM-SCR-22, TC-PM-MSG-18</t>
+          <t>TC-PM-010.4-01, TC-PM-010.4-02, TC-PM-012.1-01, TC-PM-012.2-01, TC-PM-012.3-01, TC-PM-014.3-01, TC-PM-043.2-02, TC-PM-045.2-01, TC-PM-051.1-01, TC-PM-051.2-01, TC-PM-051.2-02, TC-PM-051.2-03, TC-PM-051.2-04, TC-PM-051.2-05, TC-PM-051.2-06, TC-PM-051.4-01, TC-PM-052.1-02, TC-PM-080.1-02, TC-PM-SCR-22, TC-PM-MSG-18</t>
         </is>
       </c>
     </row>
@@ -36774,7 +37027,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -11669,7 +11669,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr"/>
@@ -12886,12 +12886,12 @@
       <c r="K29" s="12" t="inlineStr">
         <is>
           <t>1. Log in as admin; open Administration &gt; Audit Trail and look for edit or delete actions on a row.
-2. Ask the DBA in the test environment to run an UPDATE and a DELETE on the audit table.</t>
+2. Ask the infrastructure administrator of the test environment to try to change, delete and clear audit entries directly.</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>The screen has no edit or delete action. The database refuses the UPDATE, DELETE and TRUNCATE.</t>
+          <t>The screen has no edit or delete action. Every attempt outside the screen is refused and the audit entries are unchanged.</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr"/>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr"/>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr"/>
@@ -20785,7 +20785,7 @@
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I132" s="12" t="inlineStr"/>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr"/>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I144" s="12" t="inlineStr"/>
@@ -22850,7 +22850,7 @@
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr"/>
@@ -23614,7 +23614,7 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr"/>
@@ -24683,7 +24683,7 @@
       </c>
       <c r="H183" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I183" s="12" t="inlineStr"/>
@@ -25134,7 +25134,7 @@
       </c>
       <c r="H189" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I189" s="12" t="inlineStr"/>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="J195" s="12" t="inlineStr">
         <is>
-          <t>A request enters FOR_MKT_APPROVAL (SLA 24 hours); the test waits 19 hours 12 minutes, or the stage entry time is moved in the test database.
+          <t>A request enters FOR_MKT_APPROVAL (SLA 24 hours); the test waits 19 hours 12 minutes, or the stage entry time is moved in the test environment.
 Data: TD-PM-02 Draft NEW generic request; TD-PM-03 AMEND request in TSU review; TD-PM-04 Client-specific request in negotiation; TD-PM-10 Package ending in 45 days</t>
         </is>
       </c>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="H198" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I198" s="12" t="inlineStr"/>
@@ -26537,7 +26537,7 @@
       </c>
       <c r="H208" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I208" s="12" t="inlineStr"/>
@@ -26610,7 +26610,7 @@
       </c>
       <c r="H209" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I209" s="12" t="inlineStr"/>
@@ -26755,7 +26755,7 @@
       </c>
       <c r="H211" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I211" s="12" t="inlineStr"/>
@@ -27270,7 +27270,7 @@
       </c>
       <c r="E218" s="12" t="inlineStr">
         <is>
-          <t>Rule parameters not valid JSON</t>
+          <t>Rule parameters not in the format of the example</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -10343,7 +10343,7 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>A criterion on an inactive product, without products or value, with invalid rule parameters or an overlapping period cannot be saved.</t>
+          <t>A criterion on an inactive product, without products or value, with a rule parameter without a valid value or an overlapping period cannot be saved.</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="E218" s="12" t="inlineStr">
         <is>
-          <t>Rule parameters not in the format of the example</t>
+          <t>Rule parameter value that is not a number</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
@@ -27300,13 +27300,13 @@
       </c>
       <c r="K218" s="12" t="inlineStr">
         <is>
-          <t>1. Value basis Rule, rule parameters "{minimumPremium 5000"; save.</t>
+          <t>1. Value basis Rule; Add Parameter, parameter Minimum Gross Premium, value "five thousand"; save.</t>
         </is>
       </c>
       <c r="L218" s="12" t="inlineStr">
         <is>
-          <t>Not saved.
-Message "The rule parameters must be valid JSON" (INCENTIVE_RULE_PARAMS_INVALID).</t>
+          <t>Not saved; the message is under the value.
+Message "Minimum Gross Premium must be a number" (INCENTIVE_RULE_PARAMS_INVALID).</t>
         </is>
       </c>
       <c r="M218" s="12" t="inlineStr">
@@ -28997,7 +28997,7 @@
       <c r="L240" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-13 Package Version of the FRS.
-Fields in this order: 1 Product / Version (Reference chip, mandatory -); 2 Version status pill (Pill, mandatory -); 3 Request tag (Tag, mandatory -); 4 Effective / Package End / Rate % / Set Up By / ManCom Ref. (Fact, mandatory -); 5 Package Rate % (Number, mandatory Cond.: or a rate for every insurer); 6 Minimum Premium (Number, mandatory Y); 7 Commission % (Number, mandatory Y); 8 Package TSI Limit (Number, mandatory N); 9 Effective From (Date, mandatory Y); 10 Package Start (Date, mandatory N); 11 Package End (Date, mandatory N); 12 Anniversary (Date, mandatory N); 13 Change Summary (Text, mandatory N); 14 ManCom Sign-off Reference (Text, mandatory N); 15 Computation Basis (Text, mandatory N); 16 Coverage (Column, mandatory Y (at least one included)); 17 Included / Optional (Check box, mandatory N); 18 Limit / Deductible (Number, mandatory N); 19 Add coverage (Drop-down, mandatory N); 20 Insurer (Column, mandatory N); 21 Role (Drop-down, mandatory Y); 22 Share % (Number, mandatory Cond.: lead and participants); 23 Rate % (Number, mandatory Cond.: when there is no package rate); 24 Minimum Premium (Number, mandatory N); 25 Add insurer (Drop-down, mandatory N); 26 Insurer / Coverage (Column, mandatory Y (every pair)); 27 Covered (Check box, mandatory N); 28 Limit / Deductible / Deductible Wording (Number / Text, mandatory N); 29 Clauses (Multi-select, mandatory N); 30 Hierarchy complete: cover type and basic coverage / Every panel insurer has terms for each included coverage / Rates and minimum premiums match the signed-off terms / Dates and package term are correct / Test premium reviewed (Check box, mandatory Y (all five)); 31 Validated by, date and test premium (Detail, mandatory -); 32 Return reason / Comment (Drop-down / Text, mandatory Y (reason)).
+Fields in this order: 1 Product / Version (Reference chip, mandatory -); 2 Version status pill (Pill, mandatory -); 3 Effective / Package End / Rate % / Set Up By / ManCom Ref. (Fact, mandatory -); 4 Package Request (Fact, mandatory -); 5 Package Rate % (Number, mandatory Cond.: or a rate for every insurer); 6 Minimum Premium (Number, mandatory Y); 7 Commission % (Number, mandatory Y); 8 Package TSI Limit (Number, mandatory N); 9 Effective From (Date, mandatory Y); 10 Package Start (Date, mandatory N); 11 Package End (Date, mandatory N); 12 Anniversary (Date, mandatory N); 13 Change Summary (Text, mandatory N); 14 ManCom Sign-off Reference (Text, mandatory N); 15 Computation Basis (Text, mandatory N); 16 Coverage (Column, mandatory Y (at least one included)); 17 Included / Optional (Check box, mandatory N); 18 Limit / Deductible (Number, mandatory N); 19 Add coverage (Drop-down, mandatory N); 20 Insurer (Column, mandatory N); 21 Role (Drop-down, mandatory Y); 22 Share % (Number, mandatory Cond.: lead and participants); 23 Rate % (Number, mandatory Cond.: when there is no package rate); 24 Minimum Premium (Number, mandatory N); 25 Add insurer (Drop-down, mandatory N); 26 Insurer / Coverage (Column, mandatory Y (every pair)); 27 Covered (Check box, mandatory N); 28 Limit / Deductible / Deductible Wording (Number / Text, mandatory N); 29 Clauses (Multi-select, mandatory N); 30 Hierarchy complete: cover type and basic coverage / Every panel insurer has terms for each included coverage / Rates and minimum premiums match the signed-off terms / Dates and package term are correct / Test premium reviewed (Check box, mandatory Y (all five)); 31 Result / Validated By / Validated On / Test Premium / Return Reason (Fact, mandatory -); 32 # / Check / Result / Details (Table, mandatory -); 33 Return reason / Comment (Drop-down / Text, mandatory Y (reason)).
 Actions: Save Draft; Submit for Validation; Validate and Release; Return to MBS.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -29234,7 +29234,7 @@
       <c r="L243" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-16 Incentive Criteria of the FRS.
-Fields in this order: 1 Current / Pending Authorization / History (Tab, mandatory -); 2 Search Criterion or Product (Text, mandatory N); 3 Code / Name / Type / Value / Products / From / Until / Status (Column, mandatory -); 4 Code (Text, mandatory Y); 5 Name (Text, mandatory Y); 6 Incentive type (Drop-down, mandatory Y); 7 Value basis (Drop-down, mandatory Y); 8 Value (Number, mandatory Cond.: rate or fixed amount); 9 Effective from (Date, mandatory Y); 10 Effective to (Date, mandatory N); 11 Rule parameters (JSON) (Text, mandatory N); 12 Description (Text, mandatory N); 13 Products matrix (Drop-down and rows, mandatory Y (at least one)).
+Fields in this order: 1 Current / Pending Authorization / History (Tab, mandatory -); 2 Search Criterion or Product (Text, mandatory N); 3 Code / Name / Type / Value / Products / From / Until / Status (Column, mandatory -); 4 Code (Text, mandatory Y); 5 Name (Text, mandatory Y); 6 Incentive type (Drop-down, mandatory Y); 7 Value basis (Drop-down, mandatory Y); 8 Value (Number, mandatory Cond.: rate or fixed amount); 9 Effective from (Date, mandatory Y); 10 Effective to (Date, mandatory N); 11 Rule Parameters (Rows: parameter and value, mandatory N (a value per row)); 12 Description (Text, mandatory N); 13 Products matrix (Drop-down and rows, mandatory Y (at least one)).
 Actions: New Criterion; Open a row; Authorize; Deactivate.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -29542,8 +29542,8 @@
       <c r="L247" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-20 Sales Organisation of the FRS.
-Fields in this order: 1 Unit line (Tree, mandatory -); 2 Account officer line (Tree, mandatory -); 3 Level (Drop-down, mandatory Y); 4 Code / Name (Text, mandatory Y); 5 Cost center (Text, mandatory N); 6 Parent (Drop-down, mandatory Cond.: department and team); 7 Team (Drop-down, mandatory Y); 8 User name (Text, mandatory Y).
-Actions: New Unit; Assign Officer; Authorize / Deactivate.
+Fields in this order: 1 Search unit code, name or officer (Text, mandatory N); 2 Expand All / Collapse All (Button, mandatory -); 3 Show Inactive (Check box, mandatory N); 4 Summary (Text, mandatory -); 5 Unit (Column, mandatory -); 6 Level (Column, mandatory -); 7 Cost Center (Column, mandatory -); 8 Account Officers (Column, mandatory -); 9 Assigned Since (Column, mandatory -); 10 Status (Pill, mandatory -); 11 Actions (Menu, mandatory -); 12 Level (Drop-down, mandatory Y); 13 Code / Name (Text, mandatory Y); 14 Cost Center (Text, mandatory N); 15 Parent (Drop-down, mandatory Cond.: department and team); 16 Code, Name, Level, Parent Unit, Cost Center, Unit Head, Sub-units, Account Officers, Status, Status Reason, Created, Last Changed, Authorized (Detail, mandatory -); 17 Team (Drop-down, mandatory Y); 18 Account Officer (Drop-down, mandatory Y); 19 Reason (Text, mandatory Y).
+Actions: New Unit; Assign Officer; View / Edit; Add Department / Add Team; Assign Officer (row); Authorize; Deactivate; Reactivate; Reassign / Assign to a Team; Remove from Team; Export to Excel.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -30629,21 +30629,21 @@
 MSG-PM-139: "Enter the minimum premium"
 MSG-PM-140: "Enter the package rate or a rate for every insurer"
 MSG-PM-141: "Include at least one coverage"
-MSG-PM-144: "The effective date cannot be before today"
-MSG-PM-145: "The package end date must be after the effective date"
-MSG-PM-146: "The package version is validated and released for use."
-MSG-PM-149: "A package version is validated by someone other than its maker and submitter" (MAKER_CHECKER_VIOLATION)
-MSG-PM-150: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-PM-151: "Enter the effective date" (PACKAGE_DATES_INVALID)
-MSG-PM-152: "The effective date cannot be before today" (PACKAGE_DATES_INVALID)
-MSG-PM-153: "The effective date must be after the start of version &lt;version no&gt;" (PACKAGE_DATES_INVALID)
-MSG-PM-154: "The package end date must be after the effective date" (PACKAGE_DATES_INVALID)
-MSG-PM-155: "The package needs its cover type and at least one included basic coverage" (PACKAGE_HIERARCHY_INCOMPLETE)
-MSG-PM-156: "Insurer &lt;insurer code&gt; has no terms for coverage &lt;coverage&gt;" (PACKAGE_INSURER_TERMS_MISSING)
-MSG-PM-157: "Enter the package rate or a rate for every insurer" (PACKAGE_RATE_MISSING)
-MSG-PM-158: "The co-insurance shares must add up to 100%" (PACKAGE_SHARES_INVALID)
-MSG-PM-159: "Enter the reason of the return" (REASON_REQUIRED)
-MSG-PM-160: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
+MSG-PM-145: "The effective date cannot be before today"
+MSG-PM-146: "The package end date must be after the effective date"
+MSG-PM-147: "The package version is validated and released for use."
+MSG-PM-150: "A package version is validated by someone other than its maker and submitter" (MAKER_CHECKER_VIOLATION)
+MSG-PM-151: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-PM-152: "Enter the effective date" (PACKAGE_DATES_INVALID)
+MSG-PM-153: "The effective date cannot be before today" (PACKAGE_DATES_INVALID)
+MSG-PM-154: "The effective date must be after the start of version &lt;version no&gt;" (PACKAGE_DATES_INVALID)
+MSG-PM-155: "The package end date must be after the effective date" (PACKAGE_DATES_INVALID)
+MSG-PM-156: "The package needs its cover type and at least one included basic coverage" (PACKAGE_HIERARCHY_INCOMPLETE)
+MSG-PM-157: "Insurer &lt;insurer code&gt; has no terms for coverage &lt;coverage&gt;" (PACKAGE_INSURER_TERMS_MISSING)
+MSG-PM-158: "Enter the package rate or a rate for every insurer" (PACKAGE_RATE_MISSING)
+MSG-PM-159: "The co-insurance shares must add up to 100%" (PACKAGE_SHARES_INVALID)
+MSG-PM-160: "Enter the reason of the return" (REASON_REQUIRED)
+MSG-PM-161: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
         </is>
       </c>
       <c r="M260" s="12" t="inlineStr">
@@ -30718,17 +30718,17 @@
       <c r="L261" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-163: "Enter the effective date"
-MSG-PM-164: "Enter the name"
-MSG-PM-165: "Enter the title"
-MSG-PM-166: "Enter the wording"
-MSG-PM-168: "Select the kind"
-MSG-PM-169: "Select the product line"
-MSG-PM-171: "The end is before the start"
-MSG-PM-172: "Use A-Z, 0-9 and _"
-MSG-PM-173: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-174: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
-MSG-PM-175: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-164: "Enter the effective date"
+MSG-PM-165: "Enter the name"
+MSG-PM-166: "Enter the title"
+MSG-PM-167: "Enter the wording"
+MSG-PM-169: "Select the kind"
+MSG-PM-170: "Select the product line"
+MSG-PM-172: "The end is before the start"
+MSG-PM-173: "Use A-Z, 0-9 and _"
+MSG-PM-174: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-175: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
+MSG-PM-176: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M261" s="12" t="inlineStr">
@@ -30803,24 +30803,25 @@
       <c r="L262" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-178: "Enter the name"
-MSG-PM-179: "Enter the start date"
-MSG-PM-180: "Enter the value"
-MSG-PM-181: "Enter valid JSON, e.g. {"minimumPremium": 5000}"
-MSG-PM-182: "Select at least one product of the matrix"
-MSG-PM-183: "Select the type"
-MSG-PM-184: "The change must start after &lt;active from&gt;"
-MSG-PM-185: "The end is before the start"
-MSG-PM-186: "Use A-Z, 0-9, _ and -"
-MSG-PM-187: "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED)
-MSG-PM-188: "Only an active criterion is amended; change the pending row" (INCENTIVE_NOT_ACTIVE)
-MSG-PM-189: "The amendment must start after &lt;effective from&gt;" (INCENTIVE_PERIOD_INVALID)
-MSG-PM-190: "Criterion &lt;code&gt; already covers part of this period" (INCENTIVE_PERIOD_OVERLAP)
-MSG-PM-191: "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED)
-MSG-PM-192: "Product &lt;product code&gt; is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE)
-MSG-PM-193: "The rule parameters must be valid JSON" (INCENTIVE_RULE_PARAMS_INVALID)
-MSG-PM-194: "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED)
-MSG-PM-195: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-179: "Enter a value for each parameter"
+MSG-PM-180: "Enter the name"
+MSG-PM-181: "Enter the start date"
+MSG-PM-182: "Enter the value"
+MSG-PM-183: "Select at least one product of the matrix"
+MSG-PM-184: "Select the parameter"
+MSG-PM-185: "Select the type"
+MSG-PM-186: "The change must start after &lt;active from&gt;"
+MSG-PM-187: "The end is before the start"
+MSG-PM-188: "Use A-Z, 0-9, _ and -"
+MSG-PM-189: "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED)
+MSG-PM-190: "Only an active criterion is amended; change the pending row" (INCENTIVE_NOT_ACTIVE)
+MSG-PM-191: "The amendment must start after &lt;effective from&gt;" (INCENTIVE_PERIOD_INVALID)
+MSG-PM-192: "Criterion &lt;code&gt; already covers part of this period" (INCENTIVE_PERIOD_OVERLAP)
+MSG-PM-193: "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED)
+MSG-PM-194: "Product &lt;product code&gt; is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE)
+MSG-PM-195: "Enter the rule parameters as parameter and value rows" (INCENTIVE_RULE_PARAMS_INVALID)
+MSG-PM-196: "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED)
+MSG-PM-197: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M262" s="12" t="inlineStr">
@@ -30895,17 +30896,17 @@
       <c r="L263" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-198: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
-MSG-PM-199: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-200: "Branch &lt;branch code&gt; is not authorized or inactive" (INSURER_BRANCH_NOT_ACTIVE)
-MSG-PM-201: "Insurer &lt;party code&gt; has no branch &lt;branch code&gt;" (INSURER_BRANCH_UNKNOWN)
-MSG-PM-202: "Insurer &lt;party code&gt; is not authorized or is inactive" (INSURER_NOT_ACTIVE)
-MSG-PM-203: "&lt;label&gt; not found: &lt;branch id&gt;" (NOT_FOUND)
-MSG-PM-204: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-205: "&lt;label&gt; not found: &lt;party code&gt;" (NOT_FOUND)
-MSG-PM-206: "Party &lt;party code&gt; exists and is not an insurer" (PARTY_NOT_INSURER)
-MSG-PM-207: "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED)
-MSG-PM-208: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
+MSG-PM-200: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
+MSG-PM-201: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-202: "Branch &lt;branch code&gt; is not authorized or inactive" (INSURER_BRANCH_NOT_ACTIVE)
+MSG-PM-203: "Insurer &lt;party code&gt; has no branch &lt;branch code&gt;" (INSURER_BRANCH_UNKNOWN)
+MSG-PM-204: "Insurer &lt;party code&gt; is not authorized or is inactive" (INSURER_NOT_ACTIVE)
+MSG-PM-205: "&lt;label&gt; not found: &lt;branch id&gt;" (NOT_FOUND)
+MSG-PM-206: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-207: "&lt;label&gt; not found: &lt;party code&gt;" (NOT_FOUND)
+MSG-PM-208: "Party &lt;party code&gt; exists and is not an insurer" (PARTY_NOT_INSURER)
+MSG-PM-209: "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED)
+MSG-PM-210: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
         </is>
       </c>
       <c r="M263" s="12" t="inlineStr">
@@ -30980,13 +30981,13 @@
       <c r="L264" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-212: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
-MSG-PM-213: "The effective-to date is before the effective-from date" (EFFECTIVITY_INVALID)
-MSG-PM-214: "The limit must be greater than zero" (LIMIT_INVALID)
-MSG-PM-215: "The premium cannot be negative" (LIMIT_PREMIUM_INVALID)
-MSG-PM-216: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-217: "&lt;label&gt; must be a percentage between 0 and 100" (RATE_INVALID)
-MSG-PM-218: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
+MSG-PM-214: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
+MSG-PM-215: "The effective-to date is before the effective-from date" (EFFECTIVITY_INVALID)
+MSG-PM-216: "The limit must be greater than zero" (LIMIT_INVALID)
+MSG-PM-217: "The premium cannot be negative" (LIMIT_PREMIUM_INVALID)
+MSG-PM-218: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-219: "&lt;label&gt; must be a percentage between 0 and 100" (RATE_INVALID)
+MSG-PM-220: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
         </is>
       </c>
       <c r="M264" s="12" t="inlineStr">
@@ -31053,13 +31054,19 @@
       <c r="L265" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-220: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-221: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-222: "&lt;label&gt; not found: &lt;unit code&gt;" (NOT_FOUND)
-MSG-PM-223: "A &lt;level&gt; must belong to a &lt;parent level&gt;" (SALES_PARENT_INVALID)
-MSG-PM-224: "Unknown team &lt;team code&gt;" (SALES_TEAM_UNKNOWN)
-MSG-PM-225: "Unknown user &lt;head&gt;" (USER_UNKNOWN)
-MSG-PM-226: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
+MSG-PM-228: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-229: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-230: "&lt;label&gt; not found: &lt;unit code&gt;" (NOT_FOUND)
+MSG-PM-231: "Enter the reason" (REASON_REQUIRED)
+MSG-PM-232: "&lt;&gt; is already removed from the team" (SALES_OFFICER_INACTIVE)
+MSG-PM-233: "A &lt;level&gt; must belong to an active &lt;parent level&gt;" (SALES_PARENT_INVALID)
+MSG-PM-234: "Reactivate &lt;parent code&gt; before &lt;code&gt;" (SALES_PARENT_INVALID)
+MSG-PM-235: "Team &lt;team code&gt; is unknown or inactive" (SALES_TEAM_UNKNOWN)
+MSG-PM-236: "Unit &lt;code&gt; is already inactive" (SALES_UNIT_INACTIVE)
+MSG-PM-237: "&lt;code&gt; still has &lt;open&gt;: deactivate or move them before deactivating the unit" (SALES_UNIT_IN_USE)
+MSG-PM-238: "Unit &lt;code&gt; is not inactive" (SALES_UNIT_NOT_INACTIVE)
+MSG-PM-239: "Unknown user &lt;head&gt;" (USER_UNKNOWN)
+MSG-PM-240: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
         </is>
       </c>
       <c r="M265" s="12" t="inlineStr">
@@ -31134,18 +31141,18 @@
       <c r="L266" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-227: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
-MSG-PM-228: "&lt;coverage&gt; limit &lt;to plain string&gt; is not in the limit table" (MOTOR_LIMIT_UNKNOWN)
-MSG-PM-229: "Package &lt;code&gt; expired and has no current version" (PRODUCT_NOT_SELLABLE)
-MSG-PM-230: "Package &lt;code&gt; has no released version in force" (PRODUCT_NOT_SELLABLE)
-MSG-PM-231: "Package &lt;code&gt; is &lt;lifecycle status&gt;: it is locked for new business" (PRODUCT_NOT_SELLABLE)
-MSG-PM-232: "Enter at least one item to rate" (RATING_NO_ITEMS)
-MSG-PM-233: "The motor OD/Theft coverage factor is not set up" (RATING_OD_FACTOR_MISSING)
-MSG-PM-234: "The period end must be after the period start" (RATING_PERIOD_INVALID)
-MSG-PM-235: "Enter the premium rate of &lt;item&gt;" (RATING_RATE_REQUIRED)
-MSG-PM-236: "No short-period percentage applies to this period" (RATING_SHORT_PERIOD_INVALID)
-MSG-PM-237: "Enter a sum insured of zero or more for every item" (RATING_SUM_INSURED_INVALID)
-MSG-PM-238: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-PM-241: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
+MSG-PM-242: "&lt;coverage&gt; limit &lt;to plain string&gt; is not in the limit table" (MOTOR_LIMIT_UNKNOWN)
+MSG-PM-243: "Package &lt;code&gt; expired and has no current version" (PRODUCT_NOT_SELLABLE)
+MSG-PM-244: "Package &lt;code&gt; has no released version in force" (PRODUCT_NOT_SELLABLE)
+MSG-PM-245: "Package &lt;code&gt; is &lt;lifecycle status&gt;: it is locked for new business" (PRODUCT_NOT_SELLABLE)
+MSG-PM-246: "Enter at least one item to rate" (RATING_NO_ITEMS)
+MSG-PM-247: "The motor OD/Theft coverage factor is not set up" (RATING_OD_FACTOR_MISSING)
+MSG-PM-248: "The period end must be after the period start" (RATING_PERIOD_INVALID)
+MSG-PM-249: "Enter the premium rate of &lt;item&gt;" (RATING_RATE_REQUIRED)
+MSG-PM-250: "No short-period percentage applies to this period" (RATING_SHORT_PERIOD_INVALID)
+MSG-PM-251: "Enter a sum insured of zero or more for every item" (RATING_SUM_INSURED_INVALID)
+MSG-PM-252: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M266" s="12" t="inlineStr">
@@ -31220,14 +31227,14 @@
       <c r="L267" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-240: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
-MSG-PM-241: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
-MSG-PM-242: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
-MSG-PM-243: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
-MSG-PM-244: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
-MSG-PM-245: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-246: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-247: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
+MSG-PM-254: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-255: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
+MSG-PM-256: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
+MSG-PM-257: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
+MSG-PM-258: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
+MSG-PM-259: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-260: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-261: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="M267" s="12" t="inlineStr">
@@ -31290,7 +31297,7 @@
       <c r="L268" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-248: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-262: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M268" s="12" t="inlineStr">
@@ -31353,13 +31360,13 @@
       <c r="L269" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-249: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-PM-250: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-PM-252: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-PM-254: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-PM-255: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-PM-260: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-PM-261: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-PM-263: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-PM-264: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-PM-266: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-PM-268: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-PM-269: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-PM-274: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-PM-275: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M269" s="12" t="inlineStr">
@@ -31422,12 +31429,12 @@
       <c r="L270" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-251: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-253: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
-MSG-PM-256: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-257: "Product &lt;code&gt; was not created by the migration" (PRODUCT_NOT_MIGRATED)
-MSG-PM-258: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
-MSG-PM-259: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
+MSG-PM-265: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-267: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-270: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-271: "Product &lt;code&gt; was not created by the migration" (PRODUCT_NOT_MIGRATED)
+MSG-PM-272: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
+MSG-PM-273: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="M270" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -11312,8 +11312,8 @@
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>The last wrong attempt locks the account; the correct password is then refused until the System Administrator unlocks the user in Administration &gt; Users.
-Message "Account is locked. Contact your administrator." (AUTHENTICATION_FAILED).</t>
+          <t>The last wrong attempt locks the account; the correct password is then refused with the same message as a wrong password until the System Administrator unlocks the user in Administration &gt; Users, where the lock shows.
+Message "Invalid user name or password" (AUTHENTICATION_FAILED).</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
@@ -28211,7 +28211,7 @@
       <c r="L230" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-03 New Package Request and Edit Package Request of the FRS.
-Fields in this order: 1 Request type (Drop-down, mandatory Y); 2 Scope (Drop-down, mandatory Y); 3 Package / programme name (Text, mandatory Y); 4 Client or prospect (Look-up, mandatory Cond.: client-specific package); 5 Product line (Drop-down, mandatory Y); 6 Cover type / subtype (Drop-down, mandatory Cond.: New package); 7 Package product (Drop-down, mandatory Cond.: every type except New package); 8 Reason (Drop-down, mandatory Y); 9 Comment on the reason (Text, mandatory N); 10 Negotiate with the insurers (Check box, mandatory N); 11 Market segments (Check boxes, mandatory N); 12 Heading / Details (Text, mandatory Cond.: sections or coverages before submission); 13 Coverage code (Text, mandatory Cond.: sections or coverages before submission); 14 Included (Check box, mandatory N); 15 Limit (Number, mandatory N); 16 Deductible (Text, mandatory N); 17 Requested rate % (Number, mandatory N); 18 Minimum premium (Number, mandatory N); 19 Commission % (Number, mandatory N); 20 Package TSI limit (Number, mandatory N); 21 Effective from (Date, mandatory N); 22 Package start (Date, mandatory N); 23 Package end (Date, mandatory Cond.: before submission (not for Retire)); 24 Anniversary (Date, mandatory N); 25 Insurer check boxes (Check boxes, mandatory Cond.: at least one when the insurers are approached); 26 Documents panel (Upload, mandatory N).
+Fields in this order: 1 Request type (Drop-down, mandatory Y); 2 Scope (Drop-down, mandatory Y); 3 Package / programme name (Text, mandatory Y); 4 Client or prospect (Look-up, mandatory Cond.: client-specific package); 5 Product line (Drop-down, mandatory Y); 6 Cover type / subtype (Drop-down, mandatory Cond.: New package); 7 Package product (Drop-down, mandatory Cond.: every type except New package); 8 Reason (Drop-down, mandatory Y); 9 Comment on the reason (Text, mandatory N); 10 Negotiate with the insurers (Check box, mandatory N); 11 Market segments (Check boxes, mandatory N); 12 Heading / Details (Text, mandatory Cond.: sections or coverages before submission); 13 Coverage (Drop-down, mandatory Cond.: sections or coverages before submission); 14 Included (Check box, mandatory N); 15 Limit (Number, mandatory N); 16 Deductible (Text, mandatory N); 17 Requested rate % (Number, mandatory N); 18 Minimum premium (Number, mandatory N); 19 Commission % (Number, mandatory N); 20 Package TSI limit (Number, mandatory N); 21 Effective from (Date, mandatory N); 22 Package start (Date, mandatory N); 23 Package end (Date, mandatory Cond.: before submission (not for Retire)); 24 Anniversary (Date, mandatory N); 25 Insurer check boxes (Check boxes, mandatory Cond.: at least one when the insurers are approached); 26 Documents panel (Upload, mandatory N).
 Actions: Load Current Terms; Save Draft; Submit for Approval.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -30542,11 +30542,11 @@
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-PM-123: "Describe the change"
-MSG-PM-128: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-129: "Complete the parameters of the &lt;type&gt; rule" (FIELD_RULE_INCOMPLETE)
-MSG-PM-130: "Unknown list of values &lt;lov type&gt;" (LOV_TYPE_UNKNOWN)
-MSG-PM-131: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-132: "Rules for every product use the scope code '*'" (RULE_SCOPE_INVALID)</t>
+MSG-PM-129: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-130: "Complete the parameters of the &lt;type&gt; rule" (FIELD_RULE_INCOMPLETE)
+MSG-PM-131: "Unknown list of values &lt;lov type&gt;" (LOV_TYPE_UNKNOWN)
+MSG-PM-132: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-133: "Rules for every product use the scope code '*'" (RULE_SCOPE_INVALID)</t>
         </is>
       </c>
       <c r="M259" s="12" t="inlineStr">
@@ -30621,29 +30621,29 @@
       <c r="L260" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-134: "Correct the highlighted fields"
-MSG-PM-135: "Enter a commission between 0 and 100"
-MSG-PM-136: "Enter a positive amount"
-MSG-PM-137: "Enter a rate between 0 and 100"
-MSG-PM-138: "Enter the effective date"
-MSG-PM-139: "Enter the minimum premium"
-MSG-PM-140: "Enter the package rate or a rate for every insurer"
-MSG-PM-141: "Include at least one coverage"
-MSG-PM-145: "The effective date cannot be before today"
-MSG-PM-146: "The package end date must be after the effective date"
-MSG-PM-147: "The package version is validated and released for use."
-MSG-PM-150: "A package version is validated by someone other than its maker and submitter" (MAKER_CHECKER_VIOLATION)
-MSG-PM-151: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-PM-152: "Enter the effective date" (PACKAGE_DATES_INVALID)
-MSG-PM-153: "The effective date cannot be before today" (PACKAGE_DATES_INVALID)
-MSG-PM-154: "The effective date must be after the start of version &lt;version no&gt;" (PACKAGE_DATES_INVALID)
-MSG-PM-155: "The package end date must be after the effective date" (PACKAGE_DATES_INVALID)
-MSG-PM-156: "The package needs its cover type and at least one included basic coverage" (PACKAGE_HIERARCHY_INCOMPLETE)
-MSG-PM-157: "Insurer &lt;insurer code&gt; has no terms for coverage &lt;coverage&gt;" (PACKAGE_INSURER_TERMS_MISSING)
-MSG-PM-158: "Enter the package rate or a rate for every insurer" (PACKAGE_RATE_MISSING)
-MSG-PM-159: "The co-insurance shares must add up to 100%" (PACKAGE_SHARES_INVALID)
-MSG-PM-160: "Enter the reason of the return" (REASON_REQUIRED)
-MSG-PM-161: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
+MSG-PM-135: "Correct the highlighted fields"
+MSG-PM-136: "Enter a commission between 0 and 100"
+MSG-PM-137: "Enter a positive amount"
+MSG-PM-138: "Enter a rate between 0 and 100"
+MSG-PM-139: "Enter the effective date"
+MSG-PM-140: "Enter the minimum premium"
+MSG-PM-141: "Enter the package rate or a rate for every insurer"
+MSG-PM-142: "Include at least one coverage"
+MSG-PM-146: "The effective date cannot be before today"
+MSG-PM-147: "The package end date must be after the effective date"
+MSG-PM-148: "The package version is validated and released for use."
+MSG-PM-151: "A package version is validated by someone other than its maker and submitter" (MAKER_CHECKER_VIOLATION)
+MSG-PM-152: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-PM-153: "Enter the effective date" (PACKAGE_DATES_INVALID)
+MSG-PM-154: "The effective date cannot be before today" (PACKAGE_DATES_INVALID)
+MSG-PM-155: "The effective date must be after the start of version &lt;version no&gt;" (PACKAGE_DATES_INVALID)
+MSG-PM-156: "The package end date must be after the effective date" (PACKAGE_DATES_INVALID)
+MSG-PM-157: "The package needs its cover type and at least one included basic coverage" (PACKAGE_HIERARCHY_INCOMPLETE)
+MSG-PM-158: "Insurer &lt;insurer code&gt; has no terms for coverage &lt;coverage&gt;" (PACKAGE_INSURER_TERMS_MISSING)
+MSG-PM-159: "Enter the package rate or a rate for every insurer" (PACKAGE_RATE_MISSING)
+MSG-PM-160: "The co-insurance shares must add up to 100%" (PACKAGE_SHARES_INVALID)
+MSG-PM-161: "Enter the reason of the return" (REASON_REQUIRED)
+MSG-PM-162: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
         </is>
       </c>
       <c r="M260" s="12" t="inlineStr">
@@ -30718,17 +30718,17 @@
       <c r="L261" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-164: "Enter the effective date"
-MSG-PM-165: "Enter the name"
-MSG-PM-166: "Enter the title"
-MSG-PM-167: "Enter the wording"
-MSG-PM-169: "Select the kind"
-MSG-PM-170: "Select the product line"
-MSG-PM-172: "The end is before the start"
-MSG-PM-173: "Use A-Z, 0-9 and _"
-MSG-PM-174: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-175: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
-MSG-PM-176: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-165: "Enter the effective date"
+MSG-PM-166: "Enter the name"
+MSG-PM-167: "Enter the title"
+MSG-PM-168: "Enter the wording"
+MSG-PM-170: "Select the kind"
+MSG-PM-171: "Select the product line"
+MSG-PM-173: "The end is before the start"
+MSG-PM-174: "Use A-Z, 0-9 and _"
+MSG-PM-175: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-176: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
+MSG-PM-177: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M261" s="12" t="inlineStr">
@@ -30803,25 +30803,25 @@
       <c r="L262" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-179: "Enter a value for each parameter"
-MSG-PM-180: "Enter the name"
-MSG-PM-181: "Enter the start date"
-MSG-PM-182: "Enter the value"
-MSG-PM-183: "Select at least one product of the matrix"
-MSG-PM-184: "Select the parameter"
-MSG-PM-185: "Select the type"
-MSG-PM-186: "The change must start after &lt;active from&gt;"
-MSG-PM-187: "The end is before the start"
-MSG-PM-188: "Use A-Z, 0-9, _ and -"
-MSG-PM-189: "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED)
-MSG-PM-190: "Only an active criterion is amended; change the pending row" (INCENTIVE_NOT_ACTIVE)
-MSG-PM-191: "The amendment must start after &lt;effective from&gt;" (INCENTIVE_PERIOD_INVALID)
-MSG-PM-192: "Criterion &lt;code&gt; already covers part of this period" (INCENTIVE_PERIOD_OVERLAP)
-MSG-PM-193: "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED)
-MSG-PM-194: "Product &lt;product code&gt; is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE)
-MSG-PM-195: "Enter the rule parameters as parameter and value rows" (INCENTIVE_RULE_PARAMS_INVALID)
-MSG-PM-196: "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED)
-MSG-PM-197: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-180: "Enter a value for each parameter"
+MSG-PM-181: "Enter the name"
+MSG-PM-182: "Enter the start date"
+MSG-PM-183: "Enter the value"
+MSG-PM-184: "Select at least one product of the matrix"
+MSG-PM-185: "Select the parameter"
+MSG-PM-186: "Select the type"
+MSG-PM-187: "The change must start after &lt;active from&gt;"
+MSG-PM-188: "The end is before the start"
+MSG-PM-189: "Use A-Z, 0-9, _ and -"
+MSG-PM-190: "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED)
+MSG-PM-191: "Only an active criterion is amended; change the pending row" (INCENTIVE_NOT_ACTIVE)
+MSG-PM-192: "The amendment must start after &lt;effective from&gt;" (INCENTIVE_PERIOD_INVALID)
+MSG-PM-193: "Criterion &lt;code&gt; already covers part of this period" (INCENTIVE_PERIOD_OVERLAP)
+MSG-PM-194: "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED)
+MSG-PM-195: "Product &lt;product code&gt; is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE)
+MSG-PM-196: "Enter the rule parameters as parameter and value rows" (INCENTIVE_RULE_PARAMS_INVALID)
+MSG-PM-197: "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED)
+MSG-PM-198: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M262" s="12" t="inlineStr">
@@ -30896,17 +30896,17 @@
       <c r="L263" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-200: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
-MSG-PM-201: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-202: "Branch &lt;branch code&gt; is not authorized or inactive" (INSURER_BRANCH_NOT_ACTIVE)
-MSG-PM-203: "Insurer &lt;party code&gt; has no branch &lt;branch code&gt;" (INSURER_BRANCH_UNKNOWN)
-MSG-PM-204: "Insurer &lt;party code&gt; is not authorized or is inactive" (INSURER_NOT_ACTIVE)
-MSG-PM-205: "&lt;label&gt; not found: &lt;branch id&gt;" (NOT_FOUND)
-MSG-PM-206: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-207: "&lt;label&gt; not found: &lt;party code&gt;" (NOT_FOUND)
-MSG-PM-208: "Party &lt;party code&gt; exists and is not an insurer" (PARTY_NOT_INSURER)
-MSG-PM-209: "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED)
-MSG-PM-210: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
+MSG-PM-201: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
+MSG-PM-202: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-203: "Branch &lt;branch code&gt; is not authorized or inactive" (INSURER_BRANCH_NOT_ACTIVE)
+MSG-PM-204: "Insurer &lt;party code&gt; has no branch &lt;branch code&gt;" (INSURER_BRANCH_UNKNOWN)
+MSG-PM-205: "Insurer &lt;party code&gt; is not authorized or is inactive" (INSURER_NOT_ACTIVE)
+MSG-PM-206: "&lt;label&gt; not found: &lt;branch id&gt;" (NOT_FOUND)
+MSG-PM-207: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-208: "&lt;label&gt; not found: &lt;party code&gt;" (NOT_FOUND)
+MSG-PM-209: "Party &lt;party code&gt; exists and is not an insurer" (PARTY_NOT_INSURER)
+MSG-PM-210: "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED)
+MSG-PM-211: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
         </is>
       </c>
       <c r="M263" s="12" t="inlineStr">
@@ -30981,13 +30981,13 @@
       <c r="L264" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-214: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
-MSG-PM-215: "The effective-to date is before the effective-from date" (EFFECTIVITY_INVALID)
-MSG-PM-216: "The limit must be greater than zero" (LIMIT_INVALID)
-MSG-PM-217: "The premium cannot be negative" (LIMIT_PREMIUM_INVALID)
-MSG-PM-218: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-219: "&lt;label&gt; must be a percentage between 0 and 100" (RATE_INVALID)
-MSG-PM-220: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
+MSG-PM-215: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
+MSG-PM-216: "The effective-to date is before the effective-from date" (EFFECTIVITY_INVALID)
+MSG-PM-217: "The limit must be greater than zero" (LIMIT_INVALID)
+MSG-PM-218: "The premium cannot be negative" (LIMIT_PREMIUM_INVALID)
+MSG-PM-219: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-220: "&lt;label&gt; must be a percentage between 0 and 100" (RATE_INVALID)
+MSG-PM-221: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
         </is>
       </c>
       <c r="M264" s="12" t="inlineStr">
@@ -31054,19 +31054,19 @@
       <c r="L265" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-228: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-229: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-230: "&lt;label&gt; not found: &lt;unit code&gt;" (NOT_FOUND)
-MSG-PM-231: "Enter the reason" (REASON_REQUIRED)
-MSG-PM-232: "&lt;&gt; is already removed from the team" (SALES_OFFICER_INACTIVE)
-MSG-PM-233: "A &lt;level&gt; must belong to an active &lt;parent level&gt;" (SALES_PARENT_INVALID)
-MSG-PM-234: "Reactivate &lt;parent code&gt; before &lt;code&gt;" (SALES_PARENT_INVALID)
-MSG-PM-235: "Team &lt;team code&gt; is unknown or inactive" (SALES_TEAM_UNKNOWN)
-MSG-PM-236: "Unit &lt;code&gt; is already inactive" (SALES_UNIT_INACTIVE)
-MSG-PM-237: "&lt;code&gt; still has &lt;open&gt;: deactivate or move them before deactivating the unit" (SALES_UNIT_IN_USE)
-MSG-PM-238: "Unit &lt;code&gt; is not inactive" (SALES_UNIT_NOT_INACTIVE)
-MSG-PM-239: "Unknown user &lt;head&gt;" (USER_UNKNOWN)
-MSG-PM-240: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
+MSG-PM-229: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-230: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-231: "&lt;label&gt; not found: &lt;unit code&gt;" (NOT_FOUND)
+MSG-PM-232: "Enter the reason" (REASON_REQUIRED)
+MSG-PM-233: "&lt;&gt; is already removed from the team" (SALES_OFFICER_INACTIVE)
+MSG-PM-234: "A &lt;level&gt; must belong to an active &lt;parent level&gt;" (SALES_PARENT_INVALID)
+MSG-PM-235: "Reactivate &lt;parent code&gt; before &lt;code&gt;" (SALES_PARENT_INVALID)
+MSG-PM-236: "Team &lt;team code&gt; is unknown or inactive" (SALES_TEAM_UNKNOWN)
+MSG-PM-237: "Unit &lt;code&gt; is already inactive" (SALES_UNIT_INACTIVE)
+MSG-PM-238: "&lt;code&gt; still has &lt;open&gt;: deactivate or move them before deactivating the unit" (SALES_UNIT_IN_USE)
+MSG-PM-239: "Unit &lt;code&gt; is not inactive" (SALES_UNIT_NOT_INACTIVE)
+MSG-PM-240: "Unknown user &lt;head&gt;" (USER_UNKNOWN)
+MSG-PM-241: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
         </is>
       </c>
       <c r="M265" s="12" t="inlineStr">
@@ -31141,18 +31141,18 @@
       <c r="L266" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-241: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
-MSG-PM-242: "&lt;coverage&gt; limit &lt;to plain string&gt; is not in the limit table" (MOTOR_LIMIT_UNKNOWN)
-MSG-PM-243: "Package &lt;code&gt; expired and has no current version" (PRODUCT_NOT_SELLABLE)
-MSG-PM-244: "Package &lt;code&gt; has no released version in force" (PRODUCT_NOT_SELLABLE)
-MSG-PM-245: "Package &lt;code&gt; is &lt;lifecycle status&gt;: it is locked for new business" (PRODUCT_NOT_SELLABLE)
-MSG-PM-246: "Enter at least one item to rate" (RATING_NO_ITEMS)
-MSG-PM-247: "The motor OD/Theft coverage factor is not set up" (RATING_OD_FACTOR_MISSING)
-MSG-PM-248: "The period end must be after the period start" (RATING_PERIOD_INVALID)
-MSG-PM-249: "Enter the premium rate of &lt;item&gt;" (RATING_RATE_REQUIRED)
-MSG-PM-250: "No short-period percentage applies to this period" (RATING_SHORT_PERIOD_INVALID)
-MSG-PM-251: "Enter a sum insured of zero or more for every item" (RATING_SUM_INSURED_INVALID)
-MSG-PM-252: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-PM-242: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
+MSG-PM-243: "&lt;coverage&gt; limit &lt;to plain string&gt; is not in the limit table" (MOTOR_LIMIT_UNKNOWN)
+MSG-PM-244: "Package &lt;code&gt; expired and has no current version" (PRODUCT_NOT_SELLABLE)
+MSG-PM-245: "Package &lt;code&gt; has no released version in force" (PRODUCT_NOT_SELLABLE)
+MSG-PM-246: "Package &lt;code&gt; is &lt;lifecycle status&gt;: it is locked for new business" (PRODUCT_NOT_SELLABLE)
+MSG-PM-247: "Enter at least one item to rate" (RATING_NO_ITEMS)
+MSG-PM-248: "The motor OD/Theft coverage factor is not set up" (RATING_OD_FACTOR_MISSING)
+MSG-PM-249: "The period end must be after the period start" (RATING_PERIOD_INVALID)
+MSG-PM-250: "Enter the premium rate of &lt;item&gt;" (RATING_RATE_REQUIRED)
+MSG-PM-251: "No short-period percentage applies to this period" (RATING_SHORT_PERIOD_INVALID)
+MSG-PM-252: "Enter a sum insured of zero or more for every item" (RATING_SUM_INSURED_INVALID)
+MSG-PM-253: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M266" s="12" t="inlineStr">
@@ -31227,14 +31227,14 @@
       <c r="L267" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-254: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
-MSG-PM-255: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
-MSG-PM-256: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
-MSG-PM-257: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
-MSG-PM-258: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
-MSG-PM-259: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-260: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-261: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
+MSG-PM-255: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-256: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
+MSG-PM-257: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
+MSG-PM-258: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
+MSG-PM-259: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
+MSG-PM-260: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-261: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-262: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="M267" s="12" t="inlineStr">
@@ -31297,7 +31297,7 @@
       <c r="L268" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-262: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-263: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M268" s="12" t="inlineStr">
@@ -31360,13 +31360,13 @@
       <c r="L269" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-263: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-PM-264: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-PM-266: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-PM-268: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-PM-269: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-PM-274: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-PM-275: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-PM-264: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-PM-265: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-PM-267: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-PM-269: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-PM-270: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-PM-275: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-PM-276: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M269" s="12" t="inlineStr">
@@ -31429,12 +31429,12 @@
       <c r="L270" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-265: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-267: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
-MSG-PM-270: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-271: "Product &lt;code&gt; was not created by the migration" (PRODUCT_NOT_MIGRATED)
-MSG-PM-272: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
-MSG-PM-273: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
+MSG-PM-266: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-268: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-271: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-272: "Product &lt;code&gt; was not created by the migration" (PRODUCT_NOT_MIGRATED)
+MSG-PM-273: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
+MSG-PM-274: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="M270" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/04_BIBS_TestPlan_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -26915,7 +26915,7 @@
       </c>
       <c r="K213" s="12" t="inlineStr">
         <is>
-          <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign (seed), value basis Fixed amount, value 500, effective from today; products MTR12; save.
+          <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign, value basis Fixed amount, value 500, effective from today; products MTR12; save.
 2. As badmin authorise it in My Approvals.</t>
         </is>
       </c>
@@ -28369,7 +28369,7 @@
       <c r="L232" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-PM-05 Package Request record: Negotiation tab of the FRS.
-Fields in this order: 1 Round n · slip number (Card title, mandatory -); 2 Round status pill and Locked tag (Pill, mandatory -); 3 Round note (Text, mandatory -); 4 Insurer check boxes (Check boxes, mandatory Y (at least one)); 5 Notes to the insurers (Text, mandatory N); 6 Insurer (Column, mandatory -); 7 Outcome (Column, mandatory -); 8 Rate % / Minimum / Conditions / Valid Until (Column, mandatory -); 9 Rev. (Column, mandatory -); 10 Outcome (Drop-down, mandatory Y); 11 Rate % (Number, mandatory Cond.: an offer (accepted, approved with changes, counter-proposal)); 12 Minimum premium (Number, mandatory N); 13 Valid until (Date, mandatory N); 14 Deductible per coverage (Text, mandatory N); 15 Conditions and warranties (Text, mandatory N); 16 Remarks (Text, mandatory N); 17 Response document (File, mandatory N); 18 Offer check box (Check box, mandatory Y (at least one)); 19 Role (Drop-down, mandatory Y); 20 Share % (Number, mandatory Cond.: co-insurance (lead and participants)); 21 Comment (Text, mandatory N); 22 Insurer check boxes (Check boxes, mandatory Y (at least one)); 23 What changes in this round (Text, mandatory N).
+Fields in this order: 1 Round n · slip number (Card title, mandatory -); 2 Round status pill and Locked tag (Pill, mandatory -); 3 Round note (Text, mandatory -); 4 Insurer check boxes (Check boxes, mandatory Y (at least one)); 5 Notes to the insurers (Text, mandatory N); 6 Insurer (Column, mandatory -); 7 Outcome (Column, mandatory -); 8 Rate % / Minimum / Conditions / Valid Until (Column, mandatory -); 9 Rev. (Column, mandatory -); 10 Row action menu (Row action menu, mandatory -); 11 Outcome (Drop-down, mandatory Y); 12 Rate % (Number, mandatory Cond.: an offer (accepted, approved with changes, counter-proposal)); 13 Minimum premium (Number, mandatory N); 14 Valid until (Date, mandatory N); 15 Deductible per coverage (Text, mandatory N); 16 Conditions and warranties (Text, mandatory N); 17 Remarks (Text, mandatory N); 18 Response document (File, mandatory N); 19 Offer check box (Check box, mandatory Y (at least one)); 20 Role (Drop-down, mandatory Y); 21 Share % (Number, mandatory Cond.: co-insurance (lead and participants)); 22 Comment (Text, mandatory N); 23 Insurer check boxes (Check boxes, mandatory Y (at least one)); 24 What changes in this round (Text, mandatory N).
 Actions: Save Slip; Submit for Approval; Approve and Send; Quotation Slip; Key In; Save Terms; Resend; Revise quotation slip (new round); Terms final.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>CPC2 (seed), type CAMPAIGN, value basis RATE 1.00, on Motor and Property packages, ACTIVE</t>
+          <t>CPC2, type CAMPAIGN, value basis RATE 1.00, on Motor and Property packages, ACTIVE</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
